--- a/data/HIWIN_Specs.xlsx
+++ b/data/HIWIN_Specs.xlsx
@@ -1,22 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e11338\Desktop\Feed System GAI\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6503D3-DAC0-430B-8A84-B3AE07D3130B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FSV" sheetId="1" r:id="rId1"/>
-    <sheet name="FSI" sheetId="2" r:id="rId2"/>
-    <sheet name="RSI" sheetId="3" r:id="rId3"/>
+    <sheet name="FSW" sheetId="4" r:id="rId2"/>
+    <sheet name="FSI" sheetId="2" r:id="rId3"/>
+    <sheet name="RSI" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="635">
   <si>
     <t>型號</t>
   </si>
@@ -1929,12 +1936,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1942,8 +1949,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1989,17 +2003,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2037,7 +2059,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2071,6 +2093,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2105,9 +2128,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2280,11 +2304,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J202"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2316,7 +2340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2348,7 +2372,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2380,7 +2404,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2412,7 +2436,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2444,7 +2468,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2476,7 +2500,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2508,7 +2532,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2540,7 +2564,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2572,7 +2596,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2604,7 +2628,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2636,7 +2660,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2668,7 +2692,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2700,7 +2724,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2732,7 +2756,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2764,7 +2788,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2796,7 +2820,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2828,7 +2852,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2860,7 +2884,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2892,7 +2916,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2924,7 +2948,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2956,7 +2980,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2988,7 +3012,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -3020,7 +3044,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3052,7 +3076,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3084,7 +3108,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -3116,7 +3140,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -3148,7 +3172,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -3180,7 +3204,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -3212,7 +3236,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -3244,7 +3268,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3276,7 +3300,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -3308,7 +3332,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -3340,7 +3364,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -3372,7 +3396,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -3404,7 +3428,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -3436,7 +3460,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -3468,7 +3492,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -3500,7 +3524,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -3532,7 +3556,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -3564,7 +3588,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -3596,7 +3620,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -3628,7 +3652,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -3660,7 +3684,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -3692,7 +3716,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -3724,7 +3748,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -3756,7 +3780,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -3788,7 +3812,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3820,7 +3844,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -3852,7 +3876,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -3884,7 +3908,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -3916,7 +3940,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -3948,7 +3972,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -3980,7 +4004,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -4012,7 +4036,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -4044,7 +4068,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -4076,7 +4100,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -4108,7 +4132,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -4140,7 +4164,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -4172,7 +4196,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -4204,7 +4228,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -4236,7 +4260,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -4268,7 +4292,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -4300,7 +4324,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -4332,7 +4356,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -4364,7 +4388,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -4396,7 +4420,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -4428,7 +4452,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -4460,7 +4484,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>77</v>
       </c>
@@ -4492,7 +4516,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -4524,7 +4548,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -4556,7 +4580,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -4588,7 +4612,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -4620,7 +4644,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -4652,7 +4676,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -4684,7 +4708,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -4716,7 +4740,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -4748,7 +4772,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>86</v>
       </c>
@@ -4780,7 +4804,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -4812,7 +4836,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>88</v>
       </c>
@@ -4844,7 +4868,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -4876,7 +4900,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>90</v>
       </c>
@@ -4908,7 +4932,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>91</v>
       </c>
@@ -4940,7 +4964,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -4972,7 +4996,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -5004,7 +5028,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -5036,7 +5060,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>95</v>
       </c>
@@ -5068,7 +5092,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>96</v>
       </c>
@@ -5100,7 +5124,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -5132,7 +5156,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>98</v>
       </c>
@@ -5164,7 +5188,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -5196,7 +5220,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>100</v>
       </c>
@@ -5228,7 +5252,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>101</v>
       </c>
@@ -5260,7 +5284,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>102</v>
       </c>
@@ -5292,7 +5316,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>103</v>
       </c>
@@ -5324,7 +5348,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -5356,7 +5380,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -5388,7 +5412,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>106</v>
       </c>
@@ -5420,3345 +5444,24 @@
         <v>398</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
-      <c r="A99" t="s">
-        <v>107</v>
-      </c>
-      <c r="B99">
-        <v>12</v>
-      </c>
-      <c r="C99">
-        <v>4</v>
-      </c>
-      <c r="D99" t="s">
-        <v>133</v>
-      </c>
-      <c r="E99" t="s">
-        <v>183</v>
-      </c>
-      <c r="F99" t="s">
-        <v>230</v>
-      </c>
-      <c r="G99" t="s">
-        <v>237</v>
-      </c>
-      <c r="H99" t="s">
-        <v>304</v>
-      </c>
-      <c r="I99">
-        <v>383</v>
-      </c>
-      <c r="J99" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
-      <c r="A100" t="s">
-        <v>108</v>
-      </c>
-      <c r="B100">
-        <v>12</v>
-      </c>
-      <c r="C100">
-        <v>4</v>
-      </c>
-      <c r="D100" t="s">
-        <v>133</v>
-      </c>
-      <c r="E100" t="s">
-        <v>183</v>
-      </c>
-      <c r="F100" t="s">
-        <v>230</v>
-      </c>
-      <c r="G100" t="s">
-        <v>238</v>
-      </c>
-      <c r="H100" t="s">
-        <v>305</v>
-      </c>
-      <c r="I100">
-        <v>511</v>
-      </c>
-      <c r="J100" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
-      <c r="A101" t="s">
-        <v>109</v>
-      </c>
-      <c r="B101">
-        <v>12</v>
-      </c>
-      <c r="C101">
-        <v>5</v>
-      </c>
-      <c r="D101" t="s">
-        <v>133</v>
-      </c>
-      <c r="E101" t="s">
-        <v>183</v>
-      </c>
-      <c r="F101" t="s">
-        <v>230</v>
-      </c>
-      <c r="G101" t="s">
-        <v>237</v>
-      </c>
-      <c r="H101" t="s">
-        <v>304</v>
-      </c>
-      <c r="I101">
-        <v>383</v>
-      </c>
-      <c r="J101" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
-      <c r="A102" t="s">
-        <v>110</v>
-      </c>
-      <c r="B102">
-        <v>14</v>
-      </c>
-      <c r="C102">
-        <v>5</v>
-      </c>
-      <c r="D102" t="s">
-        <v>134</v>
-      </c>
-      <c r="E102" t="s">
-        <v>184</v>
-      </c>
-      <c r="F102" t="s">
-        <v>231</v>
-      </c>
-      <c r="G102" t="s">
-        <v>237</v>
-      </c>
-      <c r="H102" t="s">
-        <v>306</v>
-      </c>
-      <c r="I102">
-        <v>710</v>
-      </c>
-      <c r="J102" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" t="s">
-        <v>111</v>
-      </c>
-      <c r="B103">
-        <v>15</v>
-      </c>
-      <c r="C103">
-        <v>10</v>
-      </c>
-      <c r="D103" t="s">
-        <v>134</v>
-      </c>
-      <c r="E103" t="s">
-        <v>185</v>
-      </c>
-      <c r="F103" t="s">
-        <v>232</v>
-      </c>
-      <c r="G103" t="s">
-        <v>239</v>
-      </c>
-      <c r="H103" t="s">
-        <v>305</v>
-      </c>
-      <c r="I103">
-        <v>474</v>
-      </c>
-      <c r="J103" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" t="s">
-        <v>112</v>
-      </c>
-      <c r="B104">
-        <v>15</v>
-      </c>
-      <c r="C104">
-        <v>20</v>
-      </c>
-      <c r="D104" t="s">
-        <v>134</v>
-      </c>
-      <c r="E104" t="s">
-        <v>185</v>
-      </c>
-      <c r="F104" t="s">
-        <v>232</v>
-      </c>
-      <c r="G104" t="s">
-        <v>239</v>
-      </c>
-      <c r="H104" t="s">
-        <v>305</v>
-      </c>
-      <c r="I104">
-        <v>474</v>
-      </c>
-      <c r="J104" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" t="s">
-        <v>113</v>
-      </c>
-      <c r="B105">
-        <v>16</v>
-      </c>
-      <c r="C105">
-        <v>4</v>
-      </c>
-      <c r="D105" t="s">
-        <v>133</v>
-      </c>
-      <c r="E105" t="s">
-        <v>142</v>
-      </c>
-      <c r="F105" t="s">
-        <v>189</v>
-      </c>
-      <c r="G105" t="s">
-        <v>237</v>
-      </c>
-      <c r="H105" t="s">
-        <v>307</v>
-      </c>
-      <c r="I105">
-        <v>439</v>
-      </c>
-      <c r="J105" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
-      <c r="A106" t="s">
-        <v>11</v>
-      </c>
-      <c r="B106">
-        <v>16</v>
-      </c>
-      <c r="C106">
-        <v>5</v>
-      </c>
-      <c r="D106" t="s">
-        <v>134</v>
-      </c>
-      <c r="E106" t="s">
-        <v>143</v>
-      </c>
-      <c r="F106" t="s">
-        <v>190</v>
-      </c>
-      <c r="G106" t="s">
-        <v>237</v>
-      </c>
-      <c r="H106" t="s">
-        <v>244</v>
-      </c>
-      <c r="I106">
-        <v>763</v>
-      </c>
-      <c r="J106" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
-      <c r="A107" t="s">
-        <v>12</v>
-      </c>
-      <c r="B107">
-        <v>16</v>
-      </c>
-      <c r="C107">
-        <v>5</v>
-      </c>
-      <c r="D107" t="s">
-        <v>134</v>
-      </c>
-      <c r="E107" t="s">
-        <v>143</v>
-      </c>
-      <c r="F107" t="s">
-        <v>190</v>
-      </c>
-      <c r="G107" t="s">
-        <v>236</v>
-      </c>
-      <c r="H107" t="s">
-        <v>152</v>
-      </c>
-      <c r="I107">
-        <v>1385</v>
-      </c>
-      <c r="J107" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" t="s">
-        <v>13</v>
-      </c>
-      <c r="B108">
-        <v>16</v>
-      </c>
-      <c r="C108">
-        <v>5</v>
-      </c>
-      <c r="D108" t="s">
-        <v>134</v>
-      </c>
-      <c r="E108" t="s">
-        <v>143</v>
-      </c>
-      <c r="F108" t="s">
-        <v>190</v>
-      </c>
-      <c r="G108" t="s">
-        <v>238</v>
-      </c>
-      <c r="H108" t="s">
-        <v>245</v>
-      </c>
-      <c r="I108">
-        <v>1013</v>
-      </c>
-      <c r="J108" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109">
-        <v>20</v>
-      </c>
-      <c r="C109">
-        <v>5</v>
-      </c>
-      <c r="D109" t="s">
-        <v>134</v>
-      </c>
-      <c r="E109" t="s">
-        <v>144</v>
-      </c>
-      <c r="F109" t="s">
-        <v>191</v>
-      </c>
-      <c r="G109" t="s">
-        <v>237</v>
-      </c>
-      <c r="H109" t="s">
-        <v>246</v>
-      </c>
-      <c r="I109">
-        <v>837</v>
-      </c>
-      <c r="J109" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" t="s">
-        <v>16</v>
-      </c>
-      <c r="B110">
-        <v>20</v>
-      </c>
-      <c r="C110">
-        <v>5</v>
-      </c>
-      <c r="D110" t="s">
-        <v>134</v>
-      </c>
-      <c r="E110" t="s">
-        <v>144</v>
-      </c>
-      <c r="F110" t="s">
-        <v>191</v>
-      </c>
-      <c r="G110" t="s">
-        <v>236</v>
-      </c>
-      <c r="H110" t="s">
-        <v>247</v>
-      </c>
-      <c r="I110">
-        <v>1519</v>
-      </c>
-      <c r="J110" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
-      <c r="A111" t="s">
-        <v>17</v>
-      </c>
-      <c r="B111">
-        <v>20</v>
-      </c>
-      <c r="C111">
-        <v>6</v>
-      </c>
-      <c r="D111" t="s">
-        <v>135</v>
-      </c>
-      <c r="E111" t="s">
-        <v>145</v>
-      </c>
-      <c r="F111" t="s">
-        <v>192</v>
-      </c>
-      <c r="G111" t="s">
-        <v>237</v>
-      </c>
-      <c r="H111" t="s">
-        <v>248</v>
-      </c>
-      <c r="I111">
-        <v>1137</v>
-      </c>
-      <c r="J111" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" t="s">
-        <v>18</v>
-      </c>
-      <c r="B112">
-        <v>20</v>
-      </c>
-      <c r="C112">
-        <v>6</v>
-      </c>
-      <c r="D112" t="s">
-        <v>135</v>
-      </c>
-      <c r="E112" t="s">
-        <v>145</v>
-      </c>
-      <c r="F112" t="s">
-        <v>192</v>
-      </c>
-      <c r="G112" t="s">
-        <v>238</v>
-      </c>
-      <c r="H112" t="s">
-        <v>249</v>
-      </c>
-      <c r="I112">
-        <v>1512</v>
-      </c>
-      <c r="J112" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" t="s">
-        <v>114</v>
-      </c>
-      <c r="B113">
-        <v>25</v>
-      </c>
-      <c r="C113">
-        <v>4</v>
-      </c>
-      <c r="D113" t="s">
-        <v>133</v>
-      </c>
-      <c r="E113" t="s">
-        <v>186</v>
-      </c>
-      <c r="F113" t="s">
-        <v>233</v>
-      </c>
-      <c r="G113" t="s">
-        <v>236</v>
-      </c>
-      <c r="H113" t="s">
-        <v>308</v>
-      </c>
-      <c r="I113">
-        <v>976</v>
-      </c>
-      <c r="J113" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" t="s">
-        <v>20</v>
-      </c>
-      <c r="B114">
-        <v>25</v>
-      </c>
-      <c r="C114">
-        <v>5</v>
-      </c>
-      <c r="D114" t="s">
-        <v>134</v>
-      </c>
-      <c r="E114" t="s">
-        <v>146</v>
-      </c>
-      <c r="F114" t="s">
-        <v>193</v>
-      </c>
-      <c r="G114" t="s">
-        <v>236</v>
-      </c>
-      <c r="H114" t="s">
-        <v>251</v>
-      </c>
-      <c r="I114">
-        <v>1704</v>
-      </c>
-      <c r="J114" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" t="s">
-        <v>21</v>
-      </c>
-      <c r="B115">
-        <v>25</v>
-      </c>
-      <c r="C115">
-        <v>5</v>
-      </c>
-      <c r="D115" t="s">
-        <v>134</v>
-      </c>
-      <c r="E115" t="s">
-        <v>146</v>
-      </c>
-      <c r="F115" t="s">
-        <v>193</v>
-      </c>
-      <c r="G115" t="s">
-        <v>238</v>
-      </c>
-      <c r="H115" t="s">
-        <v>252</v>
-      </c>
-      <c r="I115">
-        <v>1252</v>
-      </c>
-      <c r="J115" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-      <c r="B116">
-        <v>25</v>
-      </c>
-      <c r="C116">
-        <v>6</v>
-      </c>
-      <c r="D116" t="s">
-        <v>135</v>
-      </c>
-      <c r="E116" t="s">
-        <v>147</v>
-      </c>
-      <c r="F116" t="s">
-        <v>194</v>
-      </c>
-      <c r="G116" t="s">
-        <v>237</v>
-      </c>
-      <c r="H116" t="s">
-        <v>269</v>
-      </c>
-      <c r="I116">
-        <v>1255</v>
-      </c>
-      <c r="J116" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" t="s">
-        <v>22</v>
-      </c>
-      <c r="B117">
-        <v>25</v>
-      </c>
-      <c r="C117">
-        <v>6</v>
-      </c>
-      <c r="D117" t="s">
-        <v>135</v>
-      </c>
-      <c r="E117" t="s">
-        <v>147</v>
-      </c>
-      <c r="F117" t="s">
-        <v>194</v>
-      </c>
-      <c r="G117" t="s">
-        <v>236</v>
-      </c>
-      <c r="H117" t="s">
-        <v>253</v>
-      </c>
-      <c r="I117">
-        <v>2308</v>
-      </c>
-      <c r="J117" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" t="s">
-        <v>23</v>
-      </c>
-      <c r="B118">
-        <v>25</v>
-      </c>
-      <c r="C118">
-        <v>6</v>
-      </c>
-      <c r="D118" t="s">
-        <v>135</v>
-      </c>
-      <c r="E118" t="s">
-        <v>147</v>
-      </c>
-      <c r="F118" t="s">
-        <v>194</v>
-      </c>
-      <c r="G118" t="s">
-        <v>238</v>
-      </c>
-      <c r="H118" t="s">
-        <v>252</v>
-      </c>
-      <c r="I118">
-        <v>1690</v>
-      </c>
-      <c r="J118" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" t="s">
-        <v>25</v>
-      </c>
-      <c r="B119">
-        <v>25</v>
-      </c>
-      <c r="C119">
-        <v>10</v>
-      </c>
-      <c r="D119" t="s">
-        <v>136</v>
-      </c>
-      <c r="E119" t="s">
-        <v>148</v>
-      </c>
-      <c r="F119" t="s">
-        <v>195</v>
-      </c>
-      <c r="G119" t="s">
-        <v>237</v>
-      </c>
-      <c r="H119" t="s">
-        <v>254</v>
-      </c>
-      <c r="I119">
-        <v>1592</v>
-      </c>
-      <c r="J119" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
-      <c r="A120" t="s">
-        <v>26</v>
-      </c>
-      <c r="B120">
-        <v>25</v>
-      </c>
-      <c r="C120">
-        <v>10</v>
-      </c>
-      <c r="D120" t="s">
-        <v>136</v>
-      </c>
-      <c r="E120" t="s">
-        <v>148</v>
-      </c>
-      <c r="F120" t="s">
-        <v>195</v>
-      </c>
-      <c r="G120" t="s">
-        <v>236</v>
-      </c>
-      <c r="H120" t="s">
-        <v>251</v>
-      </c>
-      <c r="I120">
-        <v>2888</v>
-      </c>
-      <c r="J120" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
-      <c r="A121" t="s">
-        <v>116</v>
-      </c>
-      <c r="B121">
-        <v>25</v>
-      </c>
-      <c r="C121">
-        <v>12</v>
-      </c>
-      <c r="D121" t="s">
-        <v>135</v>
-      </c>
-      <c r="E121" t="s">
-        <v>147</v>
-      </c>
-      <c r="F121" t="s">
-        <v>194</v>
-      </c>
-      <c r="G121" t="s">
-        <v>237</v>
-      </c>
-      <c r="H121" t="s">
-        <v>269</v>
-      </c>
-      <c r="I121">
-        <v>1271</v>
-      </c>
-      <c r="J121" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
-      <c r="A122" t="s">
-        <v>30</v>
-      </c>
-      <c r="B122">
-        <v>28</v>
-      </c>
-      <c r="C122">
-        <v>5</v>
-      </c>
-      <c r="D122" t="s">
-        <v>134</v>
-      </c>
-      <c r="E122" t="s">
-        <v>149</v>
-      </c>
-      <c r="F122" t="s">
-        <v>196</v>
-      </c>
-      <c r="G122" t="s">
-        <v>237</v>
-      </c>
-      <c r="H122" t="s">
-        <v>148</v>
-      </c>
-      <c r="I122">
-        <v>984</v>
-      </c>
-      <c r="J122" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" t="s">
-        <v>31</v>
-      </c>
-      <c r="B123">
-        <v>28</v>
-      </c>
-      <c r="C123">
-        <v>5</v>
-      </c>
-      <c r="D123" t="s">
-        <v>134</v>
-      </c>
-      <c r="E123" t="s">
-        <v>149</v>
-      </c>
-      <c r="F123" t="s">
-        <v>196</v>
-      </c>
-      <c r="G123" t="s">
-        <v>236</v>
-      </c>
-      <c r="H123" t="s">
-        <v>255</v>
-      </c>
-      <c r="I123">
-        <v>1785</v>
-      </c>
-      <c r="J123" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="A124" t="s">
-        <v>32</v>
-      </c>
-      <c r="B124">
-        <v>28</v>
-      </c>
-      <c r="C124">
-        <v>6</v>
-      </c>
-      <c r="D124" t="s">
-        <v>134</v>
-      </c>
-      <c r="E124" t="s">
-        <v>149</v>
-      </c>
-      <c r="F124" t="s">
-        <v>196</v>
-      </c>
-      <c r="G124" t="s">
-        <v>240</v>
-      </c>
-      <c r="H124" t="s">
-        <v>187</v>
-      </c>
-      <c r="I124">
-        <v>1150</v>
-      </c>
-      <c r="J124" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" t="s">
-        <v>117</v>
-      </c>
-      <c r="B125">
-        <v>28</v>
-      </c>
-      <c r="C125">
-        <v>12</v>
-      </c>
-      <c r="D125" t="s">
-        <v>136</v>
-      </c>
-      <c r="E125" t="s">
-        <v>187</v>
-      </c>
-      <c r="F125" t="s">
-        <v>234</v>
-      </c>
-      <c r="G125" t="s">
-        <v>236</v>
-      </c>
-      <c r="H125" t="s">
-        <v>165</v>
-      </c>
-      <c r="I125">
-        <v>3060</v>
-      </c>
-      <c r="J125" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
-      <c r="A126" t="s">
-        <v>118</v>
-      </c>
-      <c r="B126">
-        <v>28</v>
-      </c>
-      <c r="C126">
-        <v>16</v>
-      </c>
-      <c r="D126" t="s">
-        <v>136</v>
-      </c>
-      <c r="E126" t="s">
-        <v>187</v>
-      </c>
-      <c r="F126" t="s">
-        <v>234</v>
-      </c>
-      <c r="G126" t="s">
-        <v>237</v>
-      </c>
-      <c r="H126" t="s">
-        <v>254</v>
-      </c>
-      <c r="I126">
-        <v>1686</v>
-      </c>
-      <c r="J126" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
-      <c r="A127" t="s">
-        <v>34</v>
-      </c>
-      <c r="B127">
-        <v>32</v>
-      </c>
-      <c r="C127">
-        <v>5</v>
-      </c>
-      <c r="D127" t="s">
-        <v>134</v>
-      </c>
-      <c r="E127" t="s">
-        <v>150</v>
-      </c>
-      <c r="F127" t="s">
-        <v>197</v>
-      </c>
-      <c r="G127" t="s">
-        <v>236</v>
-      </c>
-      <c r="H127" t="s">
-        <v>256</v>
-      </c>
-      <c r="I127">
-        <v>1886</v>
-      </c>
-      <c r="J127" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
-      <c r="A128" t="s">
-        <v>35</v>
-      </c>
-      <c r="B128">
-        <v>32</v>
-      </c>
-      <c r="C128">
-        <v>5</v>
-      </c>
-      <c r="D128" t="s">
-        <v>134</v>
-      </c>
-      <c r="E128" t="s">
-        <v>150</v>
-      </c>
-      <c r="F128" t="s">
-        <v>197</v>
-      </c>
-      <c r="G128" t="s">
-        <v>238</v>
-      </c>
-      <c r="H128" t="s">
-        <v>247</v>
-      </c>
-      <c r="I128">
-        <v>1388</v>
-      </c>
-      <c r="J128" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10">
-      <c r="A129" t="s">
-        <v>36</v>
-      </c>
-      <c r="B129">
-        <v>32</v>
-      </c>
-      <c r="C129">
-        <v>6</v>
-      </c>
-      <c r="D129" t="s">
-        <v>135</v>
-      </c>
-      <c r="E129" t="s">
-        <v>151</v>
-      </c>
-      <c r="F129" t="s">
-        <v>198</v>
-      </c>
-      <c r="G129" t="s">
-        <v>236</v>
-      </c>
-      <c r="H129" t="s">
-        <v>257</v>
-      </c>
-      <c r="I129">
-        <v>2556</v>
-      </c>
-      <c r="J129" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10">
-      <c r="A130" t="s">
-        <v>37</v>
-      </c>
-      <c r="B130">
-        <v>32</v>
-      </c>
-      <c r="C130">
-        <v>6</v>
-      </c>
-      <c r="D130" t="s">
-        <v>135</v>
-      </c>
-      <c r="E130" t="s">
-        <v>151</v>
-      </c>
-      <c r="F130" t="s">
-        <v>198</v>
-      </c>
-      <c r="G130" t="s">
-        <v>238</v>
-      </c>
-      <c r="H130" t="s">
-        <v>247</v>
-      </c>
-      <c r="I130">
-        <v>1888</v>
-      </c>
-      <c r="J130" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10">
-      <c r="A131" t="s">
-        <v>38</v>
-      </c>
-      <c r="B131">
-        <v>32</v>
-      </c>
-      <c r="C131">
-        <v>8</v>
-      </c>
-      <c r="D131" t="s">
-        <v>136</v>
-      </c>
-      <c r="E131" t="s">
-        <v>152</v>
-      </c>
-      <c r="F131" t="s">
-        <v>199</v>
-      </c>
-      <c r="G131" t="s">
-        <v>236</v>
-      </c>
-      <c r="H131" t="s">
-        <v>258</v>
-      </c>
-      <c r="I131">
-        <v>3284</v>
-      </c>
-      <c r="J131" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10">
-      <c r="A132" t="s">
-        <v>39</v>
-      </c>
-      <c r="B132">
-        <v>32</v>
-      </c>
-      <c r="C132">
-        <v>8</v>
-      </c>
-      <c r="D132" t="s">
-        <v>136</v>
-      </c>
-      <c r="E132" t="s">
-        <v>152</v>
-      </c>
-      <c r="F132" t="s">
-        <v>199</v>
-      </c>
-      <c r="G132" t="s">
-        <v>238</v>
-      </c>
-      <c r="H132" t="s">
-        <v>158</v>
-      </c>
-      <c r="I132">
-        <v>2428</v>
-      </c>
-      <c r="J132" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10">
-      <c r="A133" t="s">
-        <v>41</v>
-      </c>
-      <c r="B133">
-        <v>32</v>
-      </c>
-      <c r="C133">
-        <v>10</v>
-      </c>
-      <c r="D133" t="s">
-        <v>137</v>
-      </c>
-      <c r="E133" t="s">
-        <v>153</v>
-      </c>
-      <c r="F133" t="s">
-        <v>200</v>
-      </c>
-      <c r="G133" t="s">
-        <v>236</v>
-      </c>
-      <c r="H133" t="s">
-        <v>260</v>
-      </c>
-      <c r="I133">
-        <v>4810</v>
-      </c>
-      <c r="J133" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10">
-      <c r="A134" t="s">
-        <v>42</v>
-      </c>
-      <c r="B134">
-        <v>32</v>
-      </c>
-      <c r="C134">
-        <v>10</v>
-      </c>
-      <c r="D134" t="s">
-        <v>137</v>
-      </c>
-      <c r="E134" t="s">
-        <v>153</v>
-      </c>
-      <c r="F134" t="s">
-        <v>200</v>
-      </c>
-      <c r="G134" t="s">
-        <v>238</v>
-      </c>
-      <c r="H134" t="s">
-        <v>261</v>
-      </c>
-      <c r="I134">
-        <v>3519</v>
-      </c>
-      <c r="J134" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10">
-      <c r="A135" t="s">
-        <v>119</v>
-      </c>
-      <c r="B135">
-        <v>32</v>
-      </c>
-      <c r="C135">
-        <v>12</v>
-      </c>
-      <c r="D135" t="s">
-        <v>137</v>
-      </c>
-      <c r="E135" t="s">
-        <v>153</v>
-      </c>
-      <c r="F135" t="s">
-        <v>200</v>
-      </c>
-      <c r="G135" t="s">
-        <v>240</v>
-      </c>
-      <c r="H135" t="s">
-        <v>309</v>
-      </c>
-      <c r="I135">
-        <v>3051</v>
-      </c>
-      <c r="J135" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
-      <c r="A136" t="s">
-        <v>120</v>
-      </c>
-      <c r="B136">
-        <v>32</v>
-      </c>
-      <c r="C136">
-        <v>12</v>
-      </c>
-      <c r="D136" t="s">
-        <v>137</v>
-      </c>
-      <c r="E136" t="s">
-        <v>153</v>
-      </c>
-      <c r="F136" t="s">
-        <v>200</v>
-      </c>
-      <c r="G136" t="s">
-        <v>236</v>
-      </c>
-      <c r="H136" t="s">
-        <v>258</v>
-      </c>
-      <c r="I136">
-        <v>4810</v>
-      </c>
-      <c r="J136" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10">
-      <c r="A137" t="s">
-        <v>121</v>
-      </c>
-      <c r="B137">
-        <v>32</v>
-      </c>
-      <c r="C137">
-        <v>16</v>
-      </c>
-      <c r="D137" t="s">
-        <v>137</v>
-      </c>
-      <c r="E137" t="s">
-        <v>153</v>
-      </c>
-      <c r="F137" t="s">
-        <v>200</v>
-      </c>
-      <c r="G137" t="s">
-        <v>240</v>
-      </c>
-      <c r="H137" t="s">
-        <v>310</v>
-      </c>
-      <c r="I137">
-        <v>3035</v>
-      </c>
-      <c r="J137" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10">
-      <c r="A138" t="s">
-        <v>43</v>
-      </c>
-      <c r="B138">
-        <v>32</v>
-      </c>
-      <c r="C138">
-        <v>16</v>
-      </c>
-      <c r="D138" t="s">
-        <v>137</v>
-      </c>
-      <c r="E138" t="s">
-        <v>153</v>
-      </c>
-      <c r="F138" t="s">
-        <v>200</v>
-      </c>
-      <c r="G138" t="s">
-        <v>237</v>
-      </c>
-      <c r="H138" t="s">
-        <v>259</v>
-      </c>
-      <c r="I138">
-        <v>2650</v>
-      </c>
-      <c r="J138" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
-      <c r="A139" t="s">
-        <v>122</v>
-      </c>
-      <c r="B139">
-        <v>32</v>
-      </c>
-      <c r="C139">
-        <v>16</v>
-      </c>
-      <c r="D139" t="s">
-        <v>137</v>
-      </c>
-      <c r="E139" t="s">
-        <v>153</v>
-      </c>
-      <c r="F139" t="s">
-        <v>200</v>
-      </c>
-      <c r="G139" t="s">
-        <v>236</v>
-      </c>
-      <c r="H139" t="s">
-        <v>258</v>
-      </c>
-      <c r="I139">
-        <v>4810</v>
-      </c>
-      <c r="J139" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
-      <c r="A140" t="s">
-        <v>123</v>
-      </c>
-      <c r="B140">
-        <v>32</v>
-      </c>
-      <c r="C140">
-        <v>20</v>
-      </c>
-      <c r="D140" t="s">
-        <v>137</v>
-      </c>
-      <c r="E140" t="s">
-        <v>153</v>
-      </c>
-      <c r="F140" t="s">
-        <v>200</v>
-      </c>
-      <c r="G140" t="s">
-        <v>240</v>
-      </c>
-      <c r="H140" t="s">
-        <v>309</v>
-      </c>
-      <c r="I140">
-        <v>3035</v>
-      </c>
-      <c r="J140" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10">
-      <c r="A141" t="s">
-        <v>44</v>
-      </c>
-      <c r="B141">
-        <v>32</v>
-      </c>
-      <c r="C141">
-        <v>20</v>
-      </c>
-      <c r="D141" t="s">
-        <v>137</v>
-      </c>
-      <c r="E141" t="s">
-        <v>153</v>
-      </c>
-      <c r="F141" t="s">
-        <v>200</v>
-      </c>
-      <c r="G141" t="s">
-        <v>237</v>
-      </c>
-      <c r="H141" t="s">
-        <v>259</v>
-      </c>
-      <c r="I141">
-        <v>2650</v>
-      </c>
-      <c r="J141" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
-      <c r="A142" t="s">
-        <v>47</v>
-      </c>
-      <c r="B142">
-        <v>36</v>
-      </c>
-      <c r="C142">
-        <v>6</v>
-      </c>
-      <c r="D142" t="s">
-        <v>135</v>
-      </c>
-      <c r="E142" t="s">
-        <v>154</v>
-      </c>
-      <c r="F142" t="s">
-        <v>201</v>
-      </c>
-      <c r="G142" t="s">
-        <v>237</v>
-      </c>
-      <c r="H142" t="s">
-        <v>252</v>
-      </c>
-      <c r="I142">
-        <v>1486</v>
-      </c>
-      <c r="J142" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
-      <c r="A143" t="s">
-        <v>48</v>
-      </c>
-      <c r="B143">
-        <v>36</v>
-      </c>
-      <c r="C143">
-        <v>6</v>
-      </c>
-      <c r="D143" t="s">
-        <v>135</v>
-      </c>
-      <c r="E143" t="s">
-        <v>154</v>
-      </c>
-      <c r="F143" t="s">
-        <v>201</v>
-      </c>
-      <c r="G143" t="s">
-        <v>236</v>
-      </c>
-      <c r="H143" t="s">
-        <v>260</v>
-      </c>
-      <c r="I143">
-        <v>2696</v>
-      </c>
-      <c r="J143" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
-      <c r="A144" t="s">
-        <v>49</v>
-      </c>
-      <c r="B144">
-        <v>36</v>
-      </c>
-      <c r="C144">
-        <v>10</v>
-      </c>
-      <c r="D144" t="s">
-        <v>137</v>
-      </c>
-      <c r="E144" t="s">
-        <v>155</v>
-      </c>
-      <c r="F144" t="s">
-        <v>202</v>
-      </c>
-      <c r="G144" t="s">
-        <v>236</v>
-      </c>
-      <c r="H144" t="s">
-        <v>263</v>
-      </c>
-      <c r="I144">
-        <v>5105</v>
-      </c>
-      <c r="J144" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
-      <c r="A145" t="s">
-        <v>124</v>
-      </c>
-      <c r="B145">
-        <v>36</v>
-      </c>
-      <c r="C145">
-        <v>12</v>
-      </c>
-      <c r="D145" t="s">
-        <v>137</v>
-      </c>
-      <c r="E145" t="s">
-        <v>155</v>
-      </c>
-      <c r="F145" t="s">
-        <v>202</v>
-      </c>
-      <c r="G145" t="s">
-        <v>236</v>
-      </c>
-      <c r="H145" t="s">
-        <v>311</v>
-      </c>
-      <c r="I145">
-        <v>5105</v>
-      </c>
-      <c r="J145" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10">
-      <c r="A146" t="s">
-        <v>125</v>
-      </c>
-      <c r="B146">
-        <v>36</v>
-      </c>
-      <c r="C146">
-        <v>16</v>
-      </c>
-      <c r="D146" t="s">
-        <v>137</v>
-      </c>
-      <c r="E146" t="s">
-        <v>155</v>
-      </c>
-      <c r="F146" t="s">
-        <v>202</v>
-      </c>
-      <c r="G146" t="s">
-        <v>238</v>
-      </c>
-      <c r="H146" t="s">
-        <v>251</v>
-      </c>
-      <c r="I146">
-        <v>3736</v>
-      </c>
-      <c r="J146" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10">
-      <c r="A147" t="s">
-        <v>50</v>
-      </c>
-      <c r="B147">
-        <v>40</v>
-      </c>
-      <c r="C147">
-        <v>5</v>
-      </c>
-      <c r="D147" t="s">
-        <v>134</v>
-      </c>
-      <c r="E147" t="s">
-        <v>156</v>
-      </c>
-      <c r="F147" t="s">
-        <v>203</v>
-      </c>
-      <c r="G147" t="s">
-        <v>236</v>
-      </c>
-      <c r="H147" t="s">
-        <v>175</v>
-      </c>
-      <c r="I147">
-        <v>2071</v>
-      </c>
-      <c r="J147" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
-      <c r="A148" t="s">
-        <v>51</v>
-      </c>
-      <c r="B148">
-        <v>40</v>
-      </c>
-      <c r="C148">
-        <v>6</v>
-      </c>
-      <c r="D148" t="s">
-        <v>135</v>
-      </c>
-      <c r="E148" t="s">
-        <v>157</v>
-      </c>
-      <c r="F148" t="s">
-        <v>204</v>
-      </c>
-      <c r="G148" t="s">
-        <v>236</v>
-      </c>
-      <c r="H148" t="s">
-        <v>264</v>
-      </c>
-      <c r="I148">
-        <v>2817</v>
-      </c>
-      <c r="J148" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10">
-      <c r="A149" t="s">
-        <v>52</v>
-      </c>
-      <c r="B149">
-        <v>40</v>
-      </c>
-      <c r="C149">
-        <v>8</v>
-      </c>
-      <c r="D149" t="s">
-        <v>136</v>
-      </c>
-      <c r="E149" t="s">
-        <v>158</v>
-      </c>
-      <c r="F149" t="s">
-        <v>205</v>
-      </c>
-      <c r="G149" t="s">
-        <v>236</v>
-      </c>
-      <c r="H149" t="s">
-        <v>265</v>
-      </c>
-      <c r="I149">
-        <v>3634</v>
-      </c>
-      <c r="J149" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
-      <c r="A150" t="s">
-        <v>53</v>
-      </c>
-      <c r="B150">
-        <v>40</v>
-      </c>
-      <c r="C150">
-        <v>8</v>
-      </c>
-      <c r="D150" t="s">
-        <v>136</v>
-      </c>
-      <c r="E150" t="s">
-        <v>158</v>
-      </c>
-      <c r="F150" t="s">
-        <v>205</v>
-      </c>
-      <c r="G150" t="s">
-        <v>238</v>
-      </c>
-      <c r="H150" t="s">
-        <v>266</v>
-      </c>
-      <c r="I150">
-        <v>2679</v>
-      </c>
-      <c r="J150" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
-      <c r="A151" t="s">
-        <v>54</v>
-      </c>
-      <c r="B151">
-        <v>40</v>
-      </c>
-      <c r="C151">
-        <v>10</v>
-      </c>
-      <c r="D151" t="s">
-        <v>137</v>
-      </c>
-      <c r="E151" t="s">
-        <v>159</v>
-      </c>
-      <c r="F151" t="s">
-        <v>206</v>
-      </c>
-      <c r="G151" t="s">
-        <v>236</v>
-      </c>
-      <c r="H151" t="s">
-        <v>267</v>
-      </c>
-      <c r="I151">
-        <v>5370</v>
-      </c>
-      <c r="J151" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
-      <c r="A152" t="s">
-        <v>55</v>
-      </c>
-      <c r="B152">
-        <v>40</v>
-      </c>
-      <c r="C152">
-        <v>10</v>
-      </c>
-      <c r="D152" t="s">
-        <v>137</v>
-      </c>
-      <c r="E152" t="s">
-        <v>159</v>
-      </c>
-      <c r="F152" t="s">
-        <v>206</v>
-      </c>
-      <c r="G152" t="s">
-        <v>238</v>
-      </c>
-      <c r="H152" t="s">
-        <v>165</v>
-      </c>
-      <c r="I152">
-        <v>3932</v>
-      </c>
-      <c r="J152" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
-      <c r="A153" t="s">
-        <v>126</v>
-      </c>
-      <c r="B153">
-        <v>40</v>
-      </c>
-      <c r="C153">
-        <v>12</v>
-      </c>
-      <c r="D153" t="s">
-        <v>138</v>
-      </c>
-      <c r="E153" t="s">
-        <v>160</v>
-      </c>
-      <c r="F153" t="s">
-        <v>207</v>
-      </c>
-      <c r="G153" t="s">
-        <v>237</v>
-      </c>
-      <c r="H153" t="s">
-        <v>310</v>
-      </c>
-      <c r="I153">
-        <v>3425</v>
-      </c>
-      <c r="J153" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
-      <c r="A154" t="s">
-        <v>56</v>
-      </c>
-      <c r="B154">
-        <v>40</v>
-      </c>
-      <c r="C154">
-        <v>12</v>
-      </c>
-      <c r="D154" t="s">
-        <v>138</v>
-      </c>
-      <c r="E154" t="s">
-        <v>160</v>
-      </c>
-      <c r="F154" t="s">
-        <v>207</v>
-      </c>
-      <c r="G154" t="s">
-        <v>236</v>
-      </c>
-      <c r="H154" t="s">
-        <v>268</v>
-      </c>
-      <c r="I154">
-        <v>6217</v>
-      </c>
-      <c r="J154" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10">
-      <c r="A155" t="s">
-        <v>127</v>
-      </c>
-      <c r="B155">
-        <v>40</v>
-      </c>
-      <c r="C155">
-        <v>16</v>
-      </c>
-      <c r="D155" t="s">
-        <v>138</v>
-      </c>
-      <c r="E155" t="s">
-        <v>160</v>
-      </c>
-      <c r="F155" t="s">
-        <v>207</v>
-      </c>
-      <c r="G155" t="s">
-        <v>240</v>
-      </c>
-      <c r="H155" t="s">
-        <v>312</v>
-      </c>
-      <c r="I155">
-        <v>4007</v>
-      </c>
-      <c r="J155" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
-      <c r="A156" t="s">
-        <v>128</v>
-      </c>
-      <c r="B156">
-        <v>40</v>
-      </c>
-      <c r="C156">
-        <v>16</v>
-      </c>
-      <c r="D156" t="s">
-        <v>138</v>
-      </c>
-      <c r="E156" t="s">
-        <v>160</v>
-      </c>
-      <c r="F156" t="s">
-        <v>207</v>
-      </c>
-      <c r="G156" t="s">
-        <v>237</v>
-      </c>
-      <c r="H156" t="s">
-        <v>309</v>
-      </c>
-      <c r="I156">
-        <v>3425</v>
-      </c>
-      <c r="J156" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10">
-      <c r="A157" t="s">
-        <v>61</v>
-      </c>
-      <c r="B157">
-        <v>45</v>
-      </c>
-      <c r="C157">
-        <v>10</v>
-      </c>
-      <c r="D157" t="s">
-        <v>137</v>
-      </c>
-      <c r="E157" t="s">
-        <v>161</v>
-      </c>
-      <c r="F157" t="s">
-        <v>208</v>
-      </c>
-      <c r="G157" t="s">
-        <v>237</v>
-      </c>
-      <c r="H157" t="s">
-        <v>270</v>
-      </c>
-      <c r="I157">
-        <v>3116</v>
-      </c>
-      <c r="J157" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10">
-      <c r="A158" t="s">
-        <v>62</v>
-      </c>
-      <c r="B158">
-        <v>45</v>
-      </c>
-      <c r="C158">
-        <v>10</v>
-      </c>
-      <c r="D158" t="s">
-        <v>137</v>
-      </c>
-      <c r="E158" t="s">
-        <v>161</v>
-      </c>
-      <c r="F158" t="s">
-        <v>208</v>
-      </c>
-      <c r="G158" t="s">
-        <v>236</v>
-      </c>
-      <c r="H158" t="s">
-        <v>271</v>
-      </c>
-      <c r="I158">
-        <v>5655</v>
-      </c>
-      <c r="J158" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10">
-      <c r="A159" t="s">
-        <v>63</v>
-      </c>
-      <c r="B159">
-        <v>45</v>
-      </c>
-      <c r="C159">
-        <v>12</v>
-      </c>
-      <c r="D159" t="s">
-        <v>139</v>
-      </c>
-      <c r="E159" t="s">
-        <v>162</v>
-      </c>
-      <c r="F159" t="s">
-        <v>209</v>
-      </c>
-      <c r="G159" t="s">
-        <v>236</v>
-      </c>
-      <c r="H159" t="s">
-        <v>272</v>
-      </c>
-      <c r="I159">
-        <v>7627</v>
-      </c>
-      <c r="J159" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10">
-      <c r="A160" t="s">
-        <v>64</v>
-      </c>
-      <c r="B160">
-        <v>50</v>
-      </c>
-      <c r="C160">
-        <v>5</v>
-      </c>
-      <c r="D160" t="s">
-        <v>134</v>
-      </c>
-      <c r="E160" t="s">
-        <v>163</v>
-      </c>
-      <c r="F160" t="s">
-        <v>210</v>
-      </c>
-      <c r="G160" t="s">
-        <v>240</v>
-      </c>
-      <c r="H160" t="s">
-        <v>253</v>
-      </c>
-      <c r="I160">
-        <v>1447</v>
-      </c>
-      <c r="J160" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10">
-      <c r="A161" t="s">
-        <v>65</v>
-      </c>
-      <c r="B161">
-        <v>50</v>
-      </c>
-      <c r="C161">
-        <v>5</v>
-      </c>
-      <c r="D161" t="s">
-        <v>134</v>
-      </c>
-      <c r="E161" t="s">
-        <v>163</v>
-      </c>
-      <c r="F161" t="s">
-        <v>210</v>
-      </c>
-      <c r="G161" t="s">
-        <v>241</v>
-      </c>
-      <c r="H161" t="s">
-        <v>273</v>
-      </c>
-      <c r="I161">
-        <v>2051</v>
-      </c>
-      <c r="J161" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10">
-      <c r="A162" t="s">
-        <v>66</v>
-      </c>
-      <c r="B162">
-        <v>50</v>
-      </c>
-      <c r="C162">
-        <v>6</v>
-      </c>
-      <c r="D162" t="s">
-        <v>135</v>
-      </c>
-      <c r="E162" t="s">
-        <v>164</v>
-      </c>
-      <c r="F162" t="s">
-        <v>211</v>
-      </c>
-      <c r="G162" t="s">
-        <v>236</v>
-      </c>
-      <c r="H162" t="s">
-        <v>272</v>
-      </c>
-      <c r="I162">
-        <v>3093</v>
-      </c>
-      <c r="J162" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10">
-      <c r="A163" t="s">
-        <v>129</v>
-      </c>
-      <c r="B163">
-        <v>50</v>
-      </c>
-      <c r="C163">
-        <v>6</v>
-      </c>
-      <c r="D163" t="s">
-        <v>135</v>
-      </c>
-      <c r="E163" t="s">
-        <v>164</v>
-      </c>
-      <c r="F163" t="s">
-        <v>211</v>
-      </c>
-      <c r="G163" t="s">
-        <v>243</v>
-      </c>
-      <c r="H163" t="s">
-        <v>288</v>
-      </c>
-      <c r="I163">
-        <v>4131</v>
-      </c>
-      <c r="J163" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
-      <c r="A164" t="s">
-        <v>67</v>
-      </c>
-      <c r="B164">
-        <v>50</v>
-      </c>
-      <c r="C164">
-        <v>6</v>
-      </c>
-      <c r="D164" t="s">
-        <v>135</v>
-      </c>
-      <c r="E164" t="s">
-        <v>164</v>
-      </c>
-      <c r="F164" t="s">
-        <v>211</v>
-      </c>
-      <c r="G164" t="s">
-        <v>242</v>
-      </c>
-      <c r="H164" t="s">
-        <v>274</v>
-      </c>
-      <c r="I164">
-        <v>4384</v>
-      </c>
-      <c r="J164" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10">
-      <c r="A165" t="s">
-        <v>68</v>
-      </c>
-      <c r="B165">
-        <v>50</v>
-      </c>
-      <c r="C165">
-        <v>8</v>
-      </c>
-      <c r="D165" t="s">
-        <v>136</v>
-      </c>
-      <c r="E165" t="s">
-        <v>165</v>
-      </c>
-      <c r="F165" t="s">
-        <v>212</v>
-      </c>
-      <c r="G165" t="s">
-        <v>236</v>
-      </c>
-      <c r="H165" t="s">
-        <v>275</v>
-      </c>
-      <c r="I165">
-        <v>4004</v>
-      </c>
-      <c r="J165" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10">
-      <c r="A166" t="s">
-        <v>69</v>
-      </c>
-      <c r="B166">
-        <v>50</v>
-      </c>
-      <c r="C166">
-        <v>8</v>
-      </c>
-      <c r="D166" t="s">
-        <v>136</v>
-      </c>
-      <c r="E166" t="s">
-        <v>165</v>
-      </c>
-      <c r="F166" t="s">
-        <v>212</v>
-      </c>
-      <c r="G166" t="s">
-        <v>242</v>
-      </c>
-      <c r="H166" t="s">
-        <v>276</v>
-      </c>
-      <c r="I166">
-        <v>5674</v>
-      </c>
-      <c r="J166" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10">
-      <c r="A167" t="s">
-        <v>70</v>
-      </c>
-      <c r="B167">
-        <v>50</v>
-      </c>
-      <c r="C167">
-        <v>10</v>
-      </c>
-      <c r="D167" t="s">
-        <v>137</v>
-      </c>
-      <c r="E167" t="s">
-        <v>166</v>
-      </c>
-      <c r="F167" t="s">
-        <v>213</v>
-      </c>
-      <c r="G167" t="s">
-        <v>236</v>
-      </c>
-      <c r="H167" t="s">
-        <v>277</v>
-      </c>
-      <c r="I167">
-        <v>5923</v>
-      </c>
-      <c r="J167" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10">
-      <c r="A168" t="s">
-        <v>71</v>
-      </c>
-      <c r="B168">
-        <v>50</v>
-      </c>
-      <c r="C168">
-        <v>10</v>
-      </c>
-      <c r="D168" t="s">
-        <v>137</v>
-      </c>
-      <c r="E168" t="s">
-        <v>166</v>
-      </c>
-      <c r="F168" t="s">
-        <v>213</v>
-      </c>
-      <c r="G168" t="s">
-        <v>242</v>
-      </c>
-      <c r="H168" t="s">
-        <v>278</v>
-      </c>
-      <c r="I168">
-        <v>8394</v>
-      </c>
-      <c r="J168" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10">
-      <c r="A169" t="s">
-        <v>72</v>
-      </c>
-      <c r="B169">
-        <v>50</v>
-      </c>
-      <c r="C169">
-        <v>10</v>
-      </c>
-      <c r="D169" t="s">
-        <v>137</v>
-      </c>
-      <c r="E169" t="s">
-        <v>166</v>
-      </c>
-      <c r="F169" t="s">
-        <v>213</v>
-      </c>
-      <c r="G169" t="s">
-        <v>238</v>
-      </c>
-      <c r="H169" t="s">
-        <v>260</v>
-      </c>
-      <c r="I169">
-        <v>4393</v>
-      </c>
-      <c r="J169" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10">
-      <c r="A170" t="s">
-        <v>73</v>
-      </c>
-      <c r="B170">
-        <v>50</v>
-      </c>
-      <c r="C170">
-        <v>12</v>
-      </c>
-      <c r="D170" t="s">
-        <v>139</v>
-      </c>
-      <c r="E170" t="s">
-        <v>167</v>
-      </c>
-      <c r="F170" t="s">
-        <v>214</v>
-      </c>
-      <c r="G170" t="s">
-        <v>237</v>
-      </c>
-      <c r="H170" t="s">
-        <v>251</v>
-      </c>
-      <c r="I170">
-        <v>4420</v>
-      </c>
-      <c r="J170" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10">
-      <c r="A171" t="s">
-        <v>74</v>
-      </c>
-      <c r="B171">
-        <v>50</v>
-      </c>
-      <c r="C171">
-        <v>12</v>
-      </c>
-      <c r="D171" t="s">
-        <v>139</v>
-      </c>
-      <c r="E171" t="s">
-        <v>167</v>
-      </c>
-      <c r="F171" t="s">
-        <v>214</v>
-      </c>
-      <c r="G171" t="s">
-        <v>236</v>
-      </c>
-      <c r="H171" t="s">
-        <v>279</v>
-      </c>
-      <c r="I171">
-        <v>8022</v>
-      </c>
-      <c r="J171" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10">
-      <c r="A172" t="s">
-        <v>75</v>
-      </c>
-      <c r="B172">
-        <v>50</v>
-      </c>
-      <c r="C172">
-        <v>12</v>
-      </c>
-      <c r="D172" t="s">
-        <v>139</v>
-      </c>
-      <c r="E172" t="s">
-        <v>167</v>
-      </c>
-      <c r="F172" t="s">
-        <v>214</v>
-      </c>
-      <c r="G172" t="s">
-        <v>238</v>
-      </c>
-      <c r="H172" t="s">
-        <v>280</v>
-      </c>
-      <c r="I172">
-        <v>5875</v>
-      </c>
-      <c r="J172" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10">
-      <c r="A173" t="s">
-        <v>130</v>
-      </c>
-      <c r="B173">
-        <v>50</v>
-      </c>
-      <c r="C173">
-        <v>30</v>
-      </c>
-      <c r="D173" t="s">
-        <v>137</v>
-      </c>
-      <c r="E173" t="s">
-        <v>166</v>
-      </c>
-      <c r="F173" t="s">
-        <v>213</v>
-      </c>
-      <c r="G173" t="s">
-        <v>240</v>
-      </c>
-      <c r="H173" t="s">
-        <v>313</v>
-      </c>
-      <c r="I173">
-        <v>3834</v>
-      </c>
-      <c r="J173" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10">
-      <c r="A174" t="s">
-        <v>131</v>
-      </c>
-      <c r="B174">
-        <v>55</v>
-      </c>
-      <c r="C174">
-        <v>10</v>
-      </c>
-      <c r="D174" t="s">
-        <v>137</v>
-      </c>
-      <c r="E174" t="s">
-        <v>168</v>
-      </c>
-      <c r="F174" t="s">
-        <v>215</v>
-      </c>
-      <c r="G174" t="s">
-        <v>236</v>
-      </c>
-      <c r="H174" t="s">
-        <v>314</v>
-      </c>
-      <c r="I174">
-        <v>6071</v>
-      </c>
-      <c r="J174" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10">
-      <c r="A175" t="s">
-        <v>78</v>
-      </c>
-      <c r="B175">
-        <v>55</v>
-      </c>
-      <c r="C175">
-        <v>10</v>
-      </c>
-      <c r="D175" t="s">
-        <v>137</v>
-      </c>
-      <c r="E175" t="s">
-        <v>168</v>
-      </c>
-      <c r="F175" t="s">
-        <v>215</v>
-      </c>
-      <c r="G175" t="s">
-        <v>238</v>
-      </c>
-      <c r="H175" t="s">
-        <v>175</v>
-      </c>
-      <c r="I175">
-        <v>4562</v>
-      </c>
-      <c r="J175" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10">
-      <c r="A176" t="s">
-        <v>79</v>
-      </c>
-      <c r="B176">
-        <v>55</v>
-      </c>
-      <c r="C176">
-        <v>12</v>
-      </c>
-      <c r="D176" t="s">
-        <v>139</v>
-      </c>
-      <c r="E176" t="s">
-        <v>169</v>
-      </c>
-      <c r="F176" t="s">
-        <v>216</v>
-      </c>
-      <c r="G176" t="s">
-        <v>236</v>
-      </c>
-      <c r="H176" t="s">
-        <v>282</v>
-      </c>
-      <c r="I176">
-        <v>8392</v>
-      </c>
-      <c r="J176" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10">
-      <c r="A177" t="s">
-        <v>132</v>
-      </c>
-      <c r="B177">
-        <v>60</v>
-      </c>
-      <c r="C177">
-        <v>12</v>
-      </c>
-      <c r="D177" t="s">
-        <v>139</v>
-      </c>
-      <c r="E177" t="s">
-        <v>188</v>
-      </c>
-      <c r="F177" t="s">
-        <v>235</v>
-      </c>
-      <c r="G177" t="s">
-        <v>236</v>
-      </c>
-      <c r="H177" t="s">
-        <v>315</v>
-      </c>
-      <c r="I177">
-        <v>8742</v>
-      </c>
-      <c r="J177" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10">
-      <c r="A178" t="s">
-        <v>81</v>
-      </c>
-      <c r="B178">
-        <v>63</v>
-      </c>
-      <c r="C178">
-        <v>8</v>
-      </c>
-      <c r="D178" t="s">
-        <v>136</v>
-      </c>
-      <c r="E178" t="s">
-        <v>171</v>
-      </c>
-      <c r="F178" t="s">
-        <v>218</v>
-      </c>
-      <c r="G178" t="s">
-        <v>240</v>
-      </c>
-      <c r="H178" t="s">
-        <v>284</v>
-      </c>
-      <c r="I178">
-        <v>2826</v>
-      </c>
-      <c r="J178" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10">
-      <c r="A179" t="s">
-        <v>82</v>
-      </c>
-      <c r="B179">
-        <v>63</v>
-      </c>
-      <c r="C179">
-        <v>8</v>
-      </c>
-      <c r="D179" t="s">
-        <v>136</v>
-      </c>
-      <c r="E179" t="s">
-        <v>171</v>
-      </c>
-      <c r="F179" t="s">
-        <v>218</v>
-      </c>
-      <c r="G179" t="s">
-        <v>241</v>
-      </c>
-      <c r="H179" t="s">
-        <v>285</v>
-      </c>
-      <c r="I179">
-        <v>4004</v>
-      </c>
-      <c r="J179" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10">
-      <c r="A180" t="s">
-        <v>83</v>
-      </c>
-      <c r="B180">
-        <v>63</v>
-      </c>
-      <c r="C180">
-        <v>10</v>
-      </c>
-      <c r="D180" t="s">
-        <v>137</v>
-      </c>
-      <c r="E180" t="s">
-        <v>172</v>
-      </c>
-      <c r="F180" t="s">
-        <v>219</v>
-      </c>
-      <c r="G180" t="s">
-        <v>236</v>
-      </c>
-      <c r="H180" t="s">
-        <v>286</v>
-      </c>
-      <c r="I180">
-        <v>6533</v>
-      </c>
-      <c r="J180" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10">
-      <c r="A181" t="s">
-        <v>84</v>
-      </c>
-      <c r="B181">
-        <v>63</v>
-      </c>
-      <c r="C181">
-        <v>10</v>
-      </c>
-      <c r="D181" t="s">
-        <v>137</v>
-      </c>
-      <c r="E181" t="s">
-        <v>172</v>
-      </c>
-      <c r="F181" t="s">
-        <v>219</v>
-      </c>
-      <c r="G181" t="s">
-        <v>242</v>
-      </c>
-      <c r="H181" t="s">
-        <v>287</v>
-      </c>
-      <c r="I181">
-        <v>9528</v>
-      </c>
-      <c r="J181" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10">
-      <c r="A182" t="s">
-        <v>85</v>
-      </c>
-      <c r="B182">
-        <v>63</v>
-      </c>
-      <c r="C182">
-        <v>12</v>
-      </c>
-      <c r="D182" t="s">
-        <v>139</v>
-      </c>
-      <c r="E182" t="s">
-        <v>173</v>
-      </c>
-      <c r="F182" t="s">
-        <v>220</v>
-      </c>
-      <c r="G182" t="s">
-        <v>236</v>
-      </c>
-      <c r="H182" t="s">
-        <v>288</v>
-      </c>
-      <c r="I182">
-        <v>8943</v>
-      </c>
-      <c r="J182" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10">
-      <c r="A183" t="s">
-        <v>86</v>
-      </c>
-      <c r="B183">
-        <v>63</v>
-      </c>
-      <c r="C183">
-        <v>16</v>
-      </c>
-      <c r="D183" t="s">
-        <v>141</v>
-      </c>
-      <c r="E183" t="s">
-        <v>174</v>
-      </c>
-      <c r="F183" t="s">
-        <v>221</v>
-      </c>
-      <c r="G183" t="s">
-        <v>236</v>
-      </c>
-      <c r="H183" t="s">
-        <v>289</v>
-      </c>
-      <c r="I183">
-        <v>14862</v>
-      </c>
-      <c r="J183" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10">
-      <c r="A184" t="s">
-        <v>87</v>
-      </c>
-      <c r="B184">
-        <v>63</v>
-      </c>
-      <c r="C184">
-        <v>20</v>
-      </c>
-      <c r="D184" t="s">
-        <v>141</v>
-      </c>
-      <c r="E184" t="s">
-        <v>174</v>
-      </c>
-      <c r="F184" t="s">
-        <v>221</v>
-      </c>
-      <c r="G184" t="s">
-        <v>236</v>
-      </c>
-      <c r="H184" t="s">
-        <v>289</v>
-      </c>
-      <c r="I184">
-        <v>14862</v>
-      </c>
-      <c r="J184" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10">
-      <c r="A185" t="s">
-        <v>89</v>
-      </c>
-      <c r="B185">
-        <v>70</v>
-      </c>
-      <c r="C185">
-        <v>10</v>
-      </c>
-      <c r="D185" t="s">
-        <v>137</v>
-      </c>
-      <c r="E185" t="s">
-        <v>176</v>
-      </c>
-      <c r="F185" t="s">
-        <v>223</v>
-      </c>
-      <c r="G185" t="s">
-        <v>236</v>
-      </c>
-      <c r="H185" t="s">
-        <v>291</v>
-      </c>
-      <c r="I185">
-        <v>6843</v>
-      </c>
-      <c r="J185" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10">
-      <c r="A186" t="s">
-        <v>90</v>
-      </c>
-      <c r="B186">
-        <v>70</v>
-      </c>
-      <c r="C186">
-        <v>10</v>
-      </c>
-      <c r="D186" t="s">
-        <v>137</v>
-      </c>
-      <c r="E186" t="s">
-        <v>176</v>
-      </c>
-      <c r="F186" t="s">
-        <v>223</v>
-      </c>
-      <c r="G186" t="s">
-        <v>242</v>
-      </c>
-      <c r="H186" t="s">
-        <v>292</v>
-      </c>
-      <c r="I186">
-        <v>9698</v>
-      </c>
-      <c r="J186" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10">
-      <c r="A187" t="s">
-        <v>91</v>
-      </c>
-      <c r="B187">
-        <v>70</v>
-      </c>
-      <c r="C187">
-        <v>12</v>
-      </c>
-      <c r="D187" t="s">
-        <v>139</v>
-      </c>
-      <c r="E187" t="s">
-        <v>177</v>
-      </c>
-      <c r="F187" t="s">
-        <v>224</v>
-      </c>
-      <c r="G187" t="s">
-        <v>236</v>
-      </c>
-      <c r="H187" t="s">
-        <v>293</v>
-      </c>
-      <c r="I187">
-        <v>9382</v>
-      </c>
-      <c r="J187" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10">
-      <c r="A188" t="s">
-        <v>92</v>
-      </c>
-      <c r="B188">
-        <v>70</v>
-      </c>
-      <c r="C188">
-        <v>12</v>
-      </c>
-      <c r="D188" t="s">
-        <v>139</v>
-      </c>
-      <c r="E188" t="s">
-        <v>177</v>
-      </c>
-      <c r="F188" t="s">
-        <v>224</v>
-      </c>
-      <c r="G188" t="s">
-        <v>242</v>
-      </c>
-      <c r="H188" t="s">
-        <v>292</v>
-      </c>
-      <c r="I188">
-        <v>13296</v>
-      </c>
-      <c r="J188" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10">
-      <c r="A189" t="s">
-        <v>93</v>
-      </c>
-      <c r="B189">
-        <v>80</v>
-      </c>
-      <c r="C189">
-        <v>10</v>
-      </c>
-      <c r="D189" t="s">
-        <v>137</v>
-      </c>
-      <c r="E189" t="s">
-        <v>178</v>
-      </c>
-      <c r="F189" t="s">
-        <v>225</v>
-      </c>
-      <c r="G189" t="s">
-        <v>236</v>
-      </c>
-      <c r="H189" t="s">
-        <v>294</v>
-      </c>
-      <c r="I189">
-        <v>7202</v>
-      </c>
-      <c r="J189" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10">
-      <c r="A190" t="s">
-        <v>94</v>
-      </c>
-      <c r="B190">
-        <v>80</v>
-      </c>
-      <c r="C190">
-        <v>10</v>
-      </c>
-      <c r="D190" t="s">
-        <v>137</v>
-      </c>
-      <c r="E190" t="s">
-        <v>178</v>
-      </c>
-      <c r="F190" t="s">
-        <v>225</v>
-      </c>
-      <c r="G190" t="s">
-        <v>242</v>
-      </c>
-      <c r="H190" t="s">
-        <v>295</v>
-      </c>
-      <c r="I190">
-        <v>10207</v>
-      </c>
-      <c r="J190" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10">
-      <c r="A191" t="s">
-        <v>95</v>
-      </c>
-      <c r="B191">
-        <v>80</v>
-      </c>
-      <c r="C191">
-        <v>12</v>
-      </c>
-      <c r="D191" t="s">
-        <v>139</v>
-      </c>
-      <c r="E191" t="s">
-        <v>179</v>
-      </c>
-      <c r="F191" t="s">
-        <v>226</v>
-      </c>
-      <c r="G191" t="s">
-        <v>236</v>
-      </c>
-      <c r="H191" t="s">
-        <v>296</v>
-      </c>
-      <c r="I191">
-        <v>9797</v>
-      </c>
-      <c r="J191" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10">
-      <c r="A192" t="s">
-        <v>96</v>
-      </c>
-      <c r="B192">
-        <v>80</v>
-      </c>
-      <c r="C192">
-        <v>12</v>
-      </c>
-      <c r="D192" t="s">
-        <v>139</v>
-      </c>
-      <c r="E192" t="s">
-        <v>179</v>
-      </c>
-      <c r="F192" t="s">
-        <v>226</v>
-      </c>
-      <c r="G192" t="s">
-        <v>242</v>
-      </c>
-      <c r="H192" t="s">
-        <v>297</v>
-      </c>
-      <c r="I192">
-        <v>13844</v>
-      </c>
-      <c r="J192" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10">
-      <c r="A193" t="s">
-        <v>97</v>
-      </c>
-      <c r="B193">
-        <v>80</v>
-      </c>
-      <c r="C193">
-        <v>16</v>
-      </c>
-      <c r="D193" t="s">
-        <v>141</v>
-      </c>
-      <c r="E193" t="s">
-        <v>180</v>
-      </c>
-      <c r="F193" t="s">
-        <v>227</v>
-      </c>
-      <c r="G193" t="s">
-        <v>236</v>
-      </c>
-      <c r="H193" t="s">
-        <v>298</v>
-      </c>
-      <c r="I193">
-        <v>16485</v>
-      </c>
-      <c r="J193" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10">
-      <c r="A194" t="s">
-        <v>98</v>
-      </c>
-      <c r="B194">
-        <v>80</v>
-      </c>
-      <c r="C194">
-        <v>16</v>
-      </c>
-      <c r="D194" t="s">
-        <v>141</v>
-      </c>
-      <c r="E194" t="s">
-        <v>180</v>
-      </c>
-      <c r="F194" t="s">
-        <v>227</v>
-      </c>
-      <c r="G194" t="s">
-        <v>242</v>
-      </c>
-      <c r="H194" t="s">
-        <v>299</v>
-      </c>
-      <c r="I194">
-        <v>23363</v>
-      </c>
-      <c r="J194" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10">
-      <c r="A195" t="s">
-        <v>99</v>
-      </c>
-      <c r="B195">
-        <v>80</v>
-      </c>
-      <c r="C195">
-        <v>20</v>
-      </c>
-      <c r="D195" t="s">
-        <v>141</v>
-      </c>
-      <c r="E195" t="s">
-        <v>180</v>
-      </c>
-      <c r="F195" t="s">
-        <v>227</v>
-      </c>
-      <c r="G195" t="s">
-        <v>236</v>
-      </c>
-      <c r="H195" t="s">
-        <v>298</v>
-      </c>
-      <c r="I195">
-        <v>16485</v>
-      </c>
-      <c r="J195" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10">
-      <c r="A196" t="s">
-        <v>100</v>
-      </c>
-      <c r="B196">
-        <v>80</v>
-      </c>
-      <c r="C196">
-        <v>20</v>
-      </c>
-      <c r="D196" t="s">
-        <v>141</v>
-      </c>
-      <c r="E196" t="s">
-        <v>180</v>
-      </c>
-      <c r="F196" t="s">
-        <v>227</v>
-      </c>
-      <c r="G196" t="s">
-        <v>242</v>
-      </c>
-      <c r="H196" t="s">
-        <v>299</v>
-      </c>
-      <c r="I196">
-        <v>23363</v>
-      </c>
-      <c r="J196" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10">
-      <c r="A197" t="s">
-        <v>101</v>
-      </c>
-      <c r="B197">
-        <v>100</v>
-      </c>
-      <c r="C197">
-        <v>12</v>
-      </c>
-      <c r="D197" t="s">
-        <v>139</v>
-      </c>
-      <c r="E197" t="s">
-        <v>181</v>
-      </c>
-      <c r="F197" t="s">
-        <v>228</v>
-      </c>
-      <c r="G197" t="s">
-        <v>236</v>
-      </c>
-      <c r="H197" t="s">
-        <v>300</v>
-      </c>
-      <c r="I197">
-        <v>10761</v>
-      </c>
-      <c r="J197" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10">
-      <c r="A198" t="s">
-        <v>102</v>
-      </c>
-      <c r="B198">
-        <v>100</v>
-      </c>
-      <c r="C198">
-        <v>12</v>
-      </c>
-      <c r="D198" t="s">
-        <v>139</v>
-      </c>
-      <c r="E198" t="s">
-        <v>181</v>
-      </c>
-      <c r="F198" t="s">
-        <v>228</v>
-      </c>
-      <c r="G198" t="s">
-        <v>242</v>
-      </c>
-      <c r="H198" t="s">
-        <v>301</v>
-      </c>
-      <c r="I198">
-        <v>15251</v>
-      </c>
-      <c r="J198" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10">
-      <c r="A199" t="s">
-        <v>103</v>
-      </c>
-      <c r="B199">
-        <v>100</v>
-      </c>
-      <c r="C199">
-        <v>16</v>
-      </c>
-      <c r="D199" t="s">
-        <v>141</v>
-      </c>
-      <c r="E199" t="s">
-        <v>182</v>
-      </c>
-      <c r="F199" t="s">
-        <v>229</v>
-      </c>
-      <c r="G199" t="s">
-        <v>236</v>
-      </c>
-      <c r="H199" t="s">
-        <v>302</v>
-      </c>
-      <c r="I199">
-        <v>18123</v>
-      </c>
-      <c r="J199" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10">
-      <c r="A200" t="s">
-        <v>104</v>
-      </c>
-      <c r="B200">
-        <v>100</v>
-      </c>
-      <c r="C200">
-        <v>16</v>
-      </c>
-      <c r="D200" t="s">
-        <v>141</v>
-      </c>
-      <c r="E200" t="s">
-        <v>182</v>
-      </c>
-      <c r="F200" t="s">
-        <v>229</v>
-      </c>
-      <c r="G200" t="s">
-        <v>242</v>
-      </c>
-      <c r="H200" t="s">
-        <v>303</v>
-      </c>
-      <c r="I200">
-        <v>25684</v>
-      </c>
-      <c r="J200" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10">
-      <c r="A201" t="s">
-        <v>105</v>
-      </c>
-      <c r="B201">
-        <v>100</v>
-      </c>
-      <c r="C201">
-        <v>20</v>
-      </c>
-      <c r="D201" t="s">
-        <v>141</v>
-      </c>
-      <c r="E201" t="s">
-        <v>182</v>
-      </c>
-      <c r="F201" t="s">
-        <v>229</v>
-      </c>
-      <c r="G201" t="s">
-        <v>236</v>
-      </c>
-      <c r="H201" t="s">
-        <v>302</v>
-      </c>
-      <c r="I201">
-        <v>18123</v>
-      </c>
-      <c r="J201" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10">
-      <c r="A202" t="s">
-        <v>106</v>
-      </c>
-      <c r="B202">
-        <v>100</v>
-      </c>
-      <c r="C202">
-        <v>20</v>
-      </c>
-      <c r="D202" t="s">
-        <v>141</v>
-      </c>
-      <c r="E202" t="s">
-        <v>182</v>
-      </c>
-      <c r="F202" t="s">
-        <v>229</v>
-      </c>
-      <c r="G202" t="s">
-        <v>242</v>
-      </c>
-      <c r="H202" t="s">
-        <v>303</v>
-      </c>
-      <c r="I202">
-        <v>25684</v>
-      </c>
-      <c r="J202" t="s">
-        <v>423</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J84"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2078E8EE-8E84-43E7-8FDD-74AD65B3F347}">
+  <dimension ref="A1:J105"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8790,7 +5493,3379 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I2">
+        <v>383</v>
+      </c>
+      <c r="J2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I3">
+        <v>511</v>
+      </c>
+      <c r="J3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H4" t="s">
+        <v>304</v>
+      </c>
+      <c r="I4">
+        <v>383</v>
+      </c>
+      <c r="J4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" t="s">
+        <v>231</v>
+      </c>
+      <c r="G5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H5" t="s">
+        <v>306</v>
+      </c>
+      <c r="I5">
+        <v>710</v>
+      </c>
+      <c r="J5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" t="s">
+        <v>239</v>
+      </c>
+      <c r="H6" t="s">
+        <v>305</v>
+      </c>
+      <c r="I6">
+        <v>474</v>
+      </c>
+      <c r="J6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G7" t="s">
+        <v>239</v>
+      </c>
+      <c r="H7" t="s">
+        <v>305</v>
+      </c>
+      <c r="I7">
+        <v>474</v>
+      </c>
+      <c r="J7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H8" t="s">
+        <v>307</v>
+      </c>
+      <c r="I8">
+        <v>439</v>
+      </c>
+      <c r="J8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G9" t="s">
+        <v>237</v>
+      </c>
+      <c r="H9" t="s">
+        <v>244</v>
+      </c>
+      <c r="I9">
+        <v>763</v>
+      </c>
+      <c r="J9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" t="s">
+        <v>190</v>
+      </c>
+      <c r="G10" t="s">
+        <v>236</v>
+      </c>
+      <c r="H10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I10">
+        <v>1385</v>
+      </c>
+      <c r="J10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G11" t="s">
+        <v>238</v>
+      </c>
+      <c r="H11" t="s">
+        <v>245</v>
+      </c>
+      <c r="I11">
+        <v>1013</v>
+      </c>
+      <c r="J11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G12" t="s">
+        <v>237</v>
+      </c>
+      <c r="H12" t="s">
+        <v>246</v>
+      </c>
+      <c r="I12">
+        <v>837</v>
+      </c>
+      <c r="J12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G13" t="s">
+        <v>236</v>
+      </c>
+      <c r="H13" t="s">
+        <v>247</v>
+      </c>
+      <c r="I13">
+        <v>1519</v>
+      </c>
+      <c r="J13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" t="s">
+        <v>192</v>
+      </c>
+      <c r="G14" t="s">
+        <v>237</v>
+      </c>
+      <c r="H14" t="s">
+        <v>248</v>
+      </c>
+      <c r="I14">
+        <v>1137</v>
+      </c>
+      <c r="J14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F15" t="s">
+        <v>192</v>
+      </c>
+      <c r="G15" t="s">
+        <v>238</v>
+      </c>
+      <c r="H15" t="s">
+        <v>249</v>
+      </c>
+      <c r="I15">
+        <v>1512</v>
+      </c>
+      <c r="J15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F16" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" t="s">
+        <v>236</v>
+      </c>
+      <c r="H16" t="s">
+        <v>308</v>
+      </c>
+      <c r="I16">
+        <v>976</v>
+      </c>
+      <c r="J16" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" t="s">
+        <v>193</v>
+      </c>
+      <c r="G17" t="s">
+        <v>236</v>
+      </c>
+      <c r="H17" t="s">
+        <v>251</v>
+      </c>
+      <c r="I17">
+        <v>1704</v>
+      </c>
+      <c r="J17" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" t="s">
+        <v>238</v>
+      </c>
+      <c r="H18" t="s">
+        <v>252</v>
+      </c>
+      <c r="I18">
+        <v>1252</v>
+      </c>
+      <c r="J18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" t="s">
+        <v>194</v>
+      </c>
+      <c r="G19" t="s">
+        <v>237</v>
+      </c>
+      <c r="H19" t="s">
+        <v>269</v>
+      </c>
+      <c r="I19">
+        <v>1255</v>
+      </c>
+      <c r="J19" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G20" t="s">
+        <v>236</v>
+      </c>
+      <c r="H20" t="s">
+        <v>253</v>
+      </c>
+      <c r="I20">
+        <v>2308</v>
+      </c>
+      <c r="J20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" t="s">
+        <v>194</v>
+      </c>
+      <c r="G21" t="s">
+        <v>238</v>
+      </c>
+      <c r="H21" t="s">
+        <v>252</v>
+      </c>
+      <c r="I21">
+        <v>1690</v>
+      </c>
+      <c r="J21" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" t="s">
+        <v>195</v>
+      </c>
+      <c r="G22" t="s">
+        <v>237</v>
+      </c>
+      <c r="H22" t="s">
+        <v>254</v>
+      </c>
+      <c r="I22">
+        <v>1592</v>
+      </c>
+      <c r="J22" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" t="s">
+        <v>195</v>
+      </c>
+      <c r="G23" t="s">
+        <v>236</v>
+      </c>
+      <c r="H23" t="s">
+        <v>251</v>
+      </c>
+      <c r="I23">
+        <v>2888</v>
+      </c>
+      <c r="J23" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" t="s">
+        <v>194</v>
+      </c>
+      <c r="G24" t="s">
+        <v>237</v>
+      </c>
+      <c r="H24" t="s">
+        <v>269</v>
+      </c>
+      <c r="I24">
+        <v>1271</v>
+      </c>
+      <c r="J24" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25">
+        <v>28</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" t="s">
+        <v>196</v>
+      </c>
+      <c r="G25" t="s">
+        <v>237</v>
+      </c>
+      <c r="H25" t="s">
+        <v>148</v>
+      </c>
+      <c r="I25">
+        <v>984</v>
+      </c>
+      <c r="J25" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26">
+        <v>28</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" t="s">
+        <v>236</v>
+      </c>
+      <c r="H26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I26">
+        <v>1785</v>
+      </c>
+      <c r="J26" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27">
+        <v>28</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" t="s">
+        <v>240</v>
+      </c>
+      <c r="H27" t="s">
+        <v>187</v>
+      </c>
+      <c r="I27">
+        <v>1150</v>
+      </c>
+      <c r="J27" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28">
+        <v>28</v>
+      </c>
+      <c r="C28">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" t="s">
+        <v>234</v>
+      </c>
+      <c r="G28" t="s">
+        <v>236</v>
+      </c>
+      <c r="H28" t="s">
+        <v>165</v>
+      </c>
+      <c r="I28">
+        <v>3060</v>
+      </c>
+      <c r="J28" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" t="s">
+        <v>187</v>
+      </c>
+      <c r="F29" t="s">
+        <v>234</v>
+      </c>
+      <c r="G29" t="s">
+        <v>237</v>
+      </c>
+      <c r="H29" t="s">
+        <v>254</v>
+      </c>
+      <c r="I29">
+        <v>1686</v>
+      </c>
+      <c r="J29" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30">
+        <v>32</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" t="s">
+        <v>197</v>
+      </c>
+      <c r="G30" t="s">
+        <v>236</v>
+      </c>
+      <c r="H30" t="s">
+        <v>256</v>
+      </c>
+      <c r="I30">
+        <v>1886</v>
+      </c>
+      <c r="J30" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31">
+        <v>32</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" t="s">
+        <v>238</v>
+      </c>
+      <c r="H31" t="s">
+        <v>247</v>
+      </c>
+      <c r="I31">
+        <v>1388</v>
+      </c>
+      <c r="J31" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>32</v>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" t="s">
+        <v>236</v>
+      </c>
+      <c r="H32" t="s">
+        <v>257</v>
+      </c>
+      <c r="I32">
+        <v>2556</v>
+      </c>
+      <c r="J32" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" t="s">
+        <v>238</v>
+      </c>
+      <c r="H33" t="s">
+        <v>247</v>
+      </c>
+      <c r="I33">
+        <v>1888</v>
+      </c>
+      <c r="J33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" t="s">
+        <v>152</v>
+      </c>
+      <c r="F34" t="s">
+        <v>199</v>
+      </c>
+      <c r="G34" t="s">
+        <v>236</v>
+      </c>
+      <c r="H34" t="s">
+        <v>258</v>
+      </c>
+      <c r="I34">
+        <v>3284</v>
+      </c>
+      <c r="J34" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" t="s">
+        <v>199</v>
+      </c>
+      <c r="G35" t="s">
+        <v>238</v>
+      </c>
+      <c r="H35" t="s">
+        <v>158</v>
+      </c>
+      <c r="I35">
+        <v>2428</v>
+      </c>
+      <c r="J35" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" t="s">
+        <v>153</v>
+      </c>
+      <c r="F36" t="s">
+        <v>200</v>
+      </c>
+      <c r="G36" t="s">
+        <v>236</v>
+      </c>
+      <c r="H36" t="s">
+        <v>260</v>
+      </c>
+      <c r="I36">
+        <v>4810</v>
+      </c>
+      <c r="J36" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37">
+        <v>32</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" t="s">
+        <v>153</v>
+      </c>
+      <c r="F37" t="s">
+        <v>200</v>
+      </c>
+      <c r="G37" t="s">
+        <v>238</v>
+      </c>
+      <c r="H37" t="s">
+        <v>261</v>
+      </c>
+      <c r="I37">
+        <v>3519</v>
+      </c>
+      <c r="J37" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" t="s">
+        <v>153</v>
+      </c>
+      <c r="F38" t="s">
+        <v>200</v>
+      </c>
+      <c r="G38" t="s">
+        <v>240</v>
+      </c>
+      <c r="H38" t="s">
+        <v>309</v>
+      </c>
+      <c r="I38">
+        <v>3051</v>
+      </c>
+      <c r="J38" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" t="s">
+        <v>153</v>
+      </c>
+      <c r="F39" t="s">
+        <v>200</v>
+      </c>
+      <c r="G39" t="s">
+        <v>236</v>
+      </c>
+      <c r="H39" t="s">
+        <v>258</v>
+      </c>
+      <c r="I39">
+        <v>4810</v>
+      </c>
+      <c r="J39" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40">
+        <v>32</v>
+      </c>
+      <c r="C40">
+        <v>16</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" t="s">
+        <v>153</v>
+      </c>
+      <c r="F40" t="s">
+        <v>200</v>
+      </c>
+      <c r="G40" t="s">
+        <v>240</v>
+      </c>
+      <c r="H40" t="s">
+        <v>310</v>
+      </c>
+      <c r="I40">
+        <v>3035</v>
+      </c>
+      <c r="J40" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41">
+        <v>32</v>
+      </c>
+      <c r="C41">
+        <v>16</v>
+      </c>
+      <c r="D41" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" t="s">
+        <v>200</v>
+      </c>
+      <c r="G41" t="s">
+        <v>237</v>
+      </c>
+      <c r="H41" t="s">
+        <v>259</v>
+      </c>
+      <c r="I41">
+        <v>2650</v>
+      </c>
+      <c r="J41" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42">
+        <v>32</v>
+      </c>
+      <c r="C42">
+        <v>16</v>
+      </c>
+      <c r="D42" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F42" t="s">
+        <v>200</v>
+      </c>
+      <c r="G42" t="s">
+        <v>236</v>
+      </c>
+      <c r="H42" t="s">
+        <v>258</v>
+      </c>
+      <c r="I42">
+        <v>4810</v>
+      </c>
+      <c r="J42" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43">
+        <v>32</v>
+      </c>
+      <c r="C43">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" t="s">
+        <v>200</v>
+      </c>
+      <c r="G43" t="s">
+        <v>240</v>
+      </c>
+      <c r="H43" t="s">
+        <v>309</v>
+      </c>
+      <c r="I43">
+        <v>3035</v>
+      </c>
+      <c r="J43" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>32</v>
+      </c>
+      <c r="C44">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" t="s">
+        <v>153</v>
+      </c>
+      <c r="F44" t="s">
+        <v>200</v>
+      </c>
+      <c r="G44" t="s">
+        <v>237</v>
+      </c>
+      <c r="H44" t="s">
+        <v>259</v>
+      </c>
+      <c r="I44">
+        <v>2650</v>
+      </c>
+      <c r="J44" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45">
+        <v>36</v>
+      </c>
+      <c r="C45">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s">
+        <v>135</v>
+      </c>
+      <c r="E45" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" t="s">
+        <v>201</v>
+      </c>
+      <c r="G45" t="s">
+        <v>237</v>
+      </c>
+      <c r="H45" t="s">
+        <v>252</v>
+      </c>
+      <c r="I45">
+        <v>1486</v>
+      </c>
+      <c r="J45" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46">
+        <v>36</v>
+      </c>
+      <c r="C46">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" t="s">
+        <v>154</v>
+      </c>
+      <c r="F46" t="s">
+        <v>201</v>
+      </c>
+      <c r="G46" t="s">
+        <v>236</v>
+      </c>
+      <c r="H46" t="s">
+        <v>260</v>
+      </c>
+      <c r="I46">
+        <v>2696</v>
+      </c>
+      <c r="J46" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47">
+        <v>36</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>137</v>
+      </c>
+      <c r="E47" t="s">
+        <v>155</v>
+      </c>
+      <c r="F47" t="s">
+        <v>202</v>
+      </c>
+      <c r="G47" t="s">
+        <v>236</v>
+      </c>
+      <c r="H47" t="s">
+        <v>263</v>
+      </c>
+      <c r="I47">
+        <v>5105</v>
+      </c>
+      <c r="J47" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48">
+        <v>36</v>
+      </c>
+      <c r="C48">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" t="s">
+        <v>155</v>
+      </c>
+      <c r="F48" t="s">
+        <v>202</v>
+      </c>
+      <c r="G48" t="s">
+        <v>236</v>
+      </c>
+      <c r="H48" t="s">
+        <v>311</v>
+      </c>
+      <c r="I48">
+        <v>5105</v>
+      </c>
+      <c r="J48" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49">
+        <v>36</v>
+      </c>
+      <c r="C49">
+        <v>16</v>
+      </c>
+      <c r="D49" t="s">
+        <v>137</v>
+      </c>
+      <c r="E49" t="s">
+        <v>155</v>
+      </c>
+      <c r="F49" t="s">
+        <v>202</v>
+      </c>
+      <c r="G49" t="s">
+        <v>238</v>
+      </c>
+      <c r="H49" t="s">
+        <v>251</v>
+      </c>
+      <c r="I49">
+        <v>3736</v>
+      </c>
+      <c r="J49" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50">
+        <v>40</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>134</v>
+      </c>
+      <c r="E50" t="s">
+        <v>156</v>
+      </c>
+      <c r="F50" t="s">
+        <v>203</v>
+      </c>
+      <c r="G50" t="s">
+        <v>236</v>
+      </c>
+      <c r="H50" t="s">
+        <v>175</v>
+      </c>
+      <c r="I50">
+        <v>2071</v>
+      </c>
+      <c r="J50" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51">
+        <v>40</v>
+      </c>
+      <c r="C51">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" t="s">
+        <v>157</v>
+      </c>
+      <c r="F51" t="s">
+        <v>204</v>
+      </c>
+      <c r="G51" t="s">
+        <v>236</v>
+      </c>
+      <c r="H51" t="s">
+        <v>264</v>
+      </c>
+      <c r="I51">
+        <v>2817</v>
+      </c>
+      <c r="J51" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52">
+        <v>40</v>
+      </c>
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" t="s">
+        <v>158</v>
+      </c>
+      <c r="F52" t="s">
+        <v>205</v>
+      </c>
+      <c r="G52" t="s">
+        <v>236</v>
+      </c>
+      <c r="H52" t="s">
+        <v>265</v>
+      </c>
+      <c r="I52">
+        <v>3634</v>
+      </c>
+      <c r="J52" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53">
+        <v>40</v>
+      </c>
+      <c r="C53">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>136</v>
+      </c>
+      <c r="E53" t="s">
+        <v>158</v>
+      </c>
+      <c r="F53" t="s">
+        <v>205</v>
+      </c>
+      <c r="G53" t="s">
+        <v>238</v>
+      </c>
+      <c r="H53" t="s">
+        <v>266</v>
+      </c>
+      <c r="I53">
+        <v>2679</v>
+      </c>
+      <c r="J53" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54">
+        <v>40</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>137</v>
+      </c>
+      <c r="E54" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" t="s">
+        <v>206</v>
+      </c>
+      <c r="G54" t="s">
+        <v>236</v>
+      </c>
+      <c r="H54" t="s">
+        <v>267</v>
+      </c>
+      <c r="I54">
+        <v>5370</v>
+      </c>
+      <c r="J54" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55">
+        <v>40</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+      <c r="D55" t="s">
+        <v>137</v>
+      </c>
+      <c r="E55" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" t="s">
+        <v>206</v>
+      </c>
+      <c r="G55" t="s">
+        <v>238</v>
+      </c>
+      <c r="H55" t="s">
+        <v>165</v>
+      </c>
+      <c r="I55">
+        <v>3932</v>
+      </c>
+      <c r="J55" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56">
+        <v>40</v>
+      </c>
+      <c r="C56">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>138</v>
+      </c>
+      <c r="E56" t="s">
+        <v>160</v>
+      </c>
+      <c r="F56" t="s">
+        <v>207</v>
+      </c>
+      <c r="G56" t="s">
+        <v>237</v>
+      </c>
+      <c r="H56" t="s">
+        <v>310</v>
+      </c>
+      <c r="I56">
+        <v>3425</v>
+      </c>
+      <c r="J56" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>40</v>
+      </c>
+      <c r="C57">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>138</v>
+      </c>
+      <c r="E57" t="s">
+        <v>160</v>
+      </c>
+      <c r="F57" t="s">
+        <v>207</v>
+      </c>
+      <c r="G57" t="s">
+        <v>236</v>
+      </c>
+      <c r="H57" t="s">
+        <v>268</v>
+      </c>
+      <c r="I57">
+        <v>6217</v>
+      </c>
+      <c r="J57" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58">
+        <v>40</v>
+      </c>
+      <c r="C58">
+        <v>16</v>
+      </c>
+      <c r="D58" t="s">
+        <v>138</v>
+      </c>
+      <c r="E58" t="s">
+        <v>160</v>
+      </c>
+      <c r="F58" t="s">
+        <v>207</v>
+      </c>
+      <c r="G58" t="s">
+        <v>240</v>
+      </c>
+      <c r="H58" t="s">
+        <v>312</v>
+      </c>
+      <c r="I58">
+        <v>4007</v>
+      </c>
+      <c r="J58" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59">
+        <v>40</v>
+      </c>
+      <c r="C59">
+        <v>16</v>
+      </c>
+      <c r="D59" t="s">
+        <v>138</v>
+      </c>
+      <c r="E59" t="s">
+        <v>160</v>
+      </c>
+      <c r="F59" t="s">
+        <v>207</v>
+      </c>
+      <c r="G59" t="s">
+        <v>237</v>
+      </c>
+      <c r="H59" t="s">
+        <v>309</v>
+      </c>
+      <c r="I59">
+        <v>3425</v>
+      </c>
+      <c r="J59" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60">
+        <v>45</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+      <c r="D60" t="s">
+        <v>137</v>
+      </c>
+      <c r="E60" t="s">
+        <v>161</v>
+      </c>
+      <c r="F60" t="s">
+        <v>208</v>
+      </c>
+      <c r="G60" t="s">
+        <v>237</v>
+      </c>
+      <c r="H60" t="s">
+        <v>270</v>
+      </c>
+      <c r="I60">
+        <v>3116</v>
+      </c>
+      <c r="J60" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61">
+        <v>45</v>
+      </c>
+      <c r="C61">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F61" t="s">
+        <v>208</v>
+      </c>
+      <c r="G61" t="s">
+        <v>236</v>
+      </c>
+      <c r="H61" t="s">
+        <v>271</v>
+      </c>
+      <c r="I61">
+        <v>5655</v>
+      </c>
+      <c r="J61" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62">
+        <v>45</v>
+      </c>
+      <c r="C62">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62" t="s">
+        <v>162</v>
+      </c>
+      <c r="F62" t="s">
+        <v>209</v>
+      </c>
+      <c r="G62" t="s">
+        <v>236</v>
+      </c>
+      <c r="H62" t="s">
+        <v>272</v>
+      </c>
+      <c r="I62">
+        <v>7627</v>
+      </c>
+      <c r="J62" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63">
+        <v>50</v>
+      </c>
+      <c r="C63">
+        <v>5</v>
+      </c>
+      <c r="D63" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" t="s">
+        <v>163</v>
+      </c>
+      <c r="F63" t="s">
+        <v>210</v>
+      </c>
+      <c r="G63" t="s">
+        <v>240</v>
+      </c>
+      <c r="H63" t="s">
+        <v>253</v>
+      </c>
+      <c r="I63">
+        <v>1447</v>
+      </c>
+      <c r="J63" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64">
+        <v>50</v>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>134</v>
+      </c>
+      <c r="E64" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64" t="s">
+        <v>210</v>
+      </c>
+      <c r="G64" t="s">
+        <v>241</v>
+      </c>
+      <c r="H64" t="s">
+        <v>273</v>
+      </c>
+      <c r="I64">
+        <v>2051</v>
+      </c>
+      <c r="J64" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65">
+        <v>50</v>
+      </c>
+      <c r="C65">
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>135</v>
+      </c>
+      <c r="E65" t="s">
+        <v>164</v>
+      </c>
+      <c r="F65" t="s">
+        <v>211</v>
+      </c>
+      <c r="G65" t="s">
+        <v>236</v>
+      </c>
+      <c r="H65" t="s">
+        <v>272</v>
+      </c>
+      <c r="I65">
+        <v>3093</v>
+      </c>
+      <c r="J65" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66">
+        <v>50</v>
+      </c>
+      <c r="C66">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>135</v>
+      </c>
+      <c r="E66" t="s">
+        <v>164</v>
+      </c>
+      <c r="F66" t="s">
+        <v>211</v>
+      </c>
+      <c r="G66" t="s">
+        <v>243</v>
+      </c>
+      <c r="H66" t="s">
+        <v>288</v>
+      </c>
+      <c r="I66">
+        <v>4131</v>
+      </c>
+      <c r="J66" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67">
+        <v>50</v>
+      </c>
+      <c r="C67">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>135</v>
+      </c>
+      <c r="E67" t="s">
+        <v>164</v>
+      </c>
+      <c r="F67" t="s">
+        <v>211</v>
+      </c>
+      <c r="G67" t="s">
+        <v>242</v>
+      </c>
+      <c r="H67" t="s">
+        <v>274</v>
+      </c>
+      <c r="I67">
+        <v>4384</v>
+      </c>
+      <c r="J67" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68">
+        <v>50</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>136</v>
+      </c>
+      <c r="E68" t="s">
+        <v>165</v>
+      </c>
+      <c r="F68" t="s">
+        <v>212</v>
+      </c>
+      <c r="G68" t="s">
+        <v>236</v>
+      </c>
+      <c r="H68" t="s">
+        <v>275</v>
+      </c>
+      <c r="I68">
+        <v>4004</v>
+      </c>
+      <c r="J68" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>50</v>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>136</v>
+      </c>
+      <c r="E69" t="s">
+        <v>165</v>
+      </c>
+      <c r="F69" t="s">
+        <v>212</v>
+      </c>
+      <c r="G69" t="s">
+        <v>242</v>
+      </c>
+      <c r="H69" t="s">
+        <v>276</v>
+      </c>
+      <c r="I69">
+        <v>5674</v>
+      </c>
+      <c r="J69" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70">
+        <v>50</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>137</v>
+      </c>
+      <c r="E70" t="s">
+        <v>166</v>
+      </c>
+      <c r="F70" t="s">
+        <v>213</v>
+      </c>
+      <c r="G70" t="s">
+        <v>236</v>
+      </c>
+      <c r="H70" t="s">
+        <v>277</v>
+      </c>
+      <c r="I70">
+        <v>5923</v>
+      </c>
+      <c r="J70" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71">
+        <v>50</v>
+      </c>
+      <c r="C71">
+        <v>10</v>
+      </c>
+      <c r="D71" t="s">
+        <v>137</v>
+      </c>
+      <c r="E71" t="s">
+        <v>166</v>
+      </c>
+      <c r="F71" t="s">
+        <v>213</v>
+      </c>
+      <c r="G71" t="s">
+        <v>242</v>
+      </c>
+      <c r="H71" t="s">
+        <v>278</v>
+      </c>
+      <c r="I71">
+        <v>8394</v>
+      </c>
+      <c r="J71" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72">
+        <v>50</v>
+      </c>
+      <c r="C72">
+        <v>10</v>
+      </c>
+      <c r="D72" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" t="s">
+        <v>166</v>
+      </c>
+      <c r="F72" t="s">
+        <v>213</v>
+      </c>
+      <c r="G72" t="s">
+        <v>238</v>
+      </c>
+      <c r="H72" t="s">
+        <v>260</v>
+      </c>
+      <c r="I72">
+        <v>4393</v>
+      </c>
+      <c r="J72" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73">
+        <v>50</v>
+      </c>
+      <c r="C73">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
+        <v>139</v>
+      </c>
+      <c r="E73" t="s">
+        <v>167</v>
+      </c>
+      <c r="F73" t="s">
+        <v>214</v>
+      </c>
+      <c r="G73" t="s">
+        <v>237</v>
+      </c>
+      <c r="H73" t="s">
+        <v>251</v>
+      </c>
+      <c r="I73">
+        <v>4420</v>
+      </c>
+      <c r="J73" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74">
+        <v>50</v>
+      </c>
+      <c r="C74">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>139</v>
+      </c>
+      <c r="E74" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" t="s">
+        <v>214</v>
+      </c>
+      <c r="G74" t="s">
+        <v>236</v>
+      </c>
+      <c r="H74" t="s">
+        <v>279</v>
+      </c>
+      <c r="I74">
+        <v>8022</v>
+      </c>
+      <c r="J74" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75">
+        <v>50</v>
+      </c>
+      <c r="C75">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>139</v>
+      </c>
+      <c r="E75" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" t="s">
+        <v>214</v>
+      </c>
+      <c r="G75" t="s">
+        <v>238</v>
+      </c>
+      <c r="H75" t="s">
+        <v>280</v>
+      </c>
+      <c r="I75">
+        <v>5875</v>
+      </c>
+      <c r="J75" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76">
+        <v>50</v>
+      </c>
+      <c r="C76">
+        <v>30</v>
+      </c>
+      <c r="D76" t="s">
+        <v>137</v>
+      </c>
+      <c r="E76" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G76" t="s">
+        <v>240</v>
+      </c>
+      <c r="H76" t="s">
+        <v>313</v>
+      </c>
+      <c r="I76">
+        <v>3834</v>
+      </c>
+      <c r="J76" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77">
+        <v>55</v>
+      </c>
+      <c r="C77">
+        <v>10</v>
+      </c>
+      <c r="D77" t="s">
+        <v>137</v>
+      </c>
+      <c r="E77" t="s">
+        <v>168</v>
+      </c>
+      <c r="F77" t="s">
+        <v>215</v>
+      </c>
+      <c r="G77" t="s">
+        <v>236</v>
+      </c>
+      <c r="H77" t="s">
+        <v>314</v>
+      </c>
+      <c r="I77">
+        <v>6071</v>
+      </c>
+      <c r="J77" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78">
+        <v>55</v>
+      </c>
+      <c r="C78">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
+        <v>137</v>
+      </c>
+      <c r="E78" t="s">
+        <v>168</v>
+      </c>
+      <c r="F78" t="s">
+        <v>215</v>
+      </c>
+      <c r="G78" t="s">
+        <v>238</v>
+      </c>
+      <c r="H78" t="s">
+        <v>175</v>
+      </c>
+      <c r="I78">
+        <v>4562</v>
+      </c>
+      <c r="J78" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79">
+        <v>55</v>
+      </c>
+      <c r="C79">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>139</v>
+      </c>
+      <c r="E79" t="s">
+        <v>169</v>
+      </c>
+      <c r="F79" t="s">
+        <v>216</v>
+      </c>
+      <c r="G79" t="s">
+        <v>236</v>
+      </c>
+      <c r="H79" t="s">
+        <v>282</v>
+      </c>
+      <c r="I79">
+        <v>8392</v>
+      </c>
+      <c r="J79" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>132</v>
+      </c>
+      <c r="B80">
+        <v>60</v>
+      </c>
+      <c r="C80">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>139</v>
+      </c>
+      <c r="E80" t="s">
+        <v>188</v>
+      </c>
+      <c r="F80" t="s">
+        <v>235</v>
+      </c>
+      <c r="G80" t="s">
+        <v>236</v>
+      </c>
+      <c r="H80" t="s">
+        <v>315</v>
+      </c>
+      <c r="I80">
+        <v>8742</v>
+      </c>
+      <c r="J80" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81">
+        <v>63</v>
+      </c>
+      <c r="C81">
+        <v>8</v>
+      </c>
+      <c r="D81" t="s">
+        <v>136</v>
+      </c>
+      <c r="E81" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" t="s">
+        <v>218</v>
+      </c>
+      <c r="G81" t="s">
+        <v>240</v>
+      </c>
+      <c r="H81" t="s">
+        <v>284</v>
+      </c>
+      <c r="I81">
+        <v>2826</v>
+      </c>
+      <c r="J81" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82">
+        <v>63</v>
+      </c>
+      <c r="C82">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
+        <v>136</v>
+      </c>
+      <c r="E82" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82" t="s">
+        <v>218</v>
+      </c>
+      <c r="G82" t="s">
+        <v>241</v>
+      </c>
+      <c r="H82" t="s">
+        <v>285</v>
+      </c>
+      <c r="I82">
+        <v>4004</v>
+      </c>
+      <c r="J82" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83">
+        <v>63</v>
+      </c>
+      <c r="C83">
+        <v>10</v>
+      </c>
+      <c r="D83" t="s">
+        <v>137</v>
+      </c>
+      <c r="E83" t="s">
+        <v>172</v>
+      </c>
+      <c r="F83" t="s">
+        <v>219</v>
+      </c>
+      <c r="G83" t="s">
+        <v>236</v>
+      </c>
+      <c r="H83" t="s">
+        <v>286</v>
+      </c>
+      <c r="I83">
+        <v>6533</v>
+      </c>
+      <c r="J83" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84">
+        <v>63</v>
+      </c>
+      <c r="C84">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s">
+        <v>137</v>
+      </c>
+      <c r="E84" t="s">
+        <v>172</v>
+      </c>
+      <c r="F84" t="s">
+        <v>219</v>
+      </c>
+      <c r="G84" t="s">
+        <v>242</v>
+      </c>
+      <c r="H84" t="s">
+        <v>287</v>
+      </c>
+      <c r="I84">
+        <v>9528</v>
+      </c>
+      <c r="J84" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85">
+        <v>63</v>
+      </c>
+      <c r="C85">
+        <v>12</v>
+      </c>
+      <c r="D85" t="s">
+        <v>139</v>
+      </c>
+      <c r="E85" t="s">
+        <v>173</v>
+      </c>
+      <c r="F85" t="s">
+        <v>220</v>
+      </c>
+      <c r="G85" t="s">
+        <v>236</v>
+      </c>
+      <c r="H85" t="s">
+        <v>288</v>
+      </c>
+      <c r="I85">
+        <v>8943</v>
+      </c>
+      <c r="J85" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86">
+        <v>63</v>
+      </c>
+      <c r="C86">
+        <v>16</v>
+      </c>
+      <c r="D86" t="s">
+        <v>141</v>
+      </c>
+      <c r="E86" t="s">
+        <v>174</v>
+      </c>
+      <c r="F86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G86" t="s">
+        <v>236</v>
+      </c>
+      <c r="H86" t="s">
+        <v>289</v>
+      </c>
+      <c r="I86">
+        <v>14862</v>
+      </c>
+      <c r="J86" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87">
+        <v>63</v>
+      </c>
+      <c r="C87">
+        <v>20</v>
+      </c>
+      <c r="D87" t="s">
+        <v>141</v>
+      </c>
+      <c r="E87" t="s">
+        <v>174</v>
+      </c>
+      <c r="F87" t="s">
+        <v>221</v>
+      </c>
+      <c r="G87" t="s">
+        <v>236</v>
+      </c>
+      <c r="H87" t="s">
+        <v>289</v>
+      </c>
+      <c r="I87">
+        <v>14862</v>
+      </c>
+      <c r="J87" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88">
+        <v>70</v>
+      </c>
+      <c r="C88">
+        <v>10</v>
+      </c>
+      <c r="D88" t="s">
+        <v>137</v>
+      </c>
+      <c r="E88" t="s">
+        <v>176</v>
+      </c>
+      <c r="F88" t="s">
+        <v>223</v>
+      </c>
+      <c r="G88" t="s">
+        <v>236</v>
+      </c>
+      <c r="H88" t="s">
+        <v>291</v>
+      </c>
+      <c r="I88">
+        <v>6843</v>
+      </c>
+      <c r="J88" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89">
+        <v>70</v>
+      </c>
+      <c r="C89">
+        <v>10</v>
+      </c>
+      <c r="D89" t="s">
+        <v>137</v>
+      </c>
+      <c r="E89" t="s">
+        <v>176</v>
+      </c>
+      <c r="F89" t="s">
+        <v>223</v>
+      </c>
+      <c r="G89" t="s">
+        <v>242</v>
+      </c>
+      <c r="H89" t="s">
+        <v>292</v>
+      </c>
+      <c r="I89">
+        <v>9698</v>
+      </c>
+      <c r="J89" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90">
+        <v>70</v>
+      </c>
+      <c r="C90">
+        <v>12</v>
+      </c>
+      <c r="D90" t="s">
+        <v>139</v>
+      </c>
+      <c r="E90" t="s">
+        <v>177</v>
+      </c>
+      <c r="F90" t="s">
+        <v>224</v>
+      </c>
+      <c r="G90" t="s">
+        <v>236</v>
+      </c>
+      <c r="H90" t="s">
+        <v>293</v>
+      </c>
+      <c r="I90">
+        <v>9382</v>
+      </c>
+      <c r="J90" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+      <c r="B91">
+        <v>70</v>
+      </c>
+      <c r="C91">
+        <v>12</v>
+      </c>
+      <c r="D91" t="s">
+        <v>139</v>
+      </c>
+      <c r="E91" t="s">
+        <v>177</v>
+      </c>
+      <c r="F91" t="s">
+        <v>224</v>
+      </c>
+      <c r="G91" t="s">
+        <v>242</v>
+      </c>
+      <c r="H91" t="s">
+        <v>292</v>
+      </c>
+      <c r="I91">
+        <v>13296</v>
+      </c>
+      <c r="J91" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92">
+        <v>80</v>
+      </c>
+      <c r="C92">
+        <v>10</v>
+      </c>
+      <c r="D92" t="s">
+        <v>137</v>
+      </c>
+      <c r="E92" t="s">
+        <v>178</v>
+      </c>
+      <c r="F92" t="s">
+        <v>225</v>
+      </c>
+      <c r="G92" t="s">
+        <v>236</v>
+      </c>
+      <c r="H92" t="s">
+        <v>294</v>
+      </c>
+      <c r="I92">
+        <v>7202</v>
+      </c>
+      <c r="J92" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93">
+        <v>80</v>
+      </c>
+      <c r="C93">
+        <v>10</v>
+      </c>
+      <c r="D93" t="s">
+        <v>137</v>
+      </c>
+      <c r="E93" t="s">
+        <v>178</v>
+      </c>
+      <c r="F93" t="s">
+        <v>225</v>
+      </c>
+      <c r="G93" t="s">
+        <v>242</v>
+      </c>
+      <c r="H93" t="s">
+        <v>295</v>
+      </c>
+      <c r="I93">
+        <v>10207</v>
+      </c>
+      <c r="J93" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94">
+        <v>80</v>
+      </c>
+      <c r="C94">
+        <v>12</v>
+      </c>
+      <c r="D94" t="s">
+        <v>139</v>
+      </c>
+      <c r="E94" t="s">
+        <v>179</v>
+      </c>
+      <c r="F94" t="s">
+        <v>226</v>
+      </c>
+      <c r="G94" t="s">
+        <v>236</v>
+      </c>
+      <c r="H94" t="s">
+        <v>296</v>
+      </c>
+      <c r="I94">
+        <v>9797</v>
+      </c>
+      <c r="J94" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95">
+        <v>80</v>
+      </c>
+      <c r="C95">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>139</v>
+      </c>
+      <c r="E95" t="s">
+        <v>179</v>
+      </c>
+      <c r="F95" t="s">
+        <v>226</v>
+      </c>
+      <c r="G95" t="s">
+        <v>242</v>
+      </c>
+      <c r="H95" t="s">
+        <v>297</v>
+      </c>
+      <c r="I95">
+        <v>13844</v>
+      </c>
+      <c r="J95" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96">
+        <v>80</v>
+      </c>
+      <c r="C96">
+        <v>16</v>
+      </c>
+      <c r="D96" t="s">
+        <v>141</v>
+      </c>
+      <c r="E96" t="s">
+        <v>180</v>
+      </c>
+      <c r="F96" t="s">
+        <v>227</v>
+      </c>
+      <c r="G96" t="s">
+        <v>236</v>
+      </c>
+      <c r="H96" t="s">
+        <v>298</v>
+      </c>
+      <c r="I96">
+        <v>16485</v>
+      </c>
+      <c r="J96" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97">
+        <v>80</v>
+      </c>
+      <c r="C97">
+        <v>16</v>
+      </c>
+      <c r="D97" t="s">
+        <v>141</v>
+      </c>
+      <c r="E97" t="s">
+        <v>180</v>
+      </c>
+      <c r="F97" t="s">
+        <v>227</v>
+      </c>
+      <c r="G97" t="s">
+        <v>242</v>
+      </c>
+      <c r="H97" t="s">
+        <v>299</v>
+      </c>
+      <c r="I97">
+        <v>23363</v>
+      </c>
+      <c r="J97" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98">
+        <v>80</v>
+      </c>
+      <c r="C98">
+        <v>20</v>
+      </c>
+      <c r="D98" t="s">
+        <v>141</v>
+      </c>
+      <c r="E98" t="s">
+        <v>180</v>
+      </c>
+      <c r="F98" t="s">
+        <v>227</v>
+      </c>
+      <c r="G98" t="s">
+        <v>236</v>
+      </c>
+      <c r="H98" t="s">
+        <v>298</v>
+      </c>
+      <c r="I98">
+        <v>16485</v>
+      </c>
+      <c r="J98" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99">
+        <v>80</v>
+      </c>
+      <c r="C99">
+        <v>20</v>
+      </c>
+      <c r="D99" t="s">
+        <v>141</v>
+      </c>
+      <c r="E99" t="s">
+        <v>180</v>
+      </c>
+      <c r="F99" t="s">
+        <v>227</v>
+      </c>
+      <c r="G99" t="s">
+        <v>242</v>
+      </c>
+      <c r="H99" t="s">
+        <v>299</v>
+      </c>
+      <c r="I99">
+        <v>23363</v>
+      </c>
+      <c r="J99" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100">
+        <v>100</v>
+      </c>
+      <c r="C100">
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
+        <v>139</v>
+      </c>
+      <c r="E100" t="s">
+        <v>181</v>
+      </c>
+      <c r="F100" t="s">
+        <v>228</v>
+      </c>
+      <c r="G100" t="s">
+        <v>236</v>
+      </c>
+      <c r="H100" t="s">
+        <v>300</v>
+      </c>
+      <c r="I100">
+        <v>10761</v>
+      </c>
+      <c r="J100" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101">
+        <v>100</v>
+      </c>
+      <c r="C101">
+        <v>12</v>
+      </c>
+      <c r="D101" t="s">
+        <v>139</v>
+      </c>
+      <c r="E101" t="s">
+        <v>181</v>
+      </c>
+      <c r="F101" t="s">
+        <v>228</v>
+      </c>
+      <c r="G101" t="s">
+        <v>242</v>
+      </c>
+      <c r="H101" t="s">
+        <v>301</v>
+      </c>
+      <c r="I101">
+        <v>15251</v>
+      </c>
+      <c r="J101" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102">
+        <v>100</v>
+      </c>
+      <c r="C102">
+        <v>16</v>
+      </c>
+      <c r="D102" t="s">
+        <v>141</v>
+      </c>
+      <c r="E102" t="s">
+        <v>182</v>
+      </c>
+      <c r="F102" t="s">
+        <v>229</v>
+      </c>
+      <c r="G102" t="s">
+        <v>236</v>
+      </c>
+      <c r="H102" t="s">
+        <v>302</v>
+      </c>
+      <c r="I102">
+        <v>18123</v>
+      </c>
+      <c r="J102" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103">
+        <v>100</v>
+      </c>
+      <c r="C103">
+        <v>16</v>
+      </c>
+      <c r="D103" t="s">
+        <v>141</v>
+      </c>
+      <c r="E103" t="s">
+        <v>182</v>
+      </c>
+      <c r="F103" t="s">
+        <v>229</v>
+      </c>
+      <c r="G103" t="s">
+        <v>242</v>
+      </c>
+      <c r="H103" t="s">
+        <v>303</v>
+      </c>
+      <c r="I103">
+        <v>25684</v>
+      </c>
+      <c r="J103" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104">
+        <v>100</v>
+      </c>
+      <c r="C104">
+        <v>20</v>
+      </c>
+      <c r="D104" t="s">
+        <v>141</v>
+      </c>
+      <c r="E104" t="s">
+        <v>182</v>
+      </c>
+      <c r="F104" t="s">
+        <v>229</v>
+      </c>
+      <c r="G104" t="s">
+        <v>236</v>
+      </c>
+      <c r="H104" t="s">
+        <v>302</v>
+      </c>
+      <c r="I104">
+        <v>18123</v>
+      </c>
+      <c r="J104" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105">
+        <v>100</v>
+      </c>
+      <c r="C105">
+        <v>20</v>
+      </c>
+      <c r="D105" t="s">
+        <v>141</v>
+      </c>
+      <c r="E105" t="s">
+        <v>182</v>
+      </c>
+      <c r="F105" t="s">
+        <v>229</v>
+      </c>
+      <c r="G105" t="s">
+        <v>242</v>
+      </c>
+      <c r="H105" t="s">
+        <v>303</v>
+      </c>
+      <c r="I105">
+        <v>25684</v>
+      </c>
+      <c r="J105" t="s">
+        <v>423</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J84"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>424</v>
       </c>
@@ -8822,7 +8897,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>425</v>
       </c>
@@ -8854,7 +8929,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>426</v>
       </c>
@@ -8886,7 +8961,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>427</v>
       </c>
@@ -8918,7 +8993,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>428</v>
       </c>
@@ -8950,7 +9025,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>429</v>
       </c>
@@ -8982,7 +9057,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>430</v>
       </c>
@@ -9014,7 +9089,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>431</v>
       </c>
@@ -9046,7 +9121,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>432</v>
       </c>
@@ -9078,7 +9153,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>433</v>
       </c>
@@ -9110,7 +9185,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>434</v>
       </c>
@@ -9142,7 +9217,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>435</v>
       </c>
@@ -9174,7 +9249,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>436</v>
       </c>
@@ -9206,7 +9281,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>437</v>
       </c>
@@ -9238,7 +9313,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>438</v>
       </c>
@@ -9270,7 +9345,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>439</v>
       </c>
@@ -9302,7 +9377,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>440</v>
       </c>
@@ -9334,7 +9409,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>441</v>
       </c>
@@ -9366,7 +9441,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>442</v>
       </c>
@@ -9398,7 +9473,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>443</v>
       </c>
@@ -9430,7 +9505,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>444</v>
       </c>
@@ -9462,7 +9537,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>445</v>
       </c>
@@ -9494,7 +9569,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>446</v>
       </c>
@@ -9526,7 +9601,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>447</v>
       </c>
@@ -9558,7 +9633,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>448</v>
       </c>
@@ -9590,7 +9665,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>449</v>
       </c>
@@ -9622,7 +9697,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>450</v>
       </c>
@@ -9654,7 +9729,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>451</v>
       </c>
@@ -9686,7 +9761,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>452</v>
       </c>
@@ -9718,7 +9793,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>453</v>
       </c>
@@ -9750,7 +9825,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>454</v>
       </c>
@@ -9782,7 +9857,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>455</v>
       </c>
@@ -9814,7 +9889,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>456</v>
       </c>
@@ -9846,7 +9921,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>457</v>
       </c>
@@ -9878,7 +9953,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>458</v>
       </c>
@@ -9910,7 +9985,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>459</v>
       </c>
@@ -9942,7 +10017,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>460</v>
       </c>
@@ -9974,7 +10049,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>461</v>
       </c>
@@ -10006,7 +10081,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>462</v>
       </c>
@@ -10038,7 +10113,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>463</v>
       </c>
@@ -10070,7 +10145,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>464</v>
       </c>
@@ -10102,7 +10177,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>465</v>
       </c>
@@ -10134,7 +10209,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>466</v>
       </c>
@@ -10166,7 +10241,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>467</v>
       </c>
@@ -10198,7 +10273,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>468</v>
       </c>
@@ -10230,7 +10305,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>469</v>
       </c>
@@ -10262,7 +10337,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>470</v>
       </c>
@@ -10294,7 +10369,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>471</v>
       </c>
@@ -10326,7 +10401,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>472</v>
       </c>
@@ -10358,7 +10433,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>473</v>
       </c>
@@ -10390,7 +10465,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>474</v>
       </c>
@@ -10422,7 +10497,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>475</v>
       </c>
@@ -10454,7 +10529,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>476</v>
       </c>
@@ -10486,7 +10561,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>477</v>
       </c>
@@ -10518,7 +10593,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>478</v>
       </c>
@@ -10550,7 +10625,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>479</v>
       </c>
@@ -10582,7 +10657,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>480</v>
       </c>
@@ -10614,7 +10689,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>481</v>
       </c>
@@ -10646,7 +10721,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>482</v>
       </c>
@@ -10678,7 +10753,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>483</v>
       </c>
@@ -10710,7 +10785,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>484</v>
       </c>
@@ -10742,7 +10817,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>485</v>
       </c>
@@ -10774,7 +10849,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>486</v>
       </c>
@@ -10806,7 +10881,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>487</v>
       </c>
@@ -10838,7 +10913,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>488</v>
       </c>
@@ -10870,7 +10945,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>489</v>
       </c>
@@ -10902,7 +10977,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>490</v>
       </c>
@@ -10934,7 +11009,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>491</v>
       </c>
@@ -10966,7 +11041,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>492</v>
       </c>
@@ -10998,7 +11073,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>493</v>
       </c>
@@ -11030,7 +11105,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>494</v>
       </c>
@@ -11062,7 +11137,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>495</v>
       </c>
@@ -11094,7 +11169,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>496</v>
       </c>
@@ -11126,7 +11201,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>497</v>
       </c>
@@ -11158,7 +11233,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>498</v>
       </c>
@@ -11190,7 +11265,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>499</v>
       </c>
@@ -11222,7 +11297,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>500</v>
       </c>
@@ -11254,7 +11329,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>501</v>
       </c>
@@ -11286,7 +11361,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>502</v>
       </c>
@@ -11318,7 +11393,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>503</v>
       </c>
@@ -11350,7 +11425,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>504</v>
       </c>
@@ -11382,7 +11457,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>505</v>
       </c>
@@ -11414,7 +11489,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>506</v>
       </c>
@@ -11447,16 +11522,17 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11488,7 +11564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>631</v>
       </c>
@@ -11520,7 +11596,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>429</v>
       </c>
@@ -11552,7 +11628,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>430</v>
       </c>
@@ -11584,7 +11660,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>437</v>
       </c>
@@ -11616,7 +11692,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>438</v>
       </c>
@@ -11648,7 +11724,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>439</v>
       </c>
@@ -11680,7 +11756,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>440</v>
       </c>
@@ -11712,7 +11788,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>447</v>
       </c>
@@ -11744,7 +11820,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>448</v>
       </c>
@@ -11776,7 +11852,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>451</v>
       </c>
@@ -11808,7 +11884,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>452</v>
       </c>
@@ -11840,7 +11916,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>455</v>
       </c>
@@ -11872,7 +11948,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>456</v>
       </c>
@@ -11904,7 +11980,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>457</v>
       </c>
@@ -11936,7 +12012,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>458</v>
       </c>
@@ -11968,7 +12044,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>459</v>
       </c>
@@ -12000,7 +12076,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>460</v>
       </c>
@@ -12032,7 +12108,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>461</v>
       </c>
@@ -12064,7 +12140,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>462</v>
       </c>
@@ -12096,7 +12172,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>463</v>
       </c>
@@ -12128,7 +12204,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>464</v>
       </c>
@@ -12160,7 +12236,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>465</v>
       </c>
@@ -12192,7 +12268,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>466</v>
       </c>
@@ -12224,7 +12300,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>468</v>
       </c>
@@ -12256,7 +12332,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>469</v>
       </c>
@@ -12288,7 +12364,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>470</v>
       </c>
@@ -12320,7 +12396,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>471</v>
       </c>
@@ -12352,7 +12428,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>472</v>
       </c>
@@ -12384,7 +12460,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>473</v>
       </c>
@@ -12416,7 +12492,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>474</v>
       </c>
@@ -12448,7 +12524,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>475</v>
       </c>
@@ -12480,7 +12556,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>476</v>
       </c>
@@ -12512,7 +12588,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>477</v>
       </c>
@@ -12544,7 +12620,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>478</v>
       </c>
@@ -12576,7 +12652,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>479</v>
       </c>
@@ -12608,7 +12684,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>480</v>
       </c>
@@ -12640,7 +12716,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>481</v>
       </c>
@@ -12672,7 +12748,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>482</v>
       </c>
@@ -12704,7 +12780,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>483</v>
       </c>
@@ -12736,7 +12812,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>484</v>
       </c>
@@ -12768,7 +12844,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>486</v>
       </c>
@@ -12800,7 +12876,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>487</v>
       </c>
@@ -12832,7 +12908,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>488</v>
       </c>
@@ -12864,7 +12940,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>489</v>
       </c>
@@ -12896,7 +12972,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>490</v>
       </c>
@@ -12928,7 +13004,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>491</v>
       </c>
@@ -12960,7 +13036,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>492</v>
       </c>
@@ -12992,7 +13068,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>493</v>
       </c>
@@ -13024,7 +13100,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>494</v>
       </c>
@@ -13056,7 +13132,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>495</v>
       </c>
@@ -13088,7 +13164,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>496</v>
       </c>
@@ -13120,7 +13196,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>497</v>
       </c>
@@ -13152,7 +13228,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>498</v>
       </c>
@@ -13184,7 +13260,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>499</v>
       </c>
@@ -13216,7 +13292,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>500</v>
       </c>
@@ -13248,7 +13324,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>501</v>
       </c>
@@ -13280,7 +13356,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>502</v>
       </c>
@@ -13312,7 +13388,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>503</v>
       </c>
@@ -13344,7 +13420,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>504</v>
       </c>
@@ -13376,7 +13452,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>505</v>
       </c>
@@ -13408,7 +13484,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>506</v>
       </c>
@@ -13441,6 +13517,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/HIWIN_Specs.xlsx
+++ b/data/HIWIN_Specs.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tonylung/Desktop/FEED-SYSTEM-GAI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639A5B72-966A-C84F-8FDA-DB8E920BEA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E257C3C7-2F44-0E4E-B70D-B0999CA5F59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16660" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FSV" sheetId="1" r:id="rId1"/>
     <sheet name="FSW" sheetId="2" r:id="rId2"/>
     <sheet name="FSI" sheetId="3" r:id="rId3"/>
     <sheet name="RSI" sheetId="4" r:id="rId4"/>
-    <sheet name="ALL" sheetId="5" r:id="rId5"/>
-    <sheet name="FDC" sheetId="6" r:id="rId6"/>
+    <sheet name="FDC" sheetId="6" r:id="rId5"/>
+    <sheet name="ALL" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -13894,6 +13894,3921 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J122"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H2" t="s">
+        <v>380</v>
+      </c>
+      <c r="I2">
+        <v>920</v>
+      </c>
+      <c r="J2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F3" t="s">
+        <v>379</v>
+      </c>
+      <c r="G3" t="s">
+        <v>379</v>
+      </c>
+      <c r="H3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I3">
+        <v>930</v>
+      </c>
+      <c r="J3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E4" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" t="s">
+        <v>379</v>
+      </c>
+      <c r="G4" t="s">
+        <v>388</v>
+      </c>
+      <c r="H4" t="s">
+        <v>389</v>
+      </c>
+      <c r="I4">
+        <v>610</v>
+      </c>
+      <c r="J4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>391</v>
+      </c>
+      <c r="E5" t="s">
+        <v>392</v>
+      </c>
+      <c r="F5" t="s">
+        <v>378</v>
+      </c>
+      <c r="G5" t="s">
+        <v>379</v>
+      </c>
+      <c r="H5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I5">
+        <v>960</v>
+      </c>
+      <c r="J5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+      <c r="E6" t="s">
+        <v>392</v>
+      </c>
+      <c r="F6" t="s">
+        <v>378</v>
+      </c>
+      <c r="G6" t="s">
+        <v>388</v>
+      </c>
+      <c r="H6" t="s">
+        <v>391</v>
+      </c>
+      <c r="I6">
+        <v>630</v>
+      </c>
+      <c r="J6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E7" t="s">
+        <v>399</v>
+      </c>
+      <c r="F7" t="s">
+        <v>378</v>
+      </c>
+      <c r="G7" t="s">
+        <v>388</v>
+      </c>
+      <c r="H7" t="s">
+        <v>400</v>
+      </c>
+      <c r="I7">
+        <v>680</v>
+      </c>
+      <c r="J7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" t="s">
+        <v>403</v>
+      </c>
+      <c r="F8" t="s">
+        <v>379</v>
+      </c>
+      <c r="G8" t="s">
+        <v>404</v>
+      </c>
+      <c r="H8" t="s">
+        <v>405</v>
+      </c>
+      <c r="I8">
+        <v>1390</v>
+      </c>
+      <c r="J8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>408</v>
+      </c>
+      <c r="E9" t="s">
+        <v>409</v>
+      </c>
+      <c r="F9" t="s">
+        <v>378</v>
+      </c>
+      <c r="G9" t="s">
+        <v>404</v>
+      </c>
+      <c r="H9" t="s">
+        <v>410</v>
+      </c>
+      <c r="I9">
+        <v>1490</v>
+      </c>
+      <c r="J9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>408</v>
+      </c>
+      <c r="E10" t="s">
+        <v>409</v>
+      </c>
+      <c r="F10" t="s">
+        <v>378</v>
+      </c>
+      <c r="G10" t="s">
+        <v>379</v>
+      </c>
+      <c r="H10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I10">
+        <v>1130</v>
+      </c>
+      <c r="J10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>415</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>408</v>
+      </c>
+      <c r="E11" t="s">
+        <v>409</v>
+      </c>
+      <c r="F11" t="s">
+        <v>378</v>
+      </c>
+      <c r="G11" t="s">
+        <v>388</v>
+      </c>
+      <c r="H11" t="s">
+        <v>416</v>
+      </c>
+      <c r="I11">
+        <v>760</v>
+      </c>
+      <c r="J11" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>418</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" t="s">
+        <v>420</v>
+      </c>
+      <c r="F12" t="s">
+        <v>421</v>
+      </c>
+      <c r="G12" t="s">
+        <v>422</v>
+      </c>
+      <c r="H12" t="s">
+        <v>423</v>
+      </c>
+      <c r="I12">
+        <v>2420</v>
+      </c>
+      <c r="J12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E13" t="s">
+        <v>426</v>
+      </c>
+      <c r="F13" t="s">
+        <v>427</v>
+      </c>
+      <c r="G13" t="s">
+        <v>422</v>
+      </c>
+      <c r="H13" t="s">
+        <v>423</v>
+      </c>
+      <c r="I13">
+        <v>2960</v>
+      </c>
+      <c r="J13" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B14">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>408</v>
+      </c>
+      <c r="E14" t="s">
+        <v>426</v>
+      </c>
+      <c r="F14" t="s">
+        <v>378</v>
+      </c>
+      <c r="G14" t="s">
+        <v>404</v>
+      </c>
+      <c r="H14" t="s">
+        <v>430</v>
+      </c>
+      <c r="I14">
+        <v>1650</v>
+      </c>
+      <c r="J14" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>432</v>
+      </c>
+      <c r="B15">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>408</v>
+      </c>
+      <c r="E15" t="s">
+        <v>426</v>
+      </c>
+      <c r="F15" t="s">
+        <v>378</v>
+      </c>
+      <c r="G15" t="s">
+        <v>379</v>
+      </c>
+      <c r="H15" t="s">
+        <v>433</v>
+      </c>
+      <c r="I15">
+        <v>1260</v>
+      </c>
+      <c r="J15" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B16">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>408</v>
+      </c>
+      <c r="E16" t="s">
+        <v>436</v>
+      </c>
+      <c r="F16" t="s">
+        <v>378</v>
+      </c>
+      <c r="G16" t="s">
+        <v>422</v>
+      </c>
+      <c r="H16" t="s">
+        <v>437</v>
+      </c>
+      <c r="I16">
+        <v>1980</v>
+      </c>
+      <c r="J16" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>439</v>
+      </c>
+      <c r="B17">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>408</v>
+      </c>
+      <c r="E17" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" t="s">
+        <v>378</v>
+      </c>
+      <c r="G17" t="s">
+        <v>379</v>
+      </c>
+      <c r="H17" t="s">
+        <v>440</v>
+      </c>
+      <c r="I17">
+        <v>1260</v>
+      </c>
+      <c r="J17" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>442</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>408</v>
+      </c>
+      <c r="E18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F18" t="s">
+        <v>378</v>
+      </c>
+      <c r="G18" t="s">
+        <v>388</v>
+      </c>
+      <c r="H18" t="s">
+        <v>443</v>
+      </c>
+      <c r="I18">
+        <v>840</v>
+      </c>
+      <c r="J18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>445</v>
+      </c>
+      <c r="B19">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>446</v>
+      </c>
+      <c r="E19" t="s">
+        <v>447</v>
+      </c>
+      <c r="F19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G19" t="s">
+        <v>422</v>
+      </c>
+      <c r="H19" t="s">
+        <v>448</v>
+      </c>
+      <c r="I19">
+        <v>2720</v>
+      </c>
+      <c r="J19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>450</v>
+      </c>
+      <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>446</v>
+      </c>
+      <c r="E20" t="s">
+        <v>447</v>
+      </c>
+      <c r="F20" t="s">
+        <v>421</v>
+      </c>
+      <c r="G20" t="s">
+        <v>422</v>
+      </c>
+      <c r="H20" t="s">
+        <v>451</v>
+      </c>
+      <c r="I20">
+        <v>2710</v>
+      </c>
+      <c r="J20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>453</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>446</v>
+      </c>
+      <c r="E21" t="s">
+        <v>447</v>
+      </c>
+      <c r="F21" t="s">
+        <v>421</v>
+      </c>
+      <c r="G21" t="s">
+        <v>404</v>
+      </c>
+      <c r="H21" t="s">
+        <v>454</v>
+      </c>
+      <c r="I21">
+        <v>2210</v>
+      </c>
+      <c r="J21" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>455</v>
+      </c>
+      <c r="B22">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>446</v>
+      </c>
+      <c r="E22" t="s">
+        <v>447</v>
+      </c>
+      <c r="F22" t="s">
+        <v>421</v>
+      </c>
+      <c r="G22" t="s">
+        <v>404</v>
+      </c>
+      <c r="H22" t="s">
+        <v>454</v>
+      </c>
+      <c r="I22">
+        <v>2200</v>
+      </c>
+      <c r="J22" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>457</v>
+      </c>
+      <c r="B23">
+        <v>25</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>446</v>
+      </c>
+      <c r="E23" t="s">
+        <v>447</v>
+      </c>
+      <c r="F23" t="s">
+        <v>421</v>
+      </c>
+      <c r="G23" t="s">
+        <v>379</v>
+      </c>
+      <c r="H23" t="s">
+        <v>410</v>
+      </c>
+      <c r="I23">
+        <v>1670</v>
+      </c>
+      <c r="J23" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>439</v>
+      </c>
+      <c r="B24">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>446</v>
+      </c>
+      <c r="E24" t="s">
+        <v>447</v>
+      </c>
+      <c r="F24" t="s">
+        <v>421</v>
+      </c>
+      <c r="G24" t="s">
+        <v>379</v>
+      </c>
+      <c r="H24" t="s">
+        <v>410</v>
+      </c>
+      <c r="I24">
+        <v>1710</v>
+      </c>
+      <c r="J24" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>450</v>
+      </c>
+      <c r="B25">
+        <v>25</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>460</v>
+      </c>
+      <c r="E25" t="s">
+        <v>461</v>
+      </c>
+      <c r="F25" t="s">
+        <v>427</v>
+      </c>
+      <c r="G25" t="s">
+        <v>422</v>
+      </c>
+      <c r="H25" t="s">
+        <v>462</v>
+      </c>
+      <c r="I25">
+        <v>3480</v>
+      </c>
+      <c r="J25" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>464</v>
+      </c>
+      <c r="B26">
+        <v>28</v>
+      </c>
+      <c r="C26">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>465</v>
+      </c>
+      <c r="E26" t="s">
+        <v>466</v>
+      </c>
+      <c r="F26" t="s">
+        <v>421</v>
+      </c>
+      <c r="G26" t="s">
+        <v>422</v>
+      </c>
+      <c r="H26" t="s">
+        <v>467</v>
+      </c>
+      <c r="I26">
+        <v>2840</v>
+      </c>
+      <c r="J26" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>469</v>
+      </c>
+      <c r="B27">
+        <v>28</v>
+      </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E27" t="s">
+        <v>470</v>
+      </c>
+      <c r="F27" t="s">
+        <v>427</v>
+      </c>
+      <c r="G27" t="s">
+        <v>422</v>
+      </c>
+      <c r="H27" t="s">
+        <v>471</v>
+      </c>
+      <c r="I27">
+        <v>3690</v>
+      </c>
+      <c r="J27" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>473</v>
+      </c>
+      <c r="B28">
+        <v>28</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>408</v>
+      </c>
+      <c r="E28" t="s">
+        <v>470</v>
+      </c>
+      <c r="F28" t="s">
+        <v>427</v>
+      </c>
+      <c r="G28" t="s">
+        <v>422</v>
+      </c>
+      <c r="H28" t="s">
+        <v>474</v>
+      </c>
+      <c r="I28">
+        <v>3680</v>
+      </c>
+      <c r="J28" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>476</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>408</v>
+      </c>
+      <c r="E29" t="s">
+        <v>470</v>
+      </c>
+      <c r="F29" t="s">
+        <v>427</v>
+      </c>
+      <c r="G29" t="s">
+        <v>404</v>
+      </c>
+      <c r="H29" t="s">
+        <v>477</v>
+      </c>
+      <c r="I29">
+        <v>2970</v>
+      </c>
+      <c r="J29" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>479</v>
+      </c>
+      <c r="B30">
+        <v>32</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>480</v>
+      </c>
+      <c r="E30" t="s">
+        <v>481</v>
+      </c>
+      <c r="F30" t="s">
+        <v>378</v>
+      </c>
+      <c r="G30" t="s">
+        <v>404</v>
+      </c>
+      <c r="H30" t="s">
+        <v>423</v>
+      </c>
+      <c r="I30">
+        <v>1840</v>
+      </c>
+      <c r="J30" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>483</v>
+      </c>
+      <c r="B31">
+        <v>32</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>480</v>
+      </c>
+      <c r="E31" t="s">
+        <v>481</v>
+      </c>
+      <c r="F31" t="s">
+        <v>378</v>
+      </c>
+      <c r="G31" t="s">
+        <v>404</v>
+      </c>
+      <c r="H31" t="s">
+        <v>423</v>
+      </c>
+      <c r="I31">
+        <v>1840</v>
+      </c>
+      <c r="J31" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>485</v>
+      </c>
+      <c r="B32">
+        <v>32</v>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>446</v>
+      </c>
+      <c r="E32" t="s">
+        <v>486</v>
+      </c>
+      <c r="F32" t="s">
+        <v>421</v>
+      </c>
+      <c r="G32" t="s">
+        <v>422</v>
+      </c>
+      <c r="H32" t="s">
+        <v>487</v>
+      </c>
+      <c r="I32">
+        <v>3090</v>
+      </c>
+      <c r="J32" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>489</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>446</v>
+      </c>
+      <c r="E33" t="s">
+        <v>486</v>
+      </c>
+      <c r="F33" t="s">
+        <v>421</v>
+      </c>
+      <c r="G33" t="s">
+        <v>422</v>
+      </c>
+      <c r="H33" t="s">
+        <v>490</v>
+      </c>
+      <c r="I33">
+        <v>3080</v>
+      </c>
+      <c r="J33" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>489</v>
+      </c>
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>446</v>
+      </c>
+      <c r="E34" t="s">
+        <v>486</v>
+      </c>
+      <c r="F34" t="s">
+        <v>421</v>
+      </c>
+      <c r="G34" t="s">
+        <v>422</v>
+      </c>
+      <c r="H34" t="s">
+        <v>490</v>
+      </c>
+      <c r="I34">
+        <v>3080</v>
+      </c>
+      <c r="J34" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>493</v>
+      </c>
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>446</v>
+      </c>
+      <c r="E35" t="s">
+        <v>486</v>
+      </c>
+      <c r="F35" t="s">
+        <v>421</v>
+      </c>
+      <c r="G35" t="s">
+        <v>422</v>
+      </c>
+      <c r="H35" t="s">
+        <v>494</v>
+      </c>
+      <c r="I35">
+        <v>3080</v>
+      </c>
+      <c r="J35" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>496</v>
+      </c>
+      <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>446</v>
+      </c>
+      <c r="E36" t="s">
+        <v>486</v>
+      </c>
+      <c r="F36" t="s">
+        <v>421</v>
+      </c>
+      <c r="G36" t="s">
+        <v>404</v>
+      </c>
+      <c r="H36" t="s">
+        <v>448</v>
+      </c>
+      <c r="I36">
+        <v>2500</v>
+      </c>
+      <c r="J36" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>498</v>
+      </c>
+      <c r="B37">
+        <v>32</v>
+      </c>
+      <c r="C37">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>446</v>
+      </c>
+      <c r="E37" t="s">
+        <v>486</v>
+      </c>
+      <c r="F37" t="s">
+        <v>421</v>
+      </c>
+      <c r="G37" t="s">
+        <v>379</v>
+      </c>
+      <c r="H37" t="s">
+        <v>499</v>
+      </c>
+      <c r="I37">
+        <v>1900</v>
+      </c>
+      <c r="J37" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>501</v>
+      </c>
+      <c r="B38">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38" t="s">
+        <v>446</v>
+      </c>
+      <c r="E38" t="s">
+        <v>486</v>
+      </c>
+      <c r="F38" t="s">
+        <v>421</v>
+      </c>
+      <c r="G38" t="s">
+        <v>388</v>
+      </c>
+      <c r="H38" t="s">
+        <v>502</v>
+      </c>
+      <c r="I38">
+        <v>1280</v>
+      </c>
+      <c r="J38" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>504</v>
+      </c>
+      <c r="B39">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>446</v>
+      </c>
+      <c r="E39" t="s">
+        <v>486</v>
+      </c>
+      <c r="F39" t="s">
+        <v>421</v>
+      </c>
+      <c r="G39" t="s">
+        <v>388</v>
+      </c>
+      <c r="H39" t="s">
+        <v>413</v>
+      </c>
+      <c r="I39">
+        <v>1240</v>
+      </c>
+      <c r="J39" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>489</v>
+      </c>
+      <c r="B40">
+        <v>32</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>408</v>
+      </c>
+      <c r="E40" t="s">
+        <v>506</v>
+      </c>
+      <c r="F40" t="s">
+        <v>427</v>
+      </c>
+      <c r="G40" t="s">
+        <v>422</v>
+      </c>
+      <c r="H40" t="s">
+        <v>490</v>
+      </c>
+      <c r="I40">
+        <v>3860</v>
+      </c>
+      <c r="J40" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>493</v>
+      </c>
+      <c r="B41">
+        <v>32</v>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>408</v>
+      </c>
+      <c r="E41" t="s">
+        <v>506</v>
+      </c>
+      <c r="F41" t="s">
+        <v>427</v>
+      </c>
+      <c r="G41" t="s">
+        <v>422</v>
+      </c>
+      <c r="H41" t="s">
+        <v>494</v>
+      </c>
+      <c r="I41">
+        <v>3850</v>
+      </c>
+      <c r="J41" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>509</v>
+      </c>
+      <c r="B42">
+        <v>32</v>
+      </c>
+      <c r="C42">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>408</v>
+      </c>
+      <c r="E42" t="s">
+        <v>506</v>
+      </c>
+      <c r="F42" t="s">
+        <v>427</v>
+      </c>
+      <c r="G42" t="s">
+        <v>422</v>
+      </c>
+      <c r="H42" t="s">
+        <v>510</v>
+      </c>
+      <c r="I42">
+        <v>3840</v>
+      </c>
+      <c r="J42" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>512</v>
+      </c>
+      <c r="B43">
+        <v>32</v>
+      </c>
+      <c r="C43">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>408</v>
+      </c>
+      <c r="E43" t="s">
+        <v>506</v>
+      </c>
+      <c r="F43" t="s">
+        <v>427</v>
+      </c>
+      <c r="G43" t="s">
+        <v>404</v>
+      </c>
+      <c r="H43" t="s">
+        <v>513</v>
+      </c>
+      <c r="I43">
+        <v>3190</v>
+      </c>
+      <c r="J43" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>515</v>
+      </c>
+      <c r="B44">
+        <v>32</v>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>408</v>
+      </c>
+      <c r="E44" t="s">
+        <v>506</v>
+      </c>
+      <c r="F44" t="s">
+        <v>427</v>
+      </c>
+      <c r="G44" t="s">
+        <v>379</v>
+      </c>
+      <c r="H44" t="s">
+        <v>516</v>
+      </c>
+      <c r="I44">
+        <v>2420</v>
+      </c>
+      <c r="J44" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>501</v>
+      </c>
+      <c r="B45">
+        <v>32</v>
+      </c>
+      <c r="C45">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>408</v>
+      </c>
+      <c r="E45" t="s">
+        <v>506</v>
+      </c>
+      <c r="F45" t="s">
+        <v>427</v>
+      </c>
+      <c r="G45" t="s">
+        <v>388</v>
+      </c>
+      <c r="H45" t="s">
+        <v>502</v>
+      </c>
+      <c r="I45">
+        <v>1620</v>
+      </c>
+      <c r="J45" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>493</v>
+      </c>
+      <c r="B46">
+        <v>32</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>519</v>
+      </c>
+      <c r="E46" t="s">
+        <v>520</v>
+      </c>
+      <c r="F46" t="s">
+        <v>521</v>
+      </c>
+      <c r="G46" t="s">
+        <v>422</v>
+      </c>
+      <c r="H46" t="s">
+        <v>522</v>
+      </c>
+      <c r="I46">
+        <v>5640</v>
+      </c>
+      <c r="J46" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>509</v>
+      </c>
+      <c r="B47">
+        <v>32</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>519</v>
+      </c>
+      <c r="E47" t="s">
+        <v>520</v>
+      </c>
+      <c r="F47" t="s">
+        <v>521</v>
+      </c>
+      <c r="G47" t="s">
+        <v>422</v>
+      </c>
+      <c r="H47" t="s">
+        <v>522</v>
+      </c>
+      <c r="I47">
+        <v>5620</v>
+      </c>
+      <c r="J47" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>525</v>
+      </c>
+      <c r="B48">
+        <v>32</v>
+      </c>
+      <c r="C48">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>519</v>
+      </c>
+      <c r="E48" t="s">
+        <v>520</v>
+      </c>
+      <c r="F48" t="s">
+        <v>521</v>
+      </c>
+      <c r="G48" t="s">
+        <v>404</v>
+      </c>
+      <c r="H48" t="s">
+        <v>462</v>
+      </c>
+      <c r="I48">
+        <v>4570</v>
+      </c>
+      <c r="J48" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>512</v>
+      </c>
+      <c r="B49">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>10</v>
+      </c>
+      <c r="D49" t="s">
+        <v>519</v>
+      </c>
+      <c r="E49" t="s">
+        <v>520</v>
+      </c>
+      <c r="F49" t="s">
+        <v>521</v>
+      </c>
+      <c r="G49" t="s">
+        <v>404</v>
+      </c>
+      <c r="H49" t="s">
+        <v>527</v>
+      </c>
+      <c r="I49">
+        <v>4240</v>
+      </c>
+      <c r="J49" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>529</v>
+      </c>
+      <c r="B50">
+        <v>36</v>
+      </c>
+      <c r="C50">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>530</v>
+      </c>
+      <c r="E50" t="s">
+        <v>531</v>
+      </c>
+      <c r="F50" t="s">
+        <v>421</v>
+      </c>
+      <c r="G50" t="s">
+        <v>422</v>
+      </c>
+      <c r="H50" t="s">
+        <v>532</v>
+      </c>
+      <c r="I50">
+        <v>3240</v>
+      </c>
+      <c r="J50" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>534</v>
+      </c>
+      <c r="B51">
+        <v>36</v>
+      </c>
+      <c r="C51">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
+        <v>519</v>
+      </c>
+      <c r="E51" t="s">
+        <v>535</v>
+      </c>
+      <c r="F51" t="s">
+        <v>521</v>
+      </c>
+      <c r="G51" t="s">
+        <v>422</v>
+      </c>
+      <c r="H51" t="s">
+        <v>536</v>
+      </c>
+      <c r="I51">
+        <v>6010</v>
+      </c>
+      <c r="J51" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>538</v>
+      </c>
+      <c r="B52">
+        <v>36</v>
+      </c>
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>519</v>
+      </c>
+      <c r="E52" t="s">
+        <v>535</v>
+      </c>
+      <c r="F52" t="s">
+        <v>521</v>
+      </c>
+      <c r="G52" t="s">
+        <v>422</v>
+      </c>
+      <c r="H52" t="s">
+        <v>539</v>
+      </c>
+      <c r="I52">
+        <v>5990</v>
+      </c>
+      <c r="J52" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>541</v>
+      </c>
+      <c r="B53">
+        <v>36</v>
+      </c>
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>519</v>
+      </c>
+      <c r="E53" t="s">
+        <v>535</v>
+      </c>
+      <c r="F53" t="s">
+        <v>521</v>
+      </c>
+      <c r="G53" t="s">
+        <v>422</v>
+      </c>
+      <c r="H53" t="s">
+        <v>542</v>
+      </c>
+      <c r="I53">
+        <v>5960</v>
+      </c>
+      <c r="J53" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>544</v>
+      </c>
+      <c r="B54">
+        <v>36</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>519</v>
+      </c>
+      <c r="E54" t="s">
+        <v>535</v>
+      </c>
+      <c r="F54" t="s">
+        <v>521</v>
+      </c>
+      <c r="G54" t="s">
+        <v>404</v>
+      </c>
+      <c r="H54" t="s">
+        <v>474</v>
+      </c>
+      <c r="I54">
+        <v>4840</v>
+      </c>
+      <c r="J54" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>544</v>
+      </c>
+      <c r="B55">
+        <v>36</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+      <c r="D55" t="s">
+        <v>519</v>
+      </c>
+      <c r="E55" t="s">
+        <v>535</v>
+      </c>
+      <c r="F55" t="s">
+        <v>521</v>
+      </c>
+      <c r="G55" t="s">
+        <v>404</v>
+      </c>
+      <c r="H55" t="s">
+        <v>474</v>
+      </c>
+      <c r="I55">
+        <v>4840</v>
+      </c>
+      <c r="J55" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>546</v>
+      </c>
+      <c r="B56">
+        <v>36</v>
+      </c>
+      <c r="C56">
+        <v>10</v>
+      </c>
+      <c r="D56" t="s">
+        <v>519</v>
+      </c>
+      <c r="E56" t="s">
+        <v>535</v>
+      </c>
+      <c r="F56" t="s">
+        <v>521</v>
+      </c>
+      <c r="G56" t="s">
+        <v>388</v>
+      </c>
+      <c r="H56" t="s">
+        <v>440</v>
+      </c>
+      <c r="I56">
+        <v>2540</v>
+      </c>
+      <c r="J56" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>548</v>
+      </c>
+      <c r="B57">
+        <v>38</v>
+      </c>
+      <c r="C57">
+        <v>8</v>
+      </c>
+      <c r="D57" t="s">
+        <v>549</v>
+      </c>
+      <c r="E57" t="s">
+        <v>550</v>
+      </c>
+      <c r="F57" t="s">
+        <v>427</v>
+      </c>
+      <c r="G57" t="s">
+        <v>422</v>
+      </c>
+      <c r="H57" t="s">
+        <v>551</v>
+      </c>
+      <c r="I57">
+        <v>4190</v>
+      </c>
+      <c r="J57" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>553</v>
+      </c>
+      <c r="B58">
+        <v>38</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>554</v>
+      </c>
+      <c r="E58" t="s">
+        <v>555</v>
+      </c>
+      <c r="F58" t="s">
+        <v>521</v>
+      </c>
+      <c r="G58" t="s">
+        <v>404</v>
+      </c>
+      <c r="H58" t="s">
+        <v>556</v>
+      </c>
+      <c r="I58">
+        <v>5050</v>
+      </c>
+      <c r="J58" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>558</v>
+      </c>
+      <c r="B59">
+        <v>38</v>
+      </c>
+      <c r="C59">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>554</v>
+      </c>
+      <c r="E59" t="s">
+        <v>555</v>
+      </c>
+      <c r="F59" t="s">
+        <v>521</v>
+      </c>
+      <c r="G59" t="s">
+        <v>404</v>
+      </c>
+      <c r="H59" t="s">
+        <v>559</v>
+      </c>
+      <c r="I59">
+        <v>5020</v>
+      </c>
+      <c r="J59" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>561</v>
+      </c>
+      <c r="B60">
+        <v>38</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+      <c r="D60" t="s">
+        <v>554</v>
+      </c>
+      <c r="E60" t="s">
+        <v>555</v>
+      </c>
+      <c r="F60" t="s">
+        <v>521</v>
+      </c>
+      <c r="G60" t="s">
+        <v>422</v>
+      </c>
+      <c r="H60" t="s">
+        <v>562</v>
+      </c>
+      <c r="I60">
+        <v>6140</v>
+      </c>
+      <c r="J60" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>564</v>
+      </c>
+      <c r="B61">
+        <v>38</v>
+      </c>
+      <c r="C61">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>554</v>
+      </c>
+      <c r="E61" t="s">
+        <v>555</v>
+      </c>
+      <c r="F61" t="s">
+        <v>521</v>
+      </c>
+      <c r="G61" t="s">
+        <v>404</v>
+      </c>
+      <c r="H61" t="s">
+        <v>565</v>
+      </c>
+      <c r="I61">
+        <v>4990</v>
+      </c>
+      <c r="J61" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>567</v>
+      </c>
+      <c r="B62">
+        <v>38</v>
+      </c>
+      <c r="C62">
+        <v>10</v>
+      </c>
+      <c r="D62" t="s">
+        <v>554</v>
+      </c>
+      <c r="E62" t="s">
+        <v>555</v>
+      </c>
+      <c r="F62" t="s">
+        <v>521</v>
+      </c>
+      <c r="G62" t="s">
+        <v>404</v>
+      </c>
+      <c r="H62" t="s">
+        <v>559</v>
+      </c>
+      <c r="I62">
+        <v>4940</v>
+      </c>
+      <c r="J62" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>569</v>
+      </c>
+      <c r="B63">
+        <v>38</v>
+      </c>
+      <c r="C63">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>554</v>
+      </c>
+      <c r="E63" t="s">
+        <v>555</v>
+      </c>
+      <c r="F63" t="s">
+        <v>521</v>
+      </c>
+      <c r="G63" t="s">
+        <v>388</v>
+      </c>
+      <c r="H63" t="s">
+        <v>570</v>
+      </c>
+      <c r="I63">
+        <v>2590</v>
+      </c>
+      <c r="J63" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>572</v>
+      </c>
+      <c r="B64">
+        <v>40</v>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>573</v>
+      </c>
+      <c r="E64" t="s">
+        <v>574</v>
+      </c>
+      <c r="F64" t="s">
+        <v>378</v>
+      </c>
+      <c r="G64" t="s">
+        <v>422</v>
+      </c>
+      <c r="H64" t="s">
+        <v>510</v>
+      </c>
+      <c r="I64">
+        <v>2470</v>
+      </c>
+      <c r="J64" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>576</v>
+      </c>
+      <c r="B65">
+        <v>40</v>
+      </c>
+      <c r="C65">
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>577</v>
+      </c>
+      <c r="E65" t="s">
+        <v>578</v>
+      </c>
+      <c r="F65" t="s">
+        <v>421</v>
+      </c>
+      <c r="G65" t="s">
+        <v>422</v>
+      </c>
+      <c r="H65" t="s">
+        <v>551</v>
+      </c>
+      <c r="I65">
+        <v>3370</v>
+      </c>
+      <c r="J65" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>580</v>
+      </c>
+      <c r="B66">
+        <v>40</v>
+      </c>
+      <c r="C66">
+        <v>8</v>
+      </c>
+      <c r="D66" t="s">
+        <v>581</v>
+      </c>
+      <c r="E66" t="s">
+        <v>582</v>
+      </c>
+      <c r="F66" t="s">
+        <v>427</v>
+      </c>
+      <c r="G66" t="s">
+        <v>422</v>
+      </c>
+      <c r="H66" t="s">
+        <v>583</v>
+      </c>
+      <c r="I66">
+        <v>4360</v>
+      </c>
+      <c r="J66" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>585</v>
+      </c>
+      <c r="B67">
+        <v>40</v>
+      </c>
+      <c r="C67">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s">
+        <v>581</v>
+      </c>
+      <c r="E67" t="s">
+        <v>582</v>
+      </c>
+      <c r="F67" t="s">
+        <v>427</v>
+      </c>
+      <c r="G67" t="s">
+        <v>422</v>
+      </c>
+      <c r="H67" t="s">
+        <v>586</v>
+      </c>
+      <c r="I67">
+        <v>4350</v>
+      </c>
+      <c r="J67" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>588</v>
+      </c>
+      <c r="B68">
+        <v>40</v>
+      </c>
+      <c r="C68">
+        <v>20</v>
+      </c>
+      <c r="D68" t="s">
+        <v>581</v>
+      </c>
+      <c r="E68" t="s">
+        <v>582</v>
+      </c>
+      <c r="F68" t="s">
+        <v>427</v>
+      </c>
+      <c r="G68" t="s">
+        <v>404</v>
+      </c>
+      <c r="H68" t="s">
+        <v>522</v>
+      </c>
+      <c r="I68">
+        <v>4300</v>
+      </c>
+      <c r="J68" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>590</v>
+      </c>
+      <c r="B69">
+        <v>40</v>
+      </c>
+      <c r="C69">
+        <v>16</v>
+      </c>
+      <c r="D69" t="s">
+        <v>591</v>
+      </c>
+      <c r="E69" t="s">
+        <v>592</v>
+      </c>
+      <c r="F69" t="s">
+        <v>593</v>
+      </c>
+      <c r="G69" t="s">
+        <v>422</v>
+      </c>
+      <c r="H69" t="s">
+        <v>594</v>
+      </c>
+      <c r="I69">
+        <v>5170</v>
+      </c>
+      <c r="J69" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>585</v>
+      </c>
+      <c r="B70">
+        <v>40</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>596</v>
+      </c>
+      <c r="E70" t="s">
+        <v>597</v>
+      </c>
+      <c r="F70" t="s">
+        <v>521</v>
+      </c>
+      <c r="G70" t="s">
+        <v>422</v>
+      </c>
+      <c r="H70" t="s">
+        <v>594</v>
+      </c>
+      <c r="I70">
+        <v>6340</v>
+      </c>
+      <c r="J70" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>599</v>
+      </c>
+      <c r="B71">
+        <v>40</v>
+      </c>
+      <c r="C71">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>596</v>
+      </c>
+      <c r="E71" t="s">
+        <v>597</v>
+      </c>
+      <c r="F71" t="s">
+        <v>521</v>
+      </c>
+      <c r="G71" t="s">
+        <v>422</v>
+      </c>
+      <c r="H71" t="s">
+        <v>600</v>
+      </c>
+      <c r="I71">
+        <v>6330</v>
+      </c>
+      <c r="J71" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>590</v>
+      </c>
+      <c r="B72">
+        <v>40</v>
+      </c>
+      <c r="C72">
+        <v>16</v>
+      </c>
+      <c r="D72" t="s">
+        <v>596</v>
+      </c>
+      <c r="E72" t="s">
+        <v>597</v>
+      </c>
+      <c r="F72" t="s">
+        <v>521</v>
+      </c>
+      <c r="G72" t="s">
+        <v>422</v>
+      </c>
+      <c r="H72" t="s">
+        <v>602</v>
+      </c>
+      <c r="I72">
+        <v>6300</v>
+      </c>
+      <c r="J72" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>588</v>
+      </c>
+      <c r="B73">
+        <v>40</v>
+      </c>
+      <c r="C73">
+        <v>20</v>
+      </c>
+      <c r="D73" t="s">
+        <v>596</v>
+      </c>
+      <c r="E73" t="s">
+        <v>597</v>
+      </c>
+      <c r="F73" t="s">
+        <v>521</v>
+      </c>
+      <c r="G73" t="s">
+        <v>404</v>
+      </c>
+      <c r="H73" t="s">
+        <v>604</v>
+      </c>
+      <c r="I73">
+        <v>5130</v>
+      </c>
+      <c r="J73" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>606</v>
+      </c>
+      <c r="B74">
+        <v>40</v>
+      </c>
+      <c r="C74">
+        <v>30</v>
+      </c>
+      <c r="D74" t="s">
+        <v>596</v>
+      </c>
+      <c r="E74" t="s">
+        <v>597</v>
+      </c>
+      <c r="F74" t="s">
+        <v>521</v>
+      </c>
+      <c r="G74" t="s">
+        <v>379</v>
+      </c>
+      <c r="H74" t="s">
+        <v>607</v>
+      </c>
+      <c r="I74">
+        <v>4000</v>
+      </c>
+      <c r="J74" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>609</v>
+      </c>
+      <c r="B75">
+        <v>40</v>
+      </c>
+      <c r="C75">
+        <v>25</v>
+      </c>
+      <c r="D75" t="s">
+        <v>596</v>
+      </c>
+      <c r="E75" t="s">
+        <v>597</v>
+      </c>
+      <c r="F75" t="s">
+        <v>521</v>
+      </c>
+      <c r="G75" t="s">
+        <v>404</v>
+      </c>
+      <c r="H75" t="s">
+        <v>510</v>
+      </c>
+      <c r="I75">
+        <v>5080</v>
+      </c>
+      <c r="J75" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>611</v>
+      </c>
+      <c r="B76">
+        <v>40</v>
+      </c>
+      <c r="C76">
+        <v>40</v>
+      </c>
+      <c r="D76" t="s">
+        <v>596</v>
+      </c>
+      <c r="E76" t="s">
+        <v>597</v>
+      </c>
+      <c r="F76" t="s">
+        <v>521</v>
+      </c>
+      <c r="G76" t="s">
+        <v>388</v>
+      </c>
+      <c r="H76" t="s">
+        <v>612</v>
+      </c>
+      <c r="I76">
+        <v>2660</v>
+      </c>
+      <c r="J76" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>599</v>
+      </c>
+      <c r="B77">
+        <v>40</v>
+      </c>
+      <c r="C77">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>614</v>
+      </c>
+      <c r="E77" t="s">
+        <v>615</v>
+      </c>
+      <c r="F77" t="s">
+        <v>616</v>
+      </c>
+      <c r="G77" t="s">
+        <v>422</v>
+      </c>
+      <c r="H77" t="s">
+        <v>617</v>
+      </c>
+      <c r="I77">
+        <v>7430</v>
+      </c>
+      <c r="J77" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>590</v>
+      </c>
+      <c r="B78">
+        <v>40</v>
+      </c>
+      <c r="C78">
+        <v>16</v>
+      </c>
+      <c r="D78" t="s">
+        <v>614</v>
+      </c>
+      <c r="E78" t="s">
+        <v>615</v>
+      </c>
+      <c r="F78" t="s">
+        <v>616</v>
+      </c>
+      <c r="G78" t="s">
+        <v>422</v>
+      </c>
+      <c r="H78" t="s">
+        <v>619</v>
+      </c>
+      <c r="I78">
+        <v>7400</v>
+      </c>
+      <c r="J78" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" t="s">
+        <v>621</v>
+      </c>
+      <c r="B79">
+        <v>45</v>
+      </c>
+      <c r="C79">
+        <v>8</v>
+      </c>
+      <c r="D79" t="s">
+        <v>622</v>
+      </c>
+      <c r="E79" t="s">
+        <v>623</v>
+      </c>
+      <c r="F79" t="s">
+        <v>427</v>
+      </c>
+      <c r="G79" t="s">
+        <v>422</v>
+      </c>
+      <c r="H79" t="s">
+        <v>624</v>
+      </c>
+      <c r="I79">
+        <v>4550</v>
+      </c>
+      <c r="J79" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" t="s">
+        <v>626</v>
+      </c>
+      <c r="B80">
+        <v>45</v>
+      </c>
+      <c r="C80">
+        <v>10</v>
+      </c>
+      <c r="D80" t="s">
+        <v>627</v>
+      </c>
+      <c r="E80" t="s">
+        <v>628</v>
+      </c>
+      <c r="F80" t="s">
+        <v>521</v>
+      </c>
+      <c r="G80" t="s">
+        <v>422</v>
+      </c>
+      <c r="H80" t="s">
+        <v>629</v>
+      </c>
+      <c r="I80">
+        <v>6810</v>
+      </c>
+      <c r="J80" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" t="s">
+        <v>631</v>
+      </c>
+      <c r="B81">
+        <v>45</v>
+      </c>
+      <c r="C81">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>627</v>
+      </c>
+      <c r="E81" t="s">
+        <v>628</v>
+      </c>
+      <c r="F81" t="s">
+        <v>521</v>
+      </c>
+      <c r="G81" t="s">
+        <v>422</v>
+      </c>
+      <c r="H81" t="s">
+        <v>632</v>
+      </c>
+      <c r="I81">
+        <v>6800</v>
+      </c>
+      <c r="J81" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>634</v>
+      </c>
+      <c r="B82">
+        <v>45</v>
+      </c>
+      <c r="C82">
+        <v>16</v>
+      </c>
+      <c r="D82" t="s">
+        <v>627</v>
+      </c>
+      <c r="E82" t="s">
+        <v>628</v>
+      </c>
+      <c r="F82" t="s">
+        <v>521</v>
+      </c>
+      <c r="G82" t="s">
+        <v>422</v>
+      </c>
+      <c r="H82" t="s">
+        <v>635</v>
+      </c>
+      <c r="I82">
+        <v>6780</v>
+      </c>
+      <c r="J82" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>637</v>
+      </c>
+      <c r="B83">
+        <v>45</v>
+      </c>
+      <c r="C83">
+        <v>20</v>
+      </c>
+      <c r="D83" t="s">
+        <v>627</v>
+      </c>
+      <c r="E83" t="s">
+        <v>628</v>
+      </c>
+      <c r="F83" t="s">
+        <v>521</v>
+      </c>
+      <c r="G83" t="s">
+        <v>404</v>
+      </c>
+      <c r="H83" t="s">
+        <v>638</v>
+      </c>
+      <c r="I83">
+        <v>5520</v>
+      </c>
+      <c r="J83" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
+        <v>640</v>
+      </c>
+      <c r="B84">
+        <v>45</v>
+      </c>
+      <c r="C84">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>627</v>
+      </c>
+      <c r="E84" t="s">
+        <v>628</v>
+      </c>
+      <c r="F84" t="s">
+        <v>521</v>
+      </c>
+      <c r="G84" t="s">
+        <v>404</v>
+      </c>
+      <c r="H84" t="s">
+        <v>638</v>
+      </c>
+      <c r="I84">
+        <v>5480</v>
+      </c>
+      <c r="J84" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
+        <v>642</v>
+      </c>
+      <c r="B85">
+        <v>45</v>
+      </c>
+      <c r="C85">
+        <v>40</v>
+      </c>
+      <c r="D85" t="s">
+        <v>627</v>
+      </c>
+      <c r="E85" t="s">
+        <v>628</v>
+      </c>
+      <c r="F85" t="s">
+        <v>521</v>
+      </c>
+      <c r="G85" t="s">
+        <v>379</v>
+      </c>
+      <c r="H85" t="s">
+        <v>467</v>
+      </c>
+      <c r="I85">
+        <v>4100</v>
+      </c>
+      <c r="J85" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" t="s">
+        <v>631</v>
+      </c>
+      <c r="B86">
+        <v>45</v>
+      </c>
+      <c r="C86">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>644</v>
+      </c>
+      <c r="E86" t="s">
+        <v>628</v>
+      </c>
+      <c r="F86" t="s">
+        <v>616</v>
+      </c>
+      <c r="G86" t="s">
+        <v>422</v>
+      </c>
+      <c r="H86" t="s">
+        <v>645</v>
+      </c>
+      <c r="I86">
+        <v>7830</v>
+      </c>
+      <c r="J86" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" t="s">
+        <v>634</v>
+      </c>
+      <c r="B87">
+        <v>45</v>
+      </c>
+      <c r="C87">
+        <v>16</v>
+      </c>
+      <c r="D87" t="s">
+        <v>644</v>
+      </c>
+      <c r="E87" t="s">
+        <v>647</v>
+      </c>
+      <c r="F87" t="s">
+        <v>616</v>
+      </c>
+      <c r="G87" t="s">
+        <v>422</v>
+      </c>
+      <c r="H87" t="s">
+        <v>648</v>
+      </c>
+      <c r="I87">
+        <v>7810</v>
+      </c>
+      <c r="J87" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" t="s">
+        <v>637</v>
+      </c>
+      <c r="B88">
+        <v>45</v>
+      </c>
+      <c r="C88">
+        <v>20</v>
+      </c>
+      <c r="D88" t="s">
+        <v>644</v>
+      </c>
+      <c r="E88" t="s">
+        <v>647</v>
+      </c>
+      <c r="F88" t="s">
+        <v>616</v>
+      </c>
+      <c r="G88" t="s">
+        <v>404</v>
+      </c>
+      <c r="H88" t="s">
+        <v>650</v>
+      </c>
+      <c r="I88">
+        <v>6360</v>
+      </c>
+      <c r="J88" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" t="s">
+        <v>652</v>
+      </c>
+      <c r="B89">
+        <v>50</v>
+      </c>
+      <c r="C89">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>653</v>
+      </c>
+      <c r="E89" t="s">
+        <v>654</v>
+      </c>
+      <c r="F89" t="s">
+        <v>378</v>
+      </c>
+      <c r="G89" t="s">
+        <v>422</v>
+      </c>
+      <c r="H89" t="s">
+        <v>638</v>
+      </c>
+      <c r="I89">
+        <v>2700</v>
+      </c>
+      <c r="J89" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" t="s">
+        <v>656</v>
+      </c>
+      <c r="B90">
+        <v>50</v>
+      </c>
+      <c r="C90">
+        <v>8</v>
+      </c>
+      <c r="D90" t="s">
+        <v>440</v>
+      </c>
+      <c r="E90" t="s">
+        <v>657</v>
+      </c>
+      <c r="F90" t="s">
+        <v>427</v>
+      </c>
+      <c r="G90" t="s">
+        <v>422</v>
+      </c>
+      <c r="H90" t="s">
+        <v>658</v>
+      </c>
+      <c r="I90">
+        <v>4730</v>
+      </c>
+      <c r="J90" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" t="s">
+        <v>660</v>
+      </c>
+      <c r="B91">
+        <v>50</v>
+      </c>
+      <c r="C91">
+        <v>10</v>
+      </c>
+      <c r="D91" t="s">
+        <v>661</v>
+      </c>
+      <c r="E91" t="s">
+        <v>662</v>
+      </c>
+      <c r="F91" t="s">
+        <v>521</v>
+      </c>
+      <c r="G91" t="s">
+        <v>422</v>
+      </c>
+      <c r="H91" t="s">
+        <v>663</v>
+      </c>
+      <c r="I91">
+        <v>7050</v>
+      </c>
+      <c r="J91" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" t="s">
+        <v>665</v>
+      </c>
+      <c r="B92">
+        <v>50</v>
+      </c>
+      <c r="C92">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>661</v>
+      </c>
+      <c r="E92" t="s">
+        <v>662</v>
+      </c>
+      <c r="F92" t="s">
+        <v>521</v>
+      </c>
+      <c r="G92" t="s">
+        <v>422</v>
+      </c>
+      <c r="H92" t="s">
+        <v>666</v>
+      </c>
+      <c r="I92">
+        <v>7040</v>
+      </c>
+      <c r="J92" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" t="s">
+        <v>668</v>
+      </c>
+      <c r="B93">
+        <v>50</v>
+      </c>
+      <c r="C93">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>661</v>
+      </c>
+      <c r="E93" t="s">
+        <v>662</v>
+      </c>
+      <c r="F93" t="s">
+        <v>521</v>
+      </c>
+      <c r="G93" t="s">
+        <v>422</v>
+      </c>
+      <c r="H93" t="s">
+        <v>669</v>
+      </c>
+      <c r="I93">
+        <v>7030</v>
+      </c>
+      <c r="J93" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" t="s">
+        <v>671</v>
+      </c>
+      <c r="B94">
+        <v>50</v>
+      </c>
+      <c r="C94">
+        <v>16</v>
+      </c>
+      <c r="D94" t="s">
+        <v>661</v>
+      </c>
+      <c r="E94" t="s">
+        <v>662</v>
+      </c>
+      <c r="F94" t="s">
+        <v>521</v>
+      </c>
+      <c r="G94" t="s">
+        <v>422</v>
+      </c>
+      <c r="H94" t="s">
+        <v>669</v>
+      </c>
+      <c r="I94">
+        <v>7020</v>
+      </c>
+      <c r="J94" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" t="s">
+        <v>672</v>
+      </c>
+      <c r="B95">
+        <v>50</v>
+      </c>
+      <c r="C95">
+        <v>20</v>
+      </c>
+      <c r="D95" t="s">
+        <v>661</v>
+      </c>
+      <c r="E95" t="s">
+        <v>662</v>
+      </c>
+      <c r="F95" t="s">
+        <v>521</v>
+      </c>
+      <c r="G95" t="s">
+        <v>404</v>
+      </c>
+      <c r="H95" t="s">
+        <v>673</v>
+      </c>
+      <c r="I95">
+        <v>5720</v>
+      </c>
+      <c r="J95" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" t="s">
+        <v>675</v>
+      </c>
+      <c r="B96">
+        <v>50</v>
+      </c>
+      <c r="C96">
+        <v>25</v>
+      </c>
+      <c r="D96" t="s">
+        <v>661</v>
+      </c>
+      <c r="E96" t="s">
+        <v>662</v>
+      </c>
+      <c r="F96" t="s">
+        <v>521</v>
+      </c>
+      <c r="G96" t="s">
+        <v>404</v>
+      </c>
+      <c r="H96" t="s">
+        <v>676</v>
+      </c>
+      <c r="I96">
+        <v>5690</v>
+      </c>
+      <c r="J96" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" t="s">
+        <v>678</v>
+      </c>
+      <c r="B97">
+        <v>50</v>
+      </c>
+      <c r="C97">
+        <v>30</v>
+      </c>
+      <c r="D97" t="s">
+        <v>661</v>
+      </c>
+      <c r="E97" t="s">
+        <v>662</v>
+      </c>
+      <c r="F97" t="s">
+        <v>521</v>
+      </c>
+      <c r="G97" t="s">
+        <v>404</v>
+      </c>
+      <c r="H97" t="s">
+        <v>586</v>
+      </c>
+      <c r="I97">
+        <v>5650</v>
+      </c>
+      <c r="J97" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" t="s">
+        <v>680</v>
+      </c>
+      <c r="B98">
+        <v>50</v>
+      </c>
+      <c r="C98">
+        <v>35</v>
+      </c>
+      <c r="D98" t="s">
+        <v>661</v>
+      </c>
+      <c r="E98" t="s">
+        <v>662</v>
+      </c>
+      <c r="F98" t="s">
+        <v>521</v>
+      </c>
+      <c r="G98" t="s">
+        <v>379</v>
+      </c>
+      <c r="H98" t="s">
+        <v>474</v>
+      </c>
+      <c r="I98">
+        <v>4430</v>
+      </c>
+      <c r="J98" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" t="s">
+        <v>682</v>
+      </c>
+      <c r="B99">
+        <v>50</v>
+      </c>
+      <c r="C99">
+        <v>40</v>
+      </c>
+      <c r="D99" t="s">
+        <v>661</v>
+      </c>
+      <c r="E99" t="s">
+        <v>662</v>
+      </c>
+      <c r="F99" t="s">
+        <v>521</v>
+      </c>
+      <c r="G99" t="s">
+        <v>379</v>
+      </c>
+      <c r="H99" t="s">
+        <v>471</v>
+      </c>
+      <c r="I99">
+        <v>4390</v>
+      </c>
+      <c r="J99" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" t="s">
+        <v>684</v>
+      </c>
+      <c r="B100">
+        <v>50</v>
+      </c>
+      <c r="C100">
+        <v>30</v>
+      </c>
+      <c r="D100" t="s">
+        <v>685</v>
+      </c>
+      <c r="E100" t="s">
+        <v>686</v>
+      </c>
+      <c r="F100" t="s">
+        <v>616</v>
+      </c>
+      <c r="G100" t="s">
+        <v>388</v>
+      </c>
+      <c r="H100" t="s">
+        <v>516</v>
+      </c>
+      <c r="I100">
+        <v>3560</v>
+      </c>
+      <c r="J100" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" t="s">
+        <v>665</v>
+      </c>
+      <c r="B101">
+        <v>50</v>
+      </c>
+      <c r="C101">
+        <v>12</v>
+      </c>
+      <c r="D101" t="s">
+        <v>688</v>
+      </c>
+      <c r="E101" t="s">
+        <v>689</v>
+      </c>
+      <c r="F101" t="s">
+        <v>690</v>
+      </c>
+      <c r="G101" t="s">
+        <v>422</v>
+      </c>
+      <c r="H101" t="s">
+        <v>691</v>
+      </c>
+      <c r="I101">
+        <v>9480</v>
+      </c>
+      <c r="J101" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" t="s">
+        <v>671</v>
+      </c>
+      <c r="B102">
+        <v>50</v>
+      </c>
+      <c r="C102">
+        <v>16</v>
+      </c>
+      <c r="D102" t="s">
+        <v>688</v>
+      </c>
+      <c r="E102" t="s">
+        <v>689</v>
+      </c>
+      <c r="F102" t="s">
+        <v>690</v>
+      </c>
+      <c r="G102" t="s">
+        <v>422</v>
+      </c>
+      <c r="H102" t="s">
+        <v>693</v>
+      </c>
+      <c r="I102">
+        <v>9450</v>
+      </c>
+      <c r="J102" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" t="s">
+        <v>695</v>
+      </c>
+      <c r="B103">
+        <v>50</v>
+      </c>
+      <c r="C103">
+        <v>20</v>
+      </c>
+      <c r="D103" t="s">
+        <v>688</v>
+      </c>
+      <c r="E103" t="s">
+        <v>689</v>
+      </c>
+      <c r="F103" t="s">
+        <v>690</v>
+      </c>
+      <c r="G103" t="s">
+        <v>422</v>
+      </c>
+      <c r="H103" t="s">
+        <v>696</v>
+      </c>
+      <c r="I103">
+        <v>9420</v>
+      </c>
+      <c r="J103" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" t="s">
+        <v>698</v>
+      </c>
+      <c r="B104">
+        <v>50</v>
+      </c>
+      <c r="C104">
+        <v>50</v>
+      </c>
+      <c r="D104" t="s">
+        <v>688</v>
+      </c>
+      <c r="E104" t="s">
+        <v>689</v>
+      </c>
+      <c r="F104" t="s">
+        <v>690</v>
+      </c>
+      <c r="G104" t="s">
+        <v>388</v>
+      </c>
+      <c r="H104" t="s">
+        <v>699</v>
+      </c>
+      <c r="I104">
+        <v>3980</v>
+      </c>
+      <c r="J104" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" t="s">
+        <v>672</v>
+      </c>
+      <c r="B105">
+        <v>50</v>
+      </c>
+      <c r="C105">
+        <v>20</v>
+      </c>
+      <c r="D105" t="s">
+        <v>701</v>
+      </c>
+      <c r="E105" t="s">
+        <v>702</v>
+      </c>
+      <c r="F105" t="s">
+        <v>703</v>
+      </c>
+      <c r="G105" t="s">
+        <v>404</v>
+      </c>
+      <c r="H105" t="s">
+        <v>704</v>
+      </c>
+      <c r="I105">
+        <v>9870</v>
+      </c>
+      <c r="J105" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" t="s">
+        <v>706</v>
+      </c>
+      <c r="B106">
+        <v>55</v>
+      </c>
+      <c r="C106">
+        <v>16</v>
+      </c>
+      <c r="D106" t="s">
+        <v>707</v>
+      </c>
+      <c r="E106" t="s">
+        <v>708</v>
+      </c>
+      <c r="F106" t="s">
+        <v>521</v>
+      </c>
+      <c r="G106" t="s">
+        <v>422</v>
+      </c>
+      <c r="H106" t="s">
+        <v>709</v>
+      </c>
+      <c r="I106">
+        <v>7420</v>
+      </c>
+      <c r="J106" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" t="s">
+        <v>711</v>
+      </c>
+      <c r="B107">
+        <v>63</v>
+      </c>
+      <c r="C107">
+        <v>10</v>
+      </c>
+      <c r="D107" t="s">
+        <v>712</v>
+      </c>
+      <c r="E107" t="s">
+        <v>713</v>
+      </c>
+      <c r="F107" t="s">
+        <v>521</v>
+      </c>
+      <c r="G107" t="s">
+        <v>422</v>
+      </c>
+      <c r="H107" t="s">
+        <v>714</v>
+      </c>
+      <c r="I107">
+        <v>7720</v>
+      </c>
+      <c r="J107" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>716</v>
+      </c>
+      <c r="B108">
+        <v>63</v>
+      </c>
+      <c r="C108">
+        <v>12</v>
+      </c>
+      <c r="D108" t="s">
+        <v>712</v>
+      </c>
+      <c r="E108" t="s">
+        <v>713</v>
+      </c>
+      <c r="F108" t="s">
+        <v>521</v>
+      </c>
+      <c r="G108" t="s">
+        <v>422</v>
+      </c>
+      <c r="H108" t="s">
+        <v>717</v>
+      </c>
+      <c r="I108">
+        <v>7720</v>
+      </c>
+      <c r="J108" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" t="s">
+        <v>719</v>
+      </c>
+      <c r="B109">
+        <v>63</v>
+      </c>
+      <c r="C109">
+        <v>20</v>
+      </c>
+      <c r="D109" t="s">
+        <v>712</v>
+      </c>
+      <c r="E109" t="s">
+        <v>713</v>
+      </c>
+      <c r="F109" t="s">
+        <v>521</v>
+      </c>
+      <c r="G109" t="s">
+        <v>422</v>
+      </c>
+      <c r="H109" t="s">
+        <v>720</v>
+      </c>
+      <c r="I109">
+        <v>7850</v>
+      </c>
+      <c r="J109" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>722</v>
+      </c>
+      <c r="B110">
+        <v>63</v>
+      </c>
+      <c r="C110">
+        <v>40</v>
+      </c>
+      <c r="D110" t="s">
+        <v>712</v>
+      </c>
+      <c r="E110" t="s">
+        <v>713</v>
+      </c>
+      <c r="F110" t="s">
+        <v>521</v>
+      </c>
+      <c r="G110" t="s">
+        <v>388</v>
+      </c>
+      <c r="H110" t="s">
+        <v>723</v>
+      </c>
+      <c r="I110">
+        <v>3310</v>
+      </c>
+      <c r="J110" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>716</v>
+      </c>
+      <c r="B111">
+        <v>63</v>
+      </c>
+      <c r="C111">
+        <v>12</v>
+      </c>
+      <c r="D111" t="s">
+        <v>725</v>
+      </c>
+      <c r="E111" t="s">
+        <v>726</v>
+      </c>
+      <c r="F111" t="s">
+        <v>690</v>
+      </c>
+      <c r="G111" t="s">
+        <v>422</v>
+      </c>
+      <c r="H111" t="s">
+        <v>727</v>
+      </c>
+      <c r="I111">
+        <v>10520</v>
+      </c>
+      <c r="J111" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" t="s">
+        <v>729</v>
+      </c>
+      <c r="B112">
+        <v>63</v>
+      </c>
+      <c r="C112">
+        <v>16</v>
+      </c>
+      <c r="D112" t="s">
+        <v>730</v>
+      </c>
+      <c r="E112" t="s">
+        <v>731</v>
+      </c>
+      <c r="F112" t="s">
+        <v>703</v>
+      </c>
+      <c r="G112" t="s">
+        <v>404</v>
+      </c>
+      <c r="H112" t="s">
+        <v>693</v>
+      </c>
+      <c r="I112">
+        <v>11010</v>
+      </c>
+      <c r="J112" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>719</v>
+      </c>
+      <c r="B113">
+        <v>63</v>
+      </c>
+      <c r="C113">
+        <v>20</v>
+      </c>
+      <c r="D113" t="s">
+        <v>730</v>
+      </c>
+      <c r="E113" t="s">
+        <v>731</v>
+      </c>
+      <c r="F113" t="s">
+        <v>703</v>
+      </c>
+      <c r="G113" t="s">
+        <v>422</v>
+      </c>
+      <c r="H113" t="s">
+        <v>733</v>
+      </c>
+      <c r="I113">
+        <v>13430</v>
+      </c>
+      <c r="J113" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" t="s">
+        <v>735</v>
+      </c>
+      <c r="B114">
+        <v>63</v>
+      </c>
+      <c r="C114">
+        <v>25</v>
+      </c>
+      <c r="D114" t="s">
+        <v>730</v>
+      </c>
+      <c r="E114" t="s">
+        <v>731</v>
+      </c>
+      <c r="F114" t="s">
+        <v>703</v>
+      </c>
+      <c r="G114" t="s">
+        <v>422</v>
+      </c>
+      <c r="H114" t="s">
+        <v>736</v>
+      </c>
+      <c r="I114">
+        <v>13390</v>
+      </c>
+      <c r="J114" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>738</v>
+      </c>
+      <c r="B115">
+        <v>70</v>
+      </c>
+      <c r="C115">
+        <v>16</v>
+      </c>
+      <c r="D115" t="s">
+        <v>739</v>
+      </c>
+      <c r="E115" t="s">
+        <v>740</v>
+      </c>
+      <c r="F115" t="s">
+        <v>703</v>
+      </c>
+      <c r="G115" t="s">
+        <v>404</v>
+      </c>
+      <c r="H115" t="s">
+        <v>741</v>
+      </c>
+      <c r="I115">
+        <v>11470</v>
+      </c>
+      <c r="J115" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>743</v>
+      </c>
+      <c r="B116">
+        <v>70</v>
+      </c>
+      <c r="C116">
+        <v>20</v>
+      </c>
+      <c r="D116" t="s">
+        <v>739</v>
+      </c>
+      <c r="E116" t="s">
+        <v>740</v>
+      </c>
+      <c r="F116" t="s">
+        <v>703</v>
+      </c>
+      <c r="G116" t="s">
+        <v>404</v>
+      </c>
+      <c r="H116" t="s">
+        <v>744</v>
+      </c>
+      <c r="I116">
+        <v>11450</v>
+      </c>
+      <c r="J116" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" t="s">
+        <v>746</v>
+      </c>
+      <c r="B117">
+        <v>80</v>
+      </c>
+      <c r="C117">
+        <v>10</v>
+      </c>
+      <c r="D117" t="s">
+        <v>747</v>
+      </c>
+      <c r="E117" t="s">
+        <v>748</v>
+      </c>
+      <c r="F117" t="s">
+        <v>521</v>
+      </c>
+      <c r="G117" t="s">
+        <v>422</v>
+      </c>
+      <c r="H117" t="s">
+        <v>749</v>
+      </c>
+      <c r="I117">
+        <v>8620</v>
+      </c>
+      <c r="J117" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" t="s">
+        <v>751</v>
+      </c>
+      <c r="B118">
+        <v>80</v>
+      </c>
+      <c r="C118">
+        <v>12</v>
+      </c>
+      <c r="D118" t="s">
+        <v>752</v>
+      </c>
+      <c r="E118" t="s">
+        <v>753</v>
+      </c>
+      <c r="F118" t="s">
+        <v>690</v>
+      </c>
+      <c r="G118" t="s">
+        <v>422</v>
+      </c>
+      <c r="H118" t="s">
+        <v>754</v>
+      </c>
+      <c r="I118">
+        <v>11740</v>
+      </c>
+      <c r="J118" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" t="s">
+        <v>756</v>
+      </c>
+      <c r="B119">
+        <v>80</v>
+      </c>
+      <c r="C119">
+        <v>16</v>
+      </c>
+      <c r="D119" t="s">
+        <v>757</v>
+      </c>
+      <c r="E119" t="s">
+        <v>753</v>
+      </c>
+      <c r="F119" t="s">
+        <v>703</v>
+      </c>
+      <c r="G119" t="s">
+        <v>404</v>
+      </c>
+      <c r="H119" t="s">
+        <v>758</v>
+      </c>
+      <c r="I119">
+        <v>12410</v>
+      </c>
+      <c r="J119" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" t="s">
+        <v>760</v>
+      </c>
+      <c r="B120">
+        <v>80</v>
+      </c>
+      <c r="C120">
+        <v>20</v>
+      </c>
+      <c r="D120" t="s">
+        <v>757</v>
+      </c>
+      <c r="E120" t="s">
+        <v>753</v>
+      </c>
+      <c r="F120" t="s">
+        <v>703</v>
+      </c>
+      <c r="G120" t="s">
+        <v>404</v>
+      </c>
+      <c r="H120" t="s">
+        <v>761</v>
+      </c>
+      <c r="I120">
+        <v>12400</v>
+      </c>
+      <c r="J120" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" t="s">
+        <v>763</v>
+      </c>
+      <c r="B121">
+        <v>80</v>
+      </c>
+      <c r="C121">
+        <v>25</v>
+      </c>
+      <c r="D121" t="s">
+        <v>757</v>
+      </c>
+      <c r="E121" t="s">
+        <v>764</v>
+      </c>
+      <c r="F121" t="s">
+        <v>703</v>
+      </c>
+      <c r="G121" t="s">
+        <v>404</v>
+      </c>
+      <c r="H121" t="s">
+        <v>765</v>
+      </c>
+      <c r="I121">
+        <v>12370</v>
+      </c>
+      <c r="J121" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" t="s">
+        <v>767</v>
+      </c>
+      <c r="B122">
+        <v>80</v>
+      </c>
+      <c r="C122">
+        <v>30</v>
+      </c>
+      <c r="D122" t="s">
+        <v>757</v>
+      </c>
+      <c r="E122" t="s">
+        <v>764</v>
+      </c>
+      <c r="F122" t="s">
+        <v>703</v>
+      </c>
+      <c r="G122" t="s">
+        <v>404</v>
+      </c>
+      <c r="H122" t="s">
+        <v>761</v>
+      </c>
+      <c r="I122">
+        <v>12340</v>
+      </c>
+      <c r="J122" t="s">
+        <v>768</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J467"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
@@ -28846,3919 +32761,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J122"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B2">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E2" t="s">
-        <v>377</v>
-      </c>
-      <c r="F2" t="s">
-        <v>378</v>
-      </c>
-      <c r="G2" t="s">
-        <v>379</v>
-      </c>
-      <c r="H2" t="s">
-        <v>380</v>
-      </c>
-      <c r="I2">
-        <v>920</v>
-      </c>
-      <c r="J2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B3">
-        <v>15</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E3" t="s">
-        <v>384</v>
-      </c>
-      <c r="F3" t="s">
-        <v>379</v>
-      </c>
-      <c r="G3" t="s">
-        <v>379</v>
-      </c>
-      <c r="H3" t="s">
-        <v>385</v>
-      </c>
-      <c r="I3">
-        <v>930</v>
-      </c>
-      <c r="J3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>387</v>
-      </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E4" t="s">
-        <v>384</v>
-      </c>
-      <c r="F4" t="s">
-        <v>379</v>
-      </c>
-      <c r="G4" t="s">
-        <v>388</v>
-      </c>
-      <c r="H4" t="s">
-        <v>389</v>
-      </c>
-      <c r="I4">
-        <v>610</v>
-      </c>
-      <c r="J4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>382</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>391</v>
-      </c>
-      <c r="E5" t="s">
-        <v>392</v>
-      </c>
-      <c r="F5" t="s">
-        <v>378</v>
-      </c>
-      <c r="G5" t="s">
-        <v>379</v>
-      </c>
-      <c r="H5" t="s">
-        <v>393</v>
-      </c>
-      <c r="I5">
-        <v>960</v>
-      </c>
-      <c r="J5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>395</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>391</v>
-      </c>
-      <c r="E6" t="s">
-        <v>392</v>
-      </c>
-      <c r="F6" t="s">
-        <v>378</v>
-      </c>
-      <c r="G6" t="s">
-        <v>388</v>
-      </c>
-      <c r="H6" t="s">
-        <v>391</v>
-      </c>
-      <c r="I6">
-        <v>630</v>
-      </c>
-      <c r="J6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>397</v>
-      </c>
-      <c r="B7">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>398</v>
-      </c>
-      <c r="E7" t="s">
-        <v>399</v>
-      </c>
-      <c r="F7" t="s">
-        <v>378</v>
-      </c>
-      <c r="G7" t="s">
-        <v>388</v>
-      </c>
-      <c r="H7" t="s">
-        <v>400</v>
-      </c>
-      <c r="I7">
-        <v>680</v>
-      </c>
-      <c r="J7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>402</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E8" t="s">
-        <v>403</v>
-      </c>
-      <c r="F8" t="s">
-        <v>379</v>
-      </c>
-      <c r="G8" t="s">
-        <v>404</v>
-      </c>
-      <c r="H8" t="s">
-        <v>405</v>
-      </c>
-      <c r="I8">
-        <v>1390</v>
-      </c>
-      <c r="J8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>407</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>408</v>
-      </c>
-      <c r="E9" t="s">
-        <v>409</v>
-      </c>
-      <c r="F9" t="s">
-        <v>378</v>
-      </c>
-      <c r="G9" t="s">
-        <v>404</v>
-      </c>
-      <c r="H9" t="s">
-        <v>410</v>
-      </c>
-      <c r="I9">
-        <v>1490</v>
-      </c>
-      <c r="J9" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>412</v>
-      </c>
-      <c r="B10">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>408</v>
-      </c>
-      <c r="E10" t="s">
-        <v>409</v>
-      </c>
-      <c r="F10" t="s">
-        <v>378</v>
-      </c>
-      <c r="G10" t="s">
-        <v>379</v>
-      </c>
-      <c r="H10" t="s">
-        <v>413</v>
-      </c>
-      <c r="I10">
-        <v>1130</v>
-      </c>
-      <c r="J10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>415</v>
-      </c>
-      <c r="B11">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>408</v>
-      </c>
-      <c r="E11" t="s">
-        <v>409</v>
-      </c>
-      <c r="F11" t="s">
-        <v>378</v>
-      </c>
-      <c r="G11" t="s">
-        <v>388</v>
-      </c>
-      <c r="H11" t="s">
-        <v>416</v>
-      </c>
-      <c r="I11">
-        <v>760</v>
-      </c>
-      <c r="J11" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>418</v>
-      </c>
-      <c r="B12">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>419</v>
-      </c>
-      <c r="E12" t="s">
-        <v>420</v>
-      </c>
-      <c r="F12" t="s">
-        <v>421</v>
-      </c>
-      <c r="G12" t="s">
-        <v>422</v>
-      </c>
-      <c r="H12" t="s">
-        <v>423</v>
-      </c>
-      <c r="I12">
-        <v>2420</v>
-      </c>
-      <c r="J12" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>425</v>
-      </c>
-      <c r="B13">
-        <v>20</v>
-      </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>389</v>
-      </c>
-      <c r="E13" t="s">
-        <v>426</v>
-      </c>
-      <c r="F13" t="s">
-        <v>427</v>
-      </c>
-      <c r="G13" t="s">
-        <v>422</v>
-      </c>
-      <c r="H13" t="s">
-        <v>423</v>
-      </c>
-      <c r="I13">
-        <v>2960</v>
-      </c>
-      <c r="J13" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>429</v>
-      </c>
-      <c r="B14">
-        <v>25</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14" t="s">
-        <v>408</v>
-      </c>
-      <c r="E14" t="s">
-        <v>426</v>
-      </c>
-      <c r="F14" t="s">
-        <v>378</v>
-      </c>
-      <c r="G14" t="s">
-        <v>404</v>
-      </c>
-      <c r="H14" t="s">
-        <v>430</v>
-      </c>
-      <c r="I14">
-        <v>1650</v>
-      </c>
-      <c r="J14" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>432</v>
-      </c>
-      <c r="B15">
-        <v>25</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15" t="s">
-        <v>408</v>
-      </c>
-      <c r="E15" t="s">
-        <v>426</v>
-      </c>
-      <c r="F15" t="s">
-        <v>378</v>
-      </c>
-      <c r="G15" t="s">
-        <v>379</v>
-      </c>
-      <c r="H15" t="s">
-        <v>433</v>
-      </c>
-      <c r="I15">
-        <v>1260</v>
-      </c>
-      <c r="J15" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>435</v>
-      </c>
-      <c r="B16">
-        <v>25</v>
-      </c>
-      <c r="C16">
-        <v>5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>408</v>
-      </c>
-      <c r="E16" t="s">
-        <v>436</v>
-      </c>
-      <c r="F16" t="s">
-        <v>378</v>
-      </c>
-      <c r="G16" t="s">
-        <v>422</v>
-      </c>
-      <c r="H16" t="s">
-        <v>437</v>
-      </c>
-      <c r="I16">
-        <v>1980</v>
-      </c>
-      <c r="J16" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>439</v>
-      </c>
-      <c r="B17">
-        <v>25</v>
-      </c>
-      <c r="C17">
-        <v>5</v>
-      </c>
-      <c r="D17" t="s">
-        <v>408</v>
-      </c>
-      <c r="E17" t="s">
-        <v>436</v>
-      </c>
-      <c r="F17" t="s">
-        <v>378</v>
-      </c>
-      <c r="G17" t="s">
-        <v>379</v>
-      </c>
-      <c r="H17" t="s">
-        <v>440</v>
-      </c>
-      <c r="I17">
-        <v>1260</v>
-      </c>
-      <c r="J17" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>442</v>
-      </c>
-      <c r="B18">
-        <v>25</v>
-      </c>
-      <c r="C18">
-        <v>5</v>
-      </c>
-      <c r="D18" t="s">
-        <v>408</v>
-      </c>
-      <c r="E18" t="s">
-        <v>436</v>
-      </c>
-      <c r="F18" t="s">
-        <v>378</v>
-      </c>
-      <c r="G18" t="s">
-        <v>388</v>
-      </c>
-      <c r="H18" t="s">
-        <v>443</v>
-      </c>
-      <c r="I18">
-        <v>840</v>
-      </c>
-      <c r="J18" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>445</v>
-      </c>
-      <c r="B19">
-        <v>25</v>
-      </c>
-      <c r="C19">
-        <v>6</v>
-      </c>
-      <c r="D19" t="s">
-        <v>446</v>
-      </c>
-      <c r="E19" t="s">
-        <v>447</v>
-      </c>
-      <c r="F19" t="s">
-        <v>421</v>
-      </c>
-      <c r="G19" t="s">
-        <v>422</v>
-      </c>
-      <c r="H19" t="s">
-        <v>448</v>
-      </c>
-      <c r="I19">
-        <v>2720</v>
-      </c>
-      <c r="J19" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>450</v>
-      </c>
-      <c r="B20">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>6</v>
-      </c>
-      <c r="D20" t="s">
-        <v>446</v>
-      </c>
-      <c r="E20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F20" t="s">
-        <v>421</v>
-      </c>
-      <c r="G20" t="s">
-        <v>422</v>
-      </c>
-      <c r="H20" t="s">
-        <v>451</v>
-      </c>
-      <c r="I20">
-        <v>2710</v>
-      </c>
-      <c r="J20" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>453</v>
-      </c>
-      <c r="B21">
-        <v>25</v>
-      </c>
-      <c r="C21">
-        <v>6</v>
-      </c>
-      <c r="D21" t="s">
-        <v>446</v>
-      </c>
-      <c r="E21" t="s">
-        <v>447</v>
-      </c>
-      <c r="F21" t="s">
-        <v>421</v>
-      </c>
-      <c r="G21" t="s">
-        <v>404</v>
-      </c>
-      <c r="H21" t="s">
-        <v>454</v>
-      </c>
-      <c r="I21">
-        <v>2210</v>
-      </c>
-      <c r="J21" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>455</v>
-      </c>
-      <c r="B22">
-        <v>25</v>
-      </c>
-      <c r="C22">
-        <v>6</v>
-      </c>
-      <c r="D22" t="s">
-        <v>446</v>
-      </c>
-      <c r="E22" t="s">
-        <v>447</v>
-      </c>
-      <c r="F22" t="s">
-        <v>421</v>
-      </c>
-      <c r="G22" t="s">
-        <v>404</v>
-      </c>
-      <c r="H22" t="s">
-        <v>454</v>
-      </c>
-      <c r="I22">
-        <v>2200</v>
-      </c>
-      <c r="J22" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>457</v>
-      </c>
-      <c r="B23">
-        <v>25</v>
-      </c>
-      <c r="C23">
-        <v>6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>446</v>
-      </c>
-      <c r="E23" t="s">
-        <v>447</v>
-      </c>
-      <c r="F23" t="s">
-        <v>421</v>
-      </c>
-      <c r="G23" t="s">
-        <v>379</v>
-      </c>
-      <c r="H23" t="s">
-        <v>410</v>
-      </c>
-      <c r="I23">
-        <v>1670</v>
-      </c>
-      <c r="J23" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>439</v>
-      </c>
-      <c r="B24">
-        <v>25</v>
-      </c>
-      <c r="C24">
-        <v>6</v>
-      </c>
-      <c r="D24" t="s">
-        <v>446</v>
-      </c>
-      <c r="E24" t="s">
-        <v>447</v>
-      </c>
-      <c r="F24" t="s">
-        <v>421</v>
-      </c>
-      <c r="G24" t="s">
-        <v>379</v>
-      </c>
-      <c r="H24" t="s">
-        <v>410</v>
-      </c>
-      <c r="I24">
-        <v>1710</v>
-      </c>
-      <c r="J24" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>450</v>
-      </c>
-      <c r="B25">
-        <v>25</v>
-      </c>
-      <c r="C25">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>460</v>
-      </c>
-      <c r="E25" t="s">
-        <v>461</v>
-      </c>
-      <c r="F25" t="s">
-        <v>427</v>
-      </c>
-      <c r="G25" t="s">
-        <v>422</v>
-      </c>
-      <c r="H25" t="s">
-        <v>462</v>
-      </c>
-      <c r="I25">
-        <v>3480</v>
-      </c>
-      <c r="J25" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>464</v>
-      </c>
-      <c r="B26">
-        <v>28</v>
-      </c>
-      <c r="C26">
-        <v>6</v>
-      </c>
-      <c r="D26" t="s">
-        <v>465</v>
-      </c>
-      <c r="E26" t="s">
-        <v>466</v>
-      </c>
-      <c r="F26" t="s">
-        <v>421</v>
-      </c>
-      <c r="G26" t="s">
-        <v>422</v>
-      </c>
-      <c r="H26" t="s">
-        <v>467</v>
-      </c>
-      <c r="I26">
-        <v>2840</v>
-      </c>
-      <c r="J26" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>469</v>
-      </c>
-      <c r="B27">
-        <v>28</v>
-      </c>
-      <c r="C27">
-        <v>8</v>
-      </c>
-      <c r="D27" t="s">
-        <v>408</v>
-      </c>
-      <c r="E27" t="s">
-        <v>470</v>
-      </c>
-      <c r="F27" t="s">
-        <v>427</v>
-      </c>
-      <c r="G27" t="s">
-        <v>422</v>
-      </c>
-      <c r="H27" t="s">
-        <v>471</v>
-      </c>
-      <c r="I27">
-        <v>3690</v>
-      </c>
-      <c r="J27" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>473</v>
-      </c>
-      <c r="B28">
-        <v>28</v>
-      </c>
-      <c r="C28">
-        <v>8</v>
-      </c>
-      <c r="D28" t="s">
-        <v>408</v>
-      </c>
-      <c r="E28" t="s">
-        <v>470</v>
-      </c>
-      <c r="F28" t="s">
-        <v>427</v>
-      </c>
-      <c r="G28" t="s">
-        <v>422</v>
-      </c>
-      <c r="H28" t="s">
-        <v>474</v>
-      </c>
-      <c r="I28">
-        <v>3680</v>
-      </c>
-      <c r="J28" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>476</v>
-      </c>
-      <c r="B29">
-        <v>28</v>
-      </c>
-      <c r="C29">
-        <v>8</v>
-      </c>
-      <c r="D29" t="s">
-        <v>408</v>
-      </c>
-      <c r="E29" t="s">
-        <v>470</v>
-      </c>
-      <c r="F29" t="s">
-        <v>427</v>
-      </c>
-      <c r="G29" t="s">
-        <v>404</v>
-      </c>
-      <c r="H29" t="s">
-        <v>477</v>
-      </c>
-      <c r="I29">
-        <v>2970</v>
-      </c>
-      <c r="J29" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>479</v>
-      </c>
-      <c r="B30">
-        <v>32</v>
-      </c>
-      <c r="C30">
-        <v>5</v>
-      </c>
-      <c r="D30" t="s">
-        <v>480</v>
-      </c>
-      <c r="E30" t="s">
-        <v>481</v>
-      </c>
-      <c r="F30" t="s">
-        <v>378</v>
-      </c>
-      <c r="G30" t="s">
-        <v>404</v>
-      </c>
-      <c r="H30" t="s">
-        <v>423</v>
-      </c>
-      <c r="I30">
-        <v>1840</v>
-      </c>
-      <c r="J30" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>483</v>
-      </c>
-      <c r="B31">
-        <v>32</v>
-      </c>
-      <c r="C31">
-        <v>5</v>
-      </c>
-      <c r="D31" t="s">
-        <v>480</v>
-      </c>
-      <c r="E31" t="s">
-        <v>481</v>
-      </c>
-      <c r="F31" t="s">
-        <v>378</v>
-      </c>
-      <c r="G31" t="s">
-        <v>404</v>
-      </c>
-      <c r="H31" t="s">
-        <v>423</v>
-      </c>
-      <c r="I31">
-        <v>1840</v>
-      </c>
-      <c r="J31" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" t="s">
-        <v>485</v>
-      </c>
-      <c r="B32">
-        <v>32</v>
-      </c>
-      <c r="C32">
-        <v>6</v>
-      </c>
-      <c r="D32" t="s">
-        <v>446</v>
-      </c>
-      <c r="E32" t="s">
-        <v>486</v>
-      </c>
-      <c r="F32" t="s">
-        <v>421</v>
-      </c>
-      <c r="G32" t="s">
-        <v>422</v>
-      </c>
-      <c r="H32" t="s">
-        <v>487</v>
-      </c>
-      <c r="I32">
-        <v>3090</v>
-      </c>
-      <c r="J32" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>489</v>
-      </c>
-      <c r="B33">
-        <v>32</v>
-      </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
-      <c r="D33" t="s">
-        <v>446</v>
-      </c>
-      <c r="E33" t="s">
-        <v>486</v>
-      </c>
-      <c r="F33" t="s">
-        <v>421</v>
-      </c>
-      <c r="G33" t="s">
-        <v>422</v>
-      </c>
-      <c r="H33" t="s">
-        <v>490</v>
-      </c>
-      <c r="I33">
-        <v>3080</v>
-      </c>
-      <c r="J33" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>489</v>
-      </c>
-      <c r="B34">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>6</v>
-      </c>
-      <c r="D34" t="s">
-        <v>446</v>
-      </c>
-      <c r="E34" t="s">
-        <v>486</v>
-      </c>
-      <c r="F34" t="s">
-        <v>421</v>
-      </c>
-      <c r="G34" t="s">
-        <v>422</v>
-      </c>
-      <c r="H34" t="s">
-        <v>490</v>
-      </c>
-      <c r="I34">
-        <v>3080</v>
-      </c>
-      <c r="J34" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>493</v>
-      </c>
-      <c r="B35">
-        <v>32</v>
-      </c>
-      <c r="C35">
-        <v>6</v>
-      </c>
-      <c r="D35" t="s">
-        <v>446</v>
-      </c>
-      <c r="E35" t="s">
-        <v>486</v>
-      </c>
-      <c r="F35" t="s">
-        <v>421</v>
-      </c>
-      <c r="G35" t="s">
-        <v>422</v>
-      </c>
-      <c r="H35" t="s">
-        <v>494</v>
-      </c>
-      <c r="I35">
-        <v>3080</v>
-      </c>
-      <c r="J35" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>496</v>
-      </c>
-      <c r="B36">
-        <v>32</v>
-      </c>
-      <c r="C36">
-        <v>6</v>
-      </c>
-      <c r="D36" t="s">
-        <v>446</v>
-      </c>
-      <c r="E36" t="s">
-        <v>486</v>
-      </c>
-      <c r="F36" t="s">
-        <v>421</v>
-      </c>
-      <c r="G36" t="s">
-        <v>404</v>
-      </c>
-      <c r="H36" t="s">
-        <v>448</v>
-      </c>
-      <c r="I36">
-        <v>2500</v>
-      </c>
-      <c r="J36" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>498</v>
-      </c>
-      <c r="B37">
-        <v>32</v>
-      </c>
-      <c r="C37">
-        <v>6</v>
-      </c>
-      <c r="D37" t="s">
-        <v>446</v>
-      </c>
-      <c r="E37" t="s">
-        <v>486</v>
-      </c>
-      <c r="F37" t="s">
-        <v>421</v>
-      </c>
-      <c r="G37" t="s">
-        <v>379</v>
-      </c>
-      <c r="H37" t="s">
-        <v>499</v>
-      </c>
-      <c r="I37">
-        <v>1900</v>
-      </c>
-      <c r="J37" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" t="s">
-        <v>501</v>
-      </c>
-      <c r="B38">
-        <v>32</v>
-      </c>
-      <c r="C38">
-        <v>6</v>
-      </c>
-      <c r="D38" t="s">
-        <v>446</v>
-      </c>
-      <c r="E38" t="s">
-        <v>486</v>
-      </c>
-      <c r="F38" t="s">
-        <v>421</v>
-      </c>
-      <c r="G38" t="s">
-        <v>388</v>
-      </c>
-      <c r="H38" t="s">
-        <v>502</v>
-      </c>
-      <c r="I38">
-        <v>1280</v>
-      </c>
-      <c r="J38" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>504</v>
-      </c>
-      <c r="B39">
-        <v>32</v>
-      </c>
-      <c r="C39">
-        <v>6</v>
-      </c>
-      <c r="D39" t="s">
-        <v>446</v>
-      </c>
-      <c r="E39" t="s">
-        <v>486</v>
-      </c>
-      <c r="F39" t="s">
-        <v>421</v>
-      </c>
-      <c r="G39" t="s">
-        <v>388</v>
-      </c>
-      <c r="H39" t="s">
-        <v>413</v>
-      </c>
-      <c r="I39">
-        <v>1240</v>
-      </c>
-      <c r="J39" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>489</v>
-      </c>
-      <c r="B40">
-        <v>32</v>
-      </c>
-      <c r="C40">
-        <v>8</v>
-      </c>
-      <c r="D40" t="s">
-        <v>408</v>
-      </c>
-      <c r="E40" t="s">
-        <v>506</v>
-      </c>
-      <c r="F40" t="s">
-        <v>427</v>
-      </c>
-      <c r="G40" t="s">
-        <v>422</v>
-      </c>
-      <c r="H40" t="s">
-        <v>490</v>
-      </c>
-      <c r="I40">
-        <v>3860</v>
-      </c>
-      <c r="J40" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" t="s">
-        <v>493</v>
-      </c>
-      <c r="B41">
-        <v>32</v>
-      </c>
-      <c r="C41">
-        <v>8</v>
-      </c>
-      <c r="D41" t="s">
-        <v>408</v>
-      </c>
-      <c r="E41" t="s">
-        <v>506</v>
-      </c>
-      <c r="F41" t="s">
-        <v>427</v>
-      </c>
-      <c r="G41" t="s">
-        <v>422</v>
-      </c>
-      <c r="H41" t="s">
-        <v>494</v>
-      </c>
-      <c r="I41">
-        <v>3850</v>
-      </c>
-      <c r="J41" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" t="s">
-        <v>509</v>
-      </c>
-      <c r="B42">
-        <v>32</v>
-      </c>
-      <c r="C42">
-        <v>8</v>
-      </c>
-      <c r="D42" t="s">
-        <v>408</v>
-      </c>
-      <c r="E42" t="s">
-        <v>506</v>
-      </c>
-      <c r="F42" t="s">
-        <v>427</v>
-      </c>
-      <c r="G42" t="s">
-        <v>422</v>
-      </c>
-      <c r="H42" t="s">
-        <v>510</v>
-      </c>
-      <c r="I42">
-        <v>3840</v>
-      </c>
-      <c r="J42" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" t="s">
-        <v>512</v>
-      </c>
-      <c r="B43">
-        <v>32</v>
-      </c>
-      <c r="C43">
-        <v>8</v>
-      </c>
-      <c r="D43" t="s">
-        <v>408</v>
-      </c>
-      <c r="E43" t="s">
-        <v>506</v>
-      </c>
-      <c r="F43" t="s">
-        <v>427</v>
-      </c>
-      <c r="G43" t="s">
-        <v>404</v>
-      </c>
-      <c r="H43" t="s">
-        <v>513</v>
-      </c>
-      <c r="I43">
-        <v>3190</v>
-      </c>
-      <c r="J43" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" t="s">
-        <v>515</v>
-      </c>
-      <c r="B44">
-        <v>32</v>
-      </c>
-      <c r="C44">
-        <v>8</v>
-      </c>
-      <c r="D44" t="s">
-        <v>408</v>
-      </c>
-      <c r="E44" t="s">
-        <v>506</v>
-      </c>
-      <c r="F44" t="s">
-        <v>427</v>
-      </c>
-      <c r="G44" t="s">
-        <v>379</v>
-      </c>
-      <c r="H44" t="s">
-        <v>516</v>
-      </c>
-      <c r="I44">
-        <v>2420</v>
-      </c>
-      <c r="J44" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>501</v>
-      </c>
-      <c r="B45">
-        <v>32</v>
-      </c>
-      <c r="C45">
-        <v>8</v>
-      </c>
-      <c r="D45" t="s">
-        <v>408</v>
-      </c>
-      <c r="E45" t="s">
-        <v>506</v>
-      </c>
-      <c r="F45" t="s">
-        <v>427</v>
-      </c>
-      <c r="G45" t="s">
-        <v>388</v>
-      </c>
-      <c r="H45" t="s">
-        <v>502</v>
-      </c>
-      <c r="I45">
-        <v>1620</v>
-      </c>
-      <c r="J45" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" t="s">
-        <v>493</v>
-      </c>
-      <c r="B46">
-        <v>32</v>
-      </c>
-      <c r="C46">
-        <v>10</v>
-      </c>
-      <c r="D46" t="s">
-        <v>519</v>
-      </c>
-      <c r="E46" t="s">
-        <v>520</v>
-      </c>
-      <c r="F46" t="s">
-        <v>521</v>
-      </c>
-      <c r="G46" t="s">
-        <v>422</v>
-      </c>
-      <c r="H46" t="s">
-        <v>522</v>
-      </c>
-      <c r="I46">
-        <v>5640</v>
-      </c>
-      <c r="J46" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" t="s">
-        <v>509</v>
-      </c>
-      <c r="B47">
-        <v>32</v>
-      </c>
-      <c r="C47">
-        <v>10</v>
-      </c>
-      <c r="D47" t="s">
-        <v>519</v>
-      </c>
-      <c r="E47" t="s">
-        <v>520</v>
-      </c>
-      <c r="F47" t="s">
-        <v>521</v>
-      </c>
-      <c r="G47" t="s">
-        <v>422</v>
-      </c>
-      <c r="H47" t="s">
-        <v>522</v>
-      </c>
-      <c r="I47">
-        <v>5620</v>
-      </c>
-      <c r="J47" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" t="s">
-        <v>525</v>
-      </c>
-      <c r="B48">
-        <v>32</v>
-      </c>
-      <c r="C48">
-        <v>10</v>
-      </c>
-      <c r="D48" t="s">
-        <v>519</v>
-      </c>
-      <c r="E48" t="s">
-        <v>520</v>
-      </c>
-      <c r="F48" t="s">
-        <v>521</v>
-      </c>
-      <c r="G48" t="s">
-        <v>404</v>
-      </c>
-      <c r="H48" t="s">
-        <v>462</v>
-      </c>
-      <c r="I48">
-        <v>4570</v>
-      </c>
-      <c r="J48" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" t="s">
-        <v>512</v>
-      </c>
-      <c r="B49">
-        <v>32</v>
-      </c>
-      <c r="C49">
-        <v>10</v>
-      </c>
-      <c r="D49" t="s">
-        <v>519</v>
-      </c>
-      <c r="E49" t="s">
-        <v>520</v>
-      </c>
-      <c r="F49" t="s">
-        <v>521</v>
-      </c>
-      <c r="G49" t="s">
-        <v>404</v>
-      </c>
-      <c r="H49" t="s">
-        <v>527</v>
-      </c>
-      <c r="I49">
-        <v>4240</v>
-      </c>
-      <c r="J49" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>529</v>
-      </c>
-      <c r="B50">
-        <v>36</v>
-      </c>
-      <c r="C50">
-        <v>6</v>
-      </c>
-      <c r="D50" t="s">
-        <v>530</v>
-      </c>
-      <c r="E50" t="s">
-        <v>531</v>
-      </c>
-      <c r="F50" t="s">
-        <v>421</v>
-      </c>
-      <c r="G50" t="s">
-        <v>422</v>
-      </c>
-      <c r="H50" t="s">
-        <v>532</v>
-      </c>
-      <c r="I50">
-        <v>3240</v>
-      </c>
-      <c r="J50" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>534</v>
-      </c>
-      <c r="B51">
-        <v>36</v>
-      </c>
-      <c r="C51">
-        <v>10</v>
-      </c>
-      <c r="D51" t="s">
-        <v>519</v>
-      </c>
-      <c r="E51" t="s">
-        <v>535</v>
-      </c>
-      <c r="F51" t="s">
-        <v>521</v>
-      </c>
-      <c r="G51" t="s">
-        <v>422</v>
-      </c>
-      <c r="H51" t="s">
-        <v>536</v>
-      </c>
-      <c r="I51">
-        <v>6010</v>
-      </c>
-      <c r="J51" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" t="s">
-        <v>538</v>
-      </c>
-      <c r="B52">
-        <v>36</v>
-      </c>
-      <c r="C52">
-        <v>10</v>
-      </c>
-      <c r="D52" t="s">
-        <v>519</v>
-      </c>
-      <c r="E52" t="s">
-        <v>535</v>
-      </c>
-      <c r="F52" t="s">
-        <v>521</v>
-      </c>
-      <c r="G52" t="s">
-        <v>422</v>
-      </c>
-      <c r="H52" t="s">
-        <v>539</v>
-      </c>
-      <c r="I52">
-        <v>5990</v>
-      </c>
-      <c r="J52" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" t="s">
-        <v>541</v>
-      </c>
-      <c r="B53">
-        <v>36</v>
-      </c>
-      <c r="C53">
-        <v>10</v>
-      </c>
-      <c r="D53" t="s">
-        <v>519</v>
-      </c>
-      <c r="E53" t="s">
-        <v>535</v>
-      </c>
-      <c r="F53" t="s">
-        <v>521</v>
-      </c>
-      <c r="G53" t="s">
-        <v>422</v>
-      </c>
-      <c r="H53" t="s">
-        <v>542</v>
-      </c>
-      <c r="I53">
-        <v>5960</v>
-      </c>
-      <c r="J53" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" t="s">
-        <v>544</v>
-      </c>
-      <c r="B54">
-        <v>36</v>
-      </c>
-      <c r="C54">
-        <v>10</v>
-      </c>
-      <c r="D54" t="s">
-        <v>519</v>
-      </c>
-      <c r="E54" t="s">
-        <v>535</v>
-      </c>
-      <c r="F54" t="s">
-        <v>521</v>
-      </c>
-      <c r="G54" t="s">
-        <v>404</v>
-      </c>
-      <c r="H54" t="s">
-        <v>474</v>
-      </c>
-      <c r="I54">
-        <v>4840</v>
-      </c>
-      <c r="J54" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" t="s">
-        <v>544</v>
-      </c>
-      <c r="B55">
-        <v>36</v>
-      </c>
-      <c r="C55">
-        <v>10</v>
-      </c>
-      <c r="D55" t="s">
-        <v>519</v>
-      </c>
-      <c r="E55" t="s">
-        <v>535</v>
-      </c>
-      <c r="F55" t="s">
-        <v>521</v>
-      </c>
-      <c r="G55" t="s">
-        <v>404</v>
-      </c>
-      <c r="H55" t="s">
-        <v>474</v>
-      </c>
-      <c r="I55">
-        <v>4840</v>
-      </c>
-      <c r="J55" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" t="s">
-        <v>546</v>
-      </c>
-      <c r="B56">
-        <v>36</v>
-      </c>
-      <c r="C56">
-        <v>10</v>
-      </c>
-      <c r="D56" t="s">
-        <v>519</v>
-      </c>
-      <c r="E56" t="s">
-        <v>535</v>
-      </c>
-      <c r="F56" t="s">
-        <v>521</v>
-      </c>
-      <c r="G56" t="s">
-        <v>388</v>
-      </c>
-      <c r="H56" t="s">
-        <v>440</v>
-      </c>
-      <c r="I56">
-        <v>2540</v>
-      </c>
-      <c r="J56" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" t="s">
-        <v>548</v>
-      </c>
-      <c r="B57">
-        <v>38</v>
-      </c>
-      <c r="C57">
-        <v>8</v>
-      </c>
-      <c r="D57" t="s">
-        <v>549</v>
-      </c>
-      <c r="E57" t="s">
-        <v>550</v>
-      </c>
-      <c r="F57" t="s">
-        <v>427</v>
-      </c>
-      <c r="G57" t="s">
-        <v>422</v>
-      </c>
-      <c r="H57" t="s">
-        <v>551</v>
-      </c>
-      <c r="I57">
-        <v>4190</v>
-      </c>
-      <c r="J57" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" t="s">
-        <v>553</v>
-      </c>
-      <c r="B58">
-        <v>38</v>
-      </c>
-      <c r="C58">
-        <v>10</v>
-      </c>
-      <c r="D58" t="s">
-        <v>554</v>
-      </c>
-      <c r="E58" t="s">
-        <v>555</v>
-      </c>
-      <c r="F58" t="s">
-        <v>521</v>
-      </c>
-      <c r="G58" t="s">
-        <v>404</v>
-      </c>
-      <c r="H58" t="s">
-        <v>556</v>
-      </c>
-      <c r="I58">
-        <v>5050</v>
-      </c>
-      <c r="J58" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" t="s">
-        <v>558</v>
-      </c>
-      <c r="B59">
-        <v>38</v>
-      </c>
-      <c r="C59">
-        <v>10</v>
-      </c>
-      <c r="D59" t="s">
-        <v>554</v>
-      </c>
-      <c r="E59" t="s">
-        <v>555</v>
-      </c>
-      <c r="F59" t="s">
-        <v>521</v>
-      </c>
-      <c r="G59" t="s">
-        <v>404</v>
-      </c>
-      <c r="H59" t="s">
-        <v>559</v>
-      </c>
-      <c r="I59">
-        <v>5020</v>
-      </c>
-      <c r="J59" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" t="s">
-        <v>561</v>
-      </c>
-      <c r="B60">
-        <v>38</v>
-      </c>
-      <c r="C60">
-        <v>10</v>
-      </c>
-      <c r="D60" t="s">
-        <v>554</v>
-      </c>
-      <c r="E60" t="s">
-        <v>555</v>
-      </c>
-      <c r="F60" t="s">
-        <v>521</v>
-      </c>
-      <c r="G60" t="s">
-        <v>422</v>
-      </c>
-      <c r="H60" t="s">
-        <v>562</v>
-      </c>
-      <c r="I60">
-        <v>6140</v>
-      </c>
-      <c r="J60" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" t="s">
-        <v>564</v>
-      </c>
-      <c r="B61">
-        <v>38</v>
-      </c>
-      <c r="C61">
-        <v>10</v>
-      </c>
-      <c r="D61" t="s">
-        <v>554</v>
-      </c>
-      <c r="E61" t="s">
-        <v>555</v>
-      </c>
-      <c r="F61" t="s">
-        <v>521</v>
-      </c>
-      <c r="G61" t="s">
-        <v>404</v>
-      </c>
-      <c r="H61" t="s">
-        <v>565</v>
-      </c>
-      <c r="I61">
-        <v>4990</v>
-      </c>
-      <c r="J61" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" t="s">
-        <v>567</v>
-      </c>
-      <c r="B62">
-        <v>38</v>
-      </c>
-      <c r="C62">
-        <v>10</v>
-      </c>
-      <c r="D62" t="s">
-        <v>554</v>
-      </c>
-      <c r="E62" t="s">
-        <v>555</v>
-      </c>
-      <c r="F62" t="s">
-        <v>521</v>
-      </c>
-      <c r="G62" t="s">
-        <v>404</v>
-      </c>
-      <c r="H62" t="s">
-        <v>559</v>
-      </c>
-      <c r="I62">
-        <v>4940</v>
-      </c>
-      <c r="J62" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" t="s">
-        <v>569</v>
-      </c>
-      <c r="B63">
-        <v>38</v>
-      </c>
-      <c r="C63">
-        <v>10</v>
-      </c>
-      <c r="D63" t="s">
-        <v>554</v>
-      </c>
-      <c r="E63" t="s">
-        <v>555</v>
-      </c>
-      <c r="F63" t="s">
-        <v>521</v>
-      </c>
-      <c r="G63" t="s">
-        <v>388</v>
-      </c>
-      <c r="H63" t="s">
-        <v>570</v>
-      </c>
-      <c r="I63">
-        <v>2590</v>
-      </c>
-      <c r="J63" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" t="s">
-        <v>572</v>
-      </c>
-      <c r="B64">
-        <v>40</v>
-      </c>
-      <c r="C64">
-        <v>5</v>
-      </c>
-      <c r="D64" t="s">
-        <v>573</v>
-      </c>
-      <c r="E64" t="s">
-        <v>574</v>
-      </c>
-      <c r="F64" t="s">
-        <v>378</v>
-      </c>
-      <c r="G64" t="s">
-        <v>422</v>
-      </c>
-      <c r="H64" t="s">
-        <v>510</v>
-      </c>
-      <c r="I64">
-        <v>2470</v>
-      </c>
-      <c r="J64" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" t="s">
-        <v>576</v>
-      </c>
-      <c r="B65">
-        <v>40</v>
-      </c>
-      <c r="C65">
-        <v>6</v>
-      </c>
-      <c r="D65" t="s">
-        <v>577</v>
-      </c>
-      <c r="E65" t="s">
-        <v>578</v>
-      </c>
-      <c r="F65" t="s">
-        <v>421</v>
-      </c>
-      <c r="G65" t="s">
-        <v>422</v>
-      </c>
-      <c r="H65" t="s">
-        <v>551</v>
-      </c>
-      <c r="I65">
-        <v>3370</v>
-      </c>
-      <c r="J65" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66" t="s">
-        <v>580</v>
-      </c>
-      <c r="B66">
-        <v>40</v>
-      </c>
-      <c r="C66">
-        <v>8</v>
-      </c>
-      <c r="D66" t="s">
-        <v>581</v>
-      </c>
-      <c r="E66" t="s">
-        <v>582</v>
-      </c>
-      <c r="F66" t="s">
-        <v>427</v>
-      </c>
-      <c r="G66" t="s">
-        <v>422</v>
-      </c>
-      <c r="H66" t="s">
-        <v>583</v>
-      </c>
-      <c r="I66">
-        <v>4360</v>
-      </c>
-      <c r="J66" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>585</v>
-      </c>
-      <c r="B67">
-        <v>40</v>
-      </c>
-      <c r="C67">
-        <v>10</v>
-      </c>
-      <c r="D67" t="s">
-        <v>581</v>
-      </c>
-      <c r="E67" t="s">
-        <v>582</v>
-      </c>
-      <c r="F67" t="s">
-        <v>427</v>
-      </c>
-      <c r="G67" t="s">
-        <v>422</v>
-      </c>
-      <c r="H67" t="s">
-        <v>586</v>
-      </c>
-      <c r="I67">
-        <v>4350</v>
-      </c>
-      <c r="J67" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>588</v>
-      </c>
-      <c r="B68">
-        <v>40</v>
-      </c>
-      <c r="C68">
-        <v>20</v>
-      </c>
-      <c r="D68" t="s">
-        <v>581</v>
-      </c>
-      <c r="E68" t="s">
-        <v>582</v>
-      </c>
-      <c r="F68" t="s">
-        <v>427</v>
-      </c>
-      <c r="G68" t="s">
-        <v>404</v>
-      </c>
-      <c r="H68" t="s">
-        <v>522</v>
-      </c>
-      <c r="I68">
-        <v>4300</v>
-      </c>
-      <c r="J68" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" t="s">
-        <v>590</v>
-      </c>
-      <c r="B69">
-        <v>40</v>
-      </c>
-      <c r="C69">
-        <v>16</v>
-      </c>
-      <c r="D69" t="s">
-        <v>591</v>
-      </c>
-      <c r="E69" t="s">
-        <v>592</v>
-      </c>
-      <c r="F69" t="s">
-        <v>593</v>
-      </c>
-      <c r="G69" t="s">
-        <v>422</v>
-      </c>
-      <c r="H69" t="s">
-        <v>594</v>
-      </c>
-      <c r="I69">
-        <v>5170</v>
-      </c>
-      <c r="J69" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" t="s">
-        <v>585</v>
-      </c>
-      <c r="B70">
-        <v>40</v>
-      </c>
-      <c r="C70">
-        <v>10</v>
-      </c>
-      <c r="D70" t="s">
-        <v>596</v>
-      </c>
-      <c r="E70" t="s">
-        <v>597</v>
-      </c>
-      <c r="F70" t="s">
-        <v>521</v>
-      </c>
-      <c r="G70" t="s">
-        <v>422</v>
-      </c>
-      <c r="H70" t="s">
-        <v>594</v>
-      </c>
-      <c r="I70">
-        <v>6340</v>
-      </c>
-      <c r="J70" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" t="s">
-        <v>599</v>
-      </c>
-      <c r="B71">
-        <v>40</v>
-      </c>
-      <c r="C71">
-        <v>12</v>
-      </c>
-      <c r="D71" t="s">
-        <v>596</v>
-      </c>
-      <c r="E71" t="s">
-        <v>597</v>
-      </c>
-      <c r="F71" t="s">
-        <v>521</v>
-      </c>
-      <c r="G71" t="s">
-        <v>422</v>
-      </c>
-      <c r="H71" t="s">
-        <v>600</v>
-      </c>
-      <c r="I71">
-        <v>6330</v>
-      </c>
-      <c r="J71" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" t="s">
-        <v>590</v>
-      </c>
-      <c r="B72">
-        <v>40</v>
-      </c>
-      <c r="C72">
-        <v>16</v>
-      </c>
-      <c r="D72" t="s">
-        <v>596</v>
-      </c>
-      <c r="E72" t="s">
-        <v>597</v>
-      </c>
-      <c r="F72" t="s">
-        <v>521</v>
-      </c>
-      <c r="G72" t="s">
-        <v>422</v>
-      </c>
-      <c r="H72" t="s">
-        <v>602</v>
-      </c>
-      <c r="I72">
-        <v>6300</v>
-      </c>
-      <c r="J72" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" t="s">
-        <v>588</v>
-      </c>
-      <c r="B73">
-        <v>40</v>
-      </c>
-      <c r="C73">
-        <v>20</v>
-      </c>
-      <c r="D73" t="s">
-        <v>596</v>
-      </c>
-      <c r="E73" t="s">
-        <v>597</v>
-      </c>
-      <c r="F73" t="s">
-        <v>521</v>
-      </c>
-      <c r="G73" t="s">
-        <v>404</v>
-      </c>
-      <c r="H73" t="s">
-        <v>604</v>
-      </c>
-      <c r="I73">
-        <v>5130</v>
-      </c>
-      <c r="J73" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" t="s">
-        <v>606</v>
-      </c>
-      <c r="B74">
-        <v>40</v>
-      </c>
-      <c r="C74">
-        <v>30</v>
-      </c>
-      <c r="D74" t="s">
-        <v>596</v>
-      </c>
-      <c r="E74" t="s">
-        <v>597</v>
-      </c>
-      <c r="F74" t="s">
-        <v>521</v>
-      </c>
-      <c r="G74" t="s">
-        <v>379</v>
-      </c>
-      <c r="H74" t="s">
-        <v>607</v>
-      </c>
-      <c r="I74">
-        <v>4000</v>
-      </c>
-      <c r="J74" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" t="s">
-        <v>609</v>
-      </c>
-      <c r="B75">
-        <v>40</v>
-      </c>
-      <c r="C75">
-        <v>25</v>
-      </c>
-      <c r="D75" t="s">
-        <v>596</v>
-      </c>
-      <c r="E75" t="s">
-        <v>597</v>
-      </c>
-      <c r="F75" t="s">
-        <v>521</v>
-      </c>
-      <c r="G75" t="s">
-        <v>404</v>
-      </c>
-      <c r="H75" t="s">
-        <v>510</v>
-      </c>
-      <c r="I75">
-        <v>5080</v>
-      </c>
-      <c r="J75" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" t="s">
-        <v>611</v>
-      </c>
-      <c r="B76">
-        <v>40</v>
-      </c>
-      <c r="C76">
-        <v>40</v>
-      </c>
-      <c r="D76" t="s">
-        <v>596</v>
-      </c>
-      <c r="E76" t="s">
-        <v>597</v>
-      </c>
-      <c r="F76" t="s">
-        <v>521</v>
-      </c>
-      <c r="G76" t="s">
-        <v>388</v>
-      </c>
-      <c r="H76" t="s">
-        <v>612</v>
-      </c>
-      <c r="I76">
-        <v>2660</v>
-      </c>
-      <c r="J76" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
-      <c r="A77" t="s">
-        <v>599</v>
-      </c>
-      <c r="B77">
-        <v>40</v>
-      </c>
-      <c r="C77">
-        <v>12</v>
-      </c>
-      <c r="D77" t="s">
-        <v>614</v>
-      </c>
-      <c r="E77" t="s">
-        <v>615</v>
-      </c>
-      <c r="F77" t="s">
-        <v>616</v>
-      </c>
-      <c r="G77" t="s">
-        <v>422</v>
-      </c>
-      <c r="H77" t="s">
-        <v>617</v>
-      </c>
-      <c r="I77">
-        <v>7430</v>
-      </c>
-      <c r="J77" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
-      <c r="A78" t="s">
-        <v>590</v>
-      </c>
-      <c r="B78">
-        <v>40</v>
-      </c>
-      <c r="C78">
-        <v>16</v>
-      </c>
-      <c r="D78" t="s">
-        <v>614</v>
-      </c>
-      <c r="E78" t="s">
-        <v>615</v>
-      </c>
-      <c r="F78" t="s">
-        <v>616</v>
-      </c>
-      <c r="G78" t="s">
-        <v>422</v>
-      </c>
-      <c r="H78" t="s">
-        <v>619</v>
-      </c>
-      <c r="I78">
-        <v>7400</v>
-      </c>
-      <c r="J78" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
-      <c r="A79" t="s">
-        <v>621</v>
-      </c>
-      <c r="B79">
-        <v>45</v>
-      </c>
-      <c r="C79">
-        <v>8</v>
-      </c>
-      <c r="D79" t="s">
-        <v>622</v>
-      </c>
-      <c r="E79" t="s">
-        <v>623</v>
-      </c>
-      <c r="F79" t="s">
-        <v>427</v>
-      </c>
-      <c r="G79" t="s">
-        <v>422</v>
-      </c>
-      <c r="H79" t="s">
-        <v>624</v>
-      </c>
-      <c r="I79">
-        <v>4550</v>
-      </c>
-      <c r="J79" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" t="s">
-        <v>626</v>
-      </c>
-      <c r="B80">
-        <v>45</v>
-      </c>
-      <c r="C80">
-        <v>10</v>
-      </c>
-      <c r="D80" t="s">
-        <v>627</v>
-      </c>
-      <c r="E80" t="s">
-        <v>628</v>
-      </c>
-      <c r="F80" t="s">
-        <v>521</v>
-      </c>
-      <c r="G80" t="s">
-        <v>422</v>
-      </c>
-      <c r="H80" t="s">
-        <v>629</v>
-      </c>
-      <c r="I80">
-        <v>6810</v>
-      </c>
-      <c r="J80" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
-      <c r="A81" t="s">
-        <v>631</v>
-      </c>
-      <c r="B81">
-        <v>45</v>
-      </c>
-      <c r="C81">
-        <v>12</v>
-      </c>
-      <c r="D81" t="s">
-        <v>627</v>
-      </c>
-      <c r="E81" t="s">
-        <v>628</v>
-      </c>
-      <c r="F81" t="s">
-        <v>521</v>
-      </c>
-      <c r="G81" t="s">
-        <v>422</v>
-      </c>
-      <c r="H81" t="s">
-        <v>632</v>
-      </c>
-      <c r="I81">
-        <v>6800</v>
-      </c>
-      <c r="J81" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
-      <c r="A82" t="s">
-        <v>634</v>
-      </c>
-      <c r="B82">
-        <v>45</v>
-      </c>
-      <c r="C82">
-        <v>16</v>
-      </c>
-      <c r="D82" t="s">
-        <v>627</v>
-      </c>
-      <c r="E82" t="s">
-        <v>628</v>
-      </c>
-      <c r="F82" t="s">
-        <v>521</v>
-      </c>
-      <c r="G82" t="s">
-        <v>422</v>
-      </c>
-      <c r="H82" t="s">
-        <v>635</v>
-      </c>
-      <c r="I82">
-        <v>6780</v>
-      </c>
-      <c r="J82" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
-      <c r="A83" t="s">
-        <v>637</v>
-      </c>
-      <c r="B83">
-        <v>45</v>
-      </c>
-      <c r="C83">
-        <v>20</v>
-      </c>
-      <c r="D83" t="s">
-        <v>627</v>
-      </c>
-      <c r="E83" t="s">
-        <v>628</v>
-      </c>
-      <c r="F83" t="s">
-        <v>521</v>
-      </c>
-      <c r="G83" t="s">
-        <v>404</v>
-      </c>
-      <c r="H83" t="s">
-        <v>638</v>
-      </c>
-      <c r="I83">
-        <v>5520</v>
-      </c>
-      <c r="J83" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
-      <c r="A84" t="s">
-        <v>640</v>
-      </c>
-      <c r="B84">
-        <v>45</v>
-      </c>
-      <c r="C84">
-        <v>25</v>
-      </c>
-      <c r="D84" t="s">
-        <v>627</v>
-      </c>
-      <c r="E84" t="s">
-        <v>628</v>
-      </c>
-      <c r="F84" t="s">
-        <v>521</v>
-      </c>
-      <c r="G84" t="s">
-        <v>404</v>
-      </c>
-      <c r="H84" t="s">
-        <v>638</v>
-      </c>
-      <c r="I84">
-        <v>5480</v>
-      </c>
-      <c r="J84" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
-      <c r="A85" t="s">
-        <v>642</v>
-      </c>
-      <c r="B85">
-        <v>45</v>
-      </c>
-      <c r="C85">
-        <v>40</v>
-      </c>
-      <c r="D85" t="s">
-        <v>627</v>
-      </c>
-      <c r="E85" t="s">
-        <v>628</v>
-      </c>
-      <c r="F85" t="s">
-        <v>521</v>
-      </c>
-      <c r="G85" t="s">
-        <v>379</v>
-      </c>
-      <c r="H85" t="s">
-        <v>467</v>
-      </c>
-      <c r="I85">
-        <v>4100</v>
-      </c>
-      <c r="J85" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
-      <c r="A86" t="s">
-        <v>631</v>
-      </c>
-      <c r="B86">
-        <v>45</v>
-      </c>
-      <c r="C86">
-        <v>12</v>
-      </c>
-      <c r="D86" t="s">
-        <v>644</v>
-      </c>
-      <c r="E86" t="s">
-        <v>628</v>
-      </c>
-      <c r="F86" t="s">
-        <v>616</v>
-      </c>
-      <c r="G86" t="s">
-        <v>422</v>
-      </c>
-      <c r="H86" t="s">
-        <v>645</v>
-      </c>
-      <c r="I86">
-        <v>7830</v>
-      </c>
-      <c r="J86" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
-      <c r="A87" t="s">
-        <v>634</v>
-      </c>
-      <c r="B87">
-        <v>45</v>
-      </c>
-      <c r="C87">
-        <v>16</v>
-      </c>
-      <c r="D87" t="s">
-        <v>644</v>
-      </c>
-      <c r="E87" t="s">
-        <v>647</v>
-      </c>
-      <c r="F87" t="s">
-        <v>616</v>
-      </c>
-      <c r="G87" t="s">
-        <v>422</v>
-      </c>
-      <c r="H87" t="s">
-        <v>648</v>
-      </c>
-      <c r="I87">
-        <v>7810</v>
-      </c>
-      <c r="J87" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
-      <c r="A88" t="s">
-        <v>637</v>
-      </c>
-      <c r="B88">
-        <v>45</v>
-      </c>
-      <c r="C88">
-        <v>20</v>
-      </c>
-      <c r="D88" t="s">
-        <v>644</v>
-      </c>
-      <c r="E88" t="s">
-        <v>647</v>
-      </c>
-      <c r="F88" t="s">
-        <v>616</v>
-      </c>
-      <c r="G88" t="s">
-        <v>404</v>
-      </c>
-      <c r="H88" t="s">
-        <v>650</v>
-      </c>
-      <c r="I88">
-        <v>6360</v>
-      </c>
-      <c r="J88" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
-      <c r="A89" t="s">
-        <v>652</v>
-      </c>
-      <c r="B89">
-        <v>50</v>
-      </c>
-      <c r="C89">
-        <v>5</v>
-      </c>
-      <c r="D89" t="s">
-        <v>653</v>
-      </c>
-      <c r="E89" t="s">
-        <v>654</v>
-      </c>
-      <c r="F89" t="s">
-        <v>378</v>
-      </c>
-      <c r="G89" t="s">
-        <v>422</v>
-      </c>
-      <c r="H89" t="s">
-        <v>638</v>
-      </c>
-      <c r="I89">
-        <v>2700</v>
-      </c>
-      <c r="J89" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" t="s">
-        <v>656</v>
-      </c>
-      <c r="B90">
-        <v>50</v>
-      </c>
-      <c r="C90">
-        <v>8</v>
-      </c>
-      <c r="D90" t="s">
-        <v>440</v>
-      </c>
-      <c r="E90" t="s">
-        <v>657</v>
-      </c>
-      <c r="F90" t="s">
-        <v>427</v>
-      </c>
-      <c r="G90" t="s">
-        <v>422</v>
-      </c>
-      <c r="H90" t="s">
-        <v>658</v>
-      </c>
-      <c r="I90">
-        <v>4730</v>
-      </c>
-      <c r="J90" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
-      <c r="A91" t="s">
-        <v>660</v>
-      </c>
-      <c r="B91">
-        <v>50</v>
-      </c>
-      <c r="C91">
-        <v>10</v>
-      </c>
-      <c r="D91" t="s">
-        <v>661</v>
-      </c>
-      <c r="E91" t="s">
-        <v>662</v>
-      </c>
-      <c r="F91" t="s">
-        <v>521</v>
-      </c>
-      <c r="G91" t="s">
-        <v>422</v>
-      </c>
-      <c r="H91" t="s">
-        <v>663</v>
-      </c>
-      <c r="I91">
-        <v>7050</v>
-      </c>
-      <c r="J91" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
-      <c r="A92" t="s">
-        <v>665</v>
-      </c>
-      <c r="B92">
-        <v>50</v>
-      </c>
-      <c r="C92">
-        <v>12</v>
-      </c>
-      <c r="D92" t="s">
-        <v>661</v>
-      </c>
-      <c r="E92" t="s">
-        <v>662</v>
-      </c>
-      <c r="F92" t="s">
-        <v>521</v>
-      </c>
-      <c r="G92" t="s">
-        <v>422</v>
-      </c>
-      <c r="H92" t="s">
-        <v>666</v>
-      </c>
-      <c r="I92">
-        <v>7040</v>
-      </c>
-      <c r="J92" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
-      <c r="A93" t="s">
-        <v>668</v>
-      </c>
-      <c r="B93">
-        <v>50</v>
-      </c>
-      <c r="C93">
-        <v>15</v>
-      </c>
-      <c r="D93" t="s">
-        <v>661</v>
-      </c>
-      <c r="E93" t="s">
-        <v>662</v>
-      </c>
-      <c r="F93" t="s">
-        <v>521</v>
-      </c>
-      <c r="G93" t="s">
-        <v>422</v>
-      </c>
-      <c r="H93" t="s">
-        <v>669</v>
-      </c>
-      <c r="I93">
-        <v>7030</v>
-      </c>
-      <c r="J93" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
-      <c r="A94" t="s">
-        <v>671</v>
-      </c>
-      <c r="B94">
-        <v>50</v>
-      </c>
-      <c r="C94">
-        <v>16</v>
-      </c>
-      <c r="D94" t="s">
-        <v>661</v>
-      </c>
-      <c r="E94" t="s">
-        <v>662</v>
-      </c>
-      <c r="F94" t="s">
-        <v>521</v>
-      </c>
-      <c r="G94" t="s">
-        <v>422</v>
-      </c>
-      <c r="H94" t="s">
-        <v>669</v>
-      </c>
-      <c r="I94">
-        <v>7020</v>
-      </c>
-      <c r="J94" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
-      <c r="A95" t="s">
-        <v>672</v>
-      </c>
-      <c r="B95">
-        <v>50</v>
-      </c>
-      <c r="C95">
-        <v>20</v>
-      </c>
-      <c r="D95" t="s">
-        <v>661</v>
-      </c>
-      <c r="E95" t="s">
-        <v>662</v>
-      </c>
-      <c r="F95" t="s">
-        <v>521</v>
-      </c>
-      <c r="G95" t="s">
-        <v>404</v>
-      </c>
-      <c r="H95" t="s">
-        <v>673</v>
-      </c>
-      <c r="I95">
-        <v>5720</v>
-      </c>
-      <c r="J95" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
-      <c r="A96" t="s">
-        <v>675</v>
-      </c>
-      <c r="B96">
-        <v>50</v>
-      </c>
-      <c r="C96">
-        <v>25</v>
-      </c>
-      <c r="D96" t="s">
-        <v>661</v>
-      </c>
-      <c r="E96" t="s">
-        <v>662</v>
-      </c>
-      <c r="F96" t="s">
-        <v>521</v>
-      </c>
-      <c r="G96" t="s">
-        <v>404</v>
-      </c>
-      <c r="H96" t="s">
-        <v>676</v>
-      </c>
-      <c r="I96">
-        <v>5690</v>
-      </c>
-      <c r="J96" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
-      <c r="A97" t="s">
-        <v>678</v>
-      </c>
-      <c r="B97">
-        <v>50</v>
-      </c>
-      <c r="C97">
-        <v>30</v>
-      </c>
-      <c r="D97" t="s">
-        <v>661</v>
-      </c>
-      <c r="E97" t="s">
-        <v>662</v>
-      </c>
-      <c r="F97" t="s">
-        <v>521</v>
-      </c>
-      <c r="G97" t="s">
-        <v>404</v>
-      </c>
-      <c r="H97" t="s">
-        <v>586</v>
-      </c>
-      <c r="I97">
-        <v>5650</v>
-      </c>
-      <c r="J97" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
-      <c r="A98" t="s">
-        <v>680</v>
-      </c>
-      <c r="B98">
-        <v>50</v>
-      </c>
-      <c r="C98">
-        <v>35</v>
-      </c>
-      <c r="D98" t="s">
-        <v>661</v>
-      </c>
-      <c r="E98" t="s">
-        <v>662</v>
-      </c>
-      <c r="F98" t="s">
-        <v>521</v>
-      </c>
-      <c r="G98" t="s">
-        <v>379</v>
-      </c>
-      <c r="H98" t="s">
-        <v>474</v>
-      </c>
-      <c r="I98">
-        <v>4430</v>
-      </c>
-      <c r="J98" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
-      <c r="A99" t="s">
-        <v>682</v>
-      </c>
-      <c r="B99">
-        <v>50</v>
-      </c>
-      <c r="C99">
-        <v>40</v>
-      </c>
-      <c r="D99" t="s">
-        <v>661</v>
-      </c>
-      <c r="E99" t="s">
-        <v>662</v>
-      </c>
-      <c r="F99" t="s">
-        <v>521</v>
-      </c>
-      <c r="G99" t="s">
-        <v>379</v>
-      </c>
-      <c r="H99" t="s">
-        <v>471</v>
-      </c>
-      <c r="I99">
-        <v>4390</v>
-      </c>
-      <c r="J99" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
-      <c r="A100" t="s">
-        <v>684</v>
-      </c>
-      <c r="B100">
-        <v>50</v>
-      </c>
-      <c r="C100">
-        <v>30</v>
-      </c>
-      <c r="D100" t="s">
-        <v>685</v>
-      </c>
-      <c r="E100" t="s">
-        <v>686</v>
-      </c>
-      <c r="F100" t="s">
-        <v>616</v>
-      </c>
-      <c r="G100" t="s">
-        <v>388</v>
-      </c>
-      <c r="H100" t="s">
-        <v>516</v>
-      </c>
-      <c r="I100">
-        <v>3560</v>
-      </c>
-      <c r="J100" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
-      <c r="A101" t="s">
-        <v>665</v>
-      </c>
-      <c r="B101">
-        <v>50</v>
-      </c>
-      <c r="C101">
-        <v>12</v>
-      </c>
-      <c r="D101" t="s">
-        <v>688</v>
-      </c>
-      <c r="E101" t="s">
-        <v>689</v>
-      </c>
-      <c r="F101" t="s">
-        <v>690</v>
-      </c>
-      <c r="G101" t="s">
-        <v>422</v>
-      </c>
-      <c r="H101" t="s">
-        <v>691</v>
-      </c>
-      <c r="I101">
-        <v>9480</v>
-      </c>
-      <c r="J101" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
-      <c r="A102" t="s">
-        <v>671</v>
-      </c>
-      <c r="B102">
-        <v>50</v>
-      </c>
-      <c r="C102">
-        <v>16</v>
-      </c>
-      <c r="D102" t="s">
-        <v>688</v>
-      </c>
-      <c r="E102" t="s">
-        <v>689</v>
-      </c>
-      <c r="F102" t="s">
-        <v>690</v>
-      </c>
-      <c r="G102" t="s">
-        <v>422</v>
-      </c>
-      <c r="H102" t="s">
-        <v>693</v>
-      </c>
-      <c r="I102">
-        <v>9450</v>
-      </c>
-      <c r="J102" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" t="s">
-        <v>695</v>
-      </c>
-      <c r="B103">
-        <v>50</v>
-      </c>
-      <c r="C103">
-        <v>20</v>
-      </c>
-      <c r="D103" t="s">
-        <v>688</v>
-      </c>
-      <c r="E103" t="s">
-        <v>689</v>
-      </c>
-      <c r="F103" t="s">
-        <v>690</v>
-      </c>
-      <c r="G103" t="s">
-        <v>422</v>
-      </c>
-      <c r="H103" t="s">
-        <v>696</v>
-      </c>
-      <c r="I103">
-        <v>9420</v>
-      </c>
-      <c r="J103" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" t="s">
-        <v>698</v>
-      </c>
-      <c r="B104">
-        <v>50</v>
-      </c>
-      <c r="C104">
-        <v>50</v>
-      </c>
-      <c r="D104" t="s">
-        <v>688</v>
-      </c>
-      <c r="E104" t="s">
-        <v>689</v>
-      </c>
-      <c r="F104" t="s">
-        <v>690</v>
-      </c>
-      <c r="G104" t="s">
-        <v>388</v>
-      </c>
-      <c r="H104" t="s">
-        <v>699</v>
-      </c>
-      <c r="I104">
-        <v>3980</v>
-      </c>
-      <c r="J104" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" t="s">
-        <v>672</v>
-      </c>
-      <c r="B105">
-        <v>50</v>
-      </c>
-      <c r="C105">
-        <v>20</v>
-      </c>
-      <c r="D105" t="s">
-        <v>701</v>
-      </c>
-      <c r="E105" t="s">
-        <v>702</v>
-      </c>
-      <c r="F105" t="s">
-        <v>703</v>
-      </c>
-      <c r="G105" t="s">
-        <v>404</v>
-      </c>
-      <c r="H105" t="s">
-        <v>704</v>
-      </c>
-      <c r="I105">
-        <v>9870</v>
-      </c>
-      <c r="J105" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
-      <c r="A106" t="s">
-        <v>706</v>
-      </c>
-      <c r="B106">
-        <v>55</v>
-      </c>
-      <c r="C106">
-        <v>16</v>
-      </c>
-      <c r="D106" t="s">
-        <v>707</v>
-      </c>
-      <c r="E106" t="s">
-        <v>708</v>
-      </c>
-      <c r="F106" t="s">
-        <v>521</v>
-      </c>
-      <c r="G106" t="s">
-        <v>422</v>
-      </c>
-      <c r="H106" t="s">
-        <v>709</v>
-      </c>
-      <c r="I106">
-        <v>7420</v>
-      </c>
-      <c r="J106" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
-      <c r="A107" t="s">
-        <v>711</v>
-      </c>
-      <c r="B107">
-        <v>63</v>
-      </c>
-      <c r="C107">
-        <v>10</v>
-      </c>
-      <c r="D107" t="s">
-        <v>712</v>
-      </c>
-      <c r="E107" t="s">
-        <v>713</v>
-      </c>
-      <c r="F107" t="s">
-        <v>521</v>
-      </c>
-      <c r="G107" t="s">
-        <v>422</v>
-      </c>
-      <c r="H107" t="s">
-        <v>714</v>
-      </c>
-      <c r="I107">
-        <v>7720</v>
-      </c>
-      <c r="J107" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" t="s">
-        <v>716</v>
-      </c>
-      <c r="B108">
-        <v>63</v>
-      </c>
-      <c r="C108">
-        <v>12</v>
-      </c>
-      <c r="D108" t="s">
-        <v>712</v>
-      </c>
-      <c r="E108" t="s">
-        <v>713</v>
-      </c>
-      <c r="F108" t="s">
-        <v>521</v>
-      </c>
-      <c r="G108" t="s">
-        <v>422</v>
-      </c>
-      <c r="H108" t="s">
-        <v>717</v>
-      </c>
-      <c r="I108">
-        <v>7720</v>
-      </c>
-      <c r="J108" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" t="s">
-        <v>719</v>
-      </c>
-      <c r="B109">
-        <v>63</v>
-      </c>
-      <c r="C109">
-        <v>20</v>
-      </c>
-      <c r="D109" t="s">
-        <v>712</v>
-      </c>
-      <c r="E109" t="s">
-        <v>713</v>
-      </c>
-      <c r="F109" t="s">
-        <v>521</v>
-      </c>
-      <c r="G109" t="s">
-        <v>422</v>
-      </c>
-      <c r="H109" t="s">
-        <v>720</v>
-      </c>
-      <c r="I109">
-        <v>7850</v>
-      </c>
-      <c r="J109" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" t="s">
-        <v>722</v>
-      </c>
-      <c r="B110">
-        <v>63</v>
-      </c>
-      <c r="C110">
-        <v>40</v>
-      </c>
-      <c r="D110" t="s">
-        <v>712</v>
-      </c>
-      <c r="E110" t="s">
-        <v>713</v>
-      </c>
-      <c r="F110" t="s">
-        <v>521</v>
-      </c>
-      <c r="G110" t="s">
-        <v>388</v>
-      </c>
-      <c r="H110" t="s">
-        <v>723</v>
-      </c>
-      <c r="I110">
-        <v>3310</v>
-      </c>
-      <c r="J110" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
-      <c r="A111" t="s">
-        <v>716</v>
-      </c>
-      <c r="B111">
-        <v>63</v>
-      </c>
-      <c r="C111">
-        <v>12</v>
-      </c>
-      <c r="D111" t="s">
-        <v>725</v>
-      </c>
-      <c r="E111" t="s">
-        <v>726</v>
-      </c>
-      <c r="F111" t="s">
-        <v>690</v>
-      </c>
-      <c r="G111" t="s">
-        <v>422</v>
-      </c>
-      <c r="H111" t="s">
-        <v>727</v>
-      </c>
-      <c r="I111">
-        <v>10520</v>
-      </c>
-      <c r="J111" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" t="s">
-        <v>729</v>
-      </c>
-      <c r="B112">
-        <v>63</v>
-      </c>
-      <c r="C112">
-        <v>16</v>
-      </c>
-      <c r="D112" t="s">
-        <v>730</v>
-      </c>
-      <c r="E112" t="s">
-        <v>731</v>
-      </c>
-      <c r="F112" t="s">
-        <v>703</v>
-      </c>
-      <c r="G112" t="s">
-        <v>404</v>
-      </c>
-      <c r="H112" t="s">
-        <v>693</v>
-      </c>
-      <c r="I112">
-        <v>11010</v>
-      </c>
-      <c r="J112" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" t="s">
-        <v>719</v>
-      </c>
-      <c r="B113">
-        <v>63</v>
-      </c>
-      <c r="C113">
-        <v>20</v>
-      </c>
-      <c r="D113" t="s">
-        <v>730</v>
-      </c>
-      <c r="E113" t="s">
-        <v>731</v>
-      </c>
-      <c r="F113" t="s">
-        <v>703</v>
-      </c>
-      <c r="G113" t="s">
-        <v>422</v>
-      </c>
-      <c r="H113" t="s">
-        <v>733</v>
-      </c>
-      <c r="I113">
-        <v>13430</v>
-      </c>
-      <c r="J113" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" t="s">
-        <v>735</v>
-      </c>
-      <c r="B114">
-        <v>63</v>
-      </c>
-      <c r="C114">
-        <v>25</v>
-      </c>
-      <c r="D114" t="s">
-        <v>730</v>
-      </c>
-      <c r="E114" t="s">
-        <v>731</v>
-      </c>
-      <c r="F114" t="s">
-        <v>703</v>
-      </c>
-      <c r="G114" t="s">
-        <v>422</v>
-      </c>
-      <c r="H114" t="s">
-        <v>736</v>
-      </c>
-      <c r="I114">
-        <v>13390</v>
-      </c>
-      <c r="J114" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" t="s">
-        <v>738</v>
-      </c>
-      <c r="B115">
-        <v>70</v>
-      </c>
-      <c r="C115">
-        <v>16</v>
-      </c>
-      <c r="D115" t="s">
-        <v>739</v>
-      </c>
-      <c r="E115" t="s">
-        <v>740</v>
-      </c>
-      <c r="F115" t="s">
-        <v>703</v>
-      </c>
-      <c r="G115" t="s">
-        <v>404</v>
-      </c>
-      <c r="H115" t="s">
-        <v>741</v>
-      </c>
-      <c r="I115">
-        <v>11470</v>
-      </c>
-      <c r="J115" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" t="s">
-        <v>743</v>
-      </c>
-      <c r="B116">
-        <v>70</v>
-      </c>
-      <c r="C116">
-        <v>20</v>
-      </c>
-      <c r="D116" t="s">
-        <v>739</v>
-      </c>
-      <c r="E116" t="s">
-        <v>740</v>
-      </c>
-      <c r="F116" t="s">
-        <v>703</v>
-      </c>
-      <c r="G116" t="s">
-        <v>404</v>
-      </c>
-      <c r="H116" t="s">
-        <v>744</v>
-      </c>
-      <c r="I116">
-        <v>11450</v>
-      </c>
-      <c r="J116" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" t="s">
-        <v>746</v>
-      </c>
-      <c r="B117">
-        <v>80</v>
-      </c>
-      <c r="C117">
-        <v>10</v>
-      </c>
-      <c r="D117" t="s">
-        <v>747</v>
-      </c>
-      <c r="E117" t="s">
-        <v>748</v>
-      </c>
-      <c r="F117" t="s">
-        <v>521</v>
-      </c>
-      <c r="G117" t="s">
-        <v>422</v>
-      </c>
-      <c r="H117" t="s">
-        <v>749</v>
-      </c>
-      <c r="I117">
-        <v>8620</v>
-      </c>
-      <c r="J117" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" t="s">
-        <v>751</v>
-      </c>
-      <c r="B118">
-        <v>80</v>
-      </c>
-      <c r="C118">
-        <v>12</v>
-      </c>
-      <c r="D118" t="s">
-        <v>752</v>
-      </c>
-      <c r="E118" t="s">
-        <v>753</v>
-      </c>
-      <c r="F118" t="s">
-        <v>690</v>
-      </c>
-      <c r="G118" t="s">
-        <v>422</v>
-      </c>
-      <c r="H118" t="s">
-        <v>754</v>
-      </c>
-      <c r="I118">
-        <v>11740</v>
-      </c>
-      <c r="J118" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" t="s">
-        <v>756</v>
-      </c>
-      <c r="B119">
-        <v>80</v>
-      </c>
-      <c r="C119">
-        <v>16</v>
-      </c>
-      <c r="D119" t="s">
-        <v>757</v>
-      </c>
-      <c r="E119" t="s">
-        <v>753</v>
-      </c>
-      <c r="F119" t="s">
-        <v>703</v>
-      </c>
-      <c r="G119" t="s">
-        <v>404</v>
-      </c>
-      <c r="H119" t="s">
-        <v>758</v>
-      </c>
-      <c r="I119">
-        <v>12410</v>
-      </c>
-      <c r="J119" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
-      <c r="A120" t="s">
-        <v>760</v>
-      </c>
-      <c r="B120">
-        <v>80</v>
-      </c>
-      <c r="C120">
-        <v>20</v>
-      </c>
-      <c r="D120" t="s">
-        <v>757</v>
-      </c>
-      <c r="E120" t="s">
-        <v>753</v>
-      </c>
-      <c r="F120" t="s">
-        <v>703</v>
-      </c>
-      <c r="G120" t="s">
-        <v>404</v>
-      </c>
-      <c r="H120" t="s">
-        <v>761</v>
-      </c>
-      <c r="I120">
-        <v>12400</v>
-      </c>
-      <c r="J120" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
-      <c r="A121" t="s">
-        <v>763</v>
-      </c>
-      <c r="B121">
-        <v>80</v>
-      </c>
-      <c r="C121">
-        <v>25</v>
-      </c>
-      <c r="D121" t="s">
-        <v>757</v>
-      </c>
-      <c r="E121" t="s">
-        <v>764</v>
-      </c>
-      <c r="F121" t="s">
-        <v>703</v>
-      </c>
-      <c r="G121" t="s">
-        <v>404</v>
-      </c>
-      <c r="H121" t="s">
-        <v>765</v>
-      </c>
-      <c r="I121">
-        <v>12370</v>
-      </c>
-      <c r="J121" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
-      <c r="A122" t="s">
-        <v>767</v>
-      </c>
-      <c r="B122">
-        <v>80</v>
-      </c>
-      <c r="C122">
-        <v>30</v>
-      </c>
-      <c r="D122" t="s">
-        <v>757</v>
-      </c>
-      <c r="E122" t="s">
-        <v>764</v>
-      </c>
-      <c r="F122" t="s">
-        <v>703</v>
-      </c>
-      <c r="G122" t="s">
-        <v>404</v>
-      </c>
-      <c r="H122" t="s">
-        <v>761</v>
-      </c>
-      <c r="I122">
-        <v>12340</v>
-      </c>
-      <c r="J122" t="s">
-        <v>768</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/HIWIN_Specs.xlsx
+++ b/data/HIWIN_Specs.xlsx
@@ -19690,7 +19690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K467"/>
+  <dimension ref="A1:L467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19749,6 +19749,11 @@
           <t>靜負荷 Co (kfg)</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>semantic_text</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19790,6 +19795,11 @@
       <c r="K2" t="n">
         <v>1722</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-4B2 (系列: FSV)。 幾何規格：公稱外徑 16mm，導程 4.0mm，珠徑 2.381mm，節圓直徑(PCD) 16.25mm，根徑 13.792mm，珠卷數為 2.5x2。 機械性能：剛性達 26 kfg/umk，額定動負荷(C)為 802 kgf，靜負荷(Co)為 1722 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19831,6 +19841,11 @@
       <c r="K3" t="n">
         <v>1400</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5B1 (系列: FSV)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 2.5x1。 機械性能：剛性達 16 kfg/umk，額定動負荷(C)為 763 kgf，靜負荷(Co)為 1400 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19872,6 +19887,11 @@
       <c r="K4" t="n">
         <v>2799</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5B2 (系列: FSV)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 2.5x2。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1385 kgf，靜負荷(Co)為 2799 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19913,6 +19933,11 @@
       <c r="K5" t="n">
         <v>1946</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5C1 (系列: FSV)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 3.5x1。 機械性能：剛性達 22 kfg/umk，額定動負荷(C)為 1013 kgf，靜負荷(Co)為 1946 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19954,6 +19979,11 @@
       <c r="K6" t="n">
         <v>1399</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-10B1 (系列: FSV)。 幾何規格：公稱外徑 16mm，導程 10.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 2.5x1。 機械性能：剛性達 16 kfg/umk，額定動負荷(C)為 763 kgf，靜負荷(Co)為 1399 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19995,6 +20025,11 @@
       <c r="K7" t="n">
         <v>1733</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5B1 (系列: FSV)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 2.5x1。 機械性能：剛性達 19 kfg/umk，額定動負荷(C)為 837 kgf，靜負荷(Co)為 1733 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20036,6 +20071,11 @@
       <c r="K8" t="n">
         <v>3465</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5B2 (系列: FSV)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 2.5x2。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 1519 kgf，靜負荷(Co)為 3465 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20077,6 +20117,11 @@
       <c r="K9" t="n">
         <v>2187</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6B1 (系列: FSV)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 2.5x1。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 1139 kgf，靜負荷(Co)為 2187 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20118,6 +20163,11 @@
       <c r="K10" t="n">
         <v>3041</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6C1 (系列: FSV)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 3.5x1。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 1512 kgf，靜負荷(Co)為 3041 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20159,6 +20209,11 @@
       <c r="K11" t="n">
         <v>1281</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-20A1 (系列: FSV)。 幾何規格：公稱外徑 20mm，導程 20.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 1.5x1。 機械性能：剛性達 13 kfg/umk，額定動負荷(C)為 719 kgf，靜負荷(Co)為 1281 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20200,6 +20255,11 @@
       <c r="K12" t="n">
         <v>4417</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5B2 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 2.5x2。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 1704 kgf，靜負荷(Co)為 4417 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20241,6 +20301,11 @@
       <c r="K13" t="n">
         <v>3085</v>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5C1 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 3.5x1。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1252 kgf，靜負荷(Co)為 3085 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20282,6 +20347,11 @@
       <c r="K14" t="n">
         <v>5523</v>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6B2 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 2.5x2。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 2308 kgf，靜負荷(Co)為 5523 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20323,6 +20393,11 @@
       <c r="K15" t="n">
         <v>3844</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6C1 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 3.5x1。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1690 kgf，靜負荷(Co)為 3844 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20364,6 +20439,11 @@
       <c r="K16" t="n">
         <v>6472</v>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-8B2 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 2.5x2。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 2888 kgf，靜負荷(Co)為 6472 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20405,6 +20485,11 @@
       <c r="K17" t="n">
         <v>3237</v>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10B1 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 10.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 2.5x1。 機械性能：剛性達 25 kfg/umk，額定動負荷(C)為 1592 kgf，靜負荷(Co)為 3237 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20446,6 +20531,11 @@
       <c r="K18" t="n">
         <v>6472</v>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10B2 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 10.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 2.5x2。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 2888 kgf，靜負荷(Co)為 6472 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20487,6 +20577,11 @@
       <c r="K19" t="n">
         <v>3237</v>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-16B1 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 16.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 2.5x1。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 1592 kgf，靜負荷(Co)為 3237 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20528,6 +20623,11 @@
       <c r="K20" t="n">
         <v>3237</v>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-20B1 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 20.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 2.5x1。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 1592 kgf，靜負荷(Co)為 3237 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20569,6 +20669,11 @@
       <c r="K21" t="n">
         <v>1927</v>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-25A1 (系列: FSV)。 幾何規格：公稱外徑 25mm，導程 25.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 1.5x1。 機械性能：剛性達 16 kfg/umk，額定動負荷(C)為 1019 kgf，靜負荷(Co)為 1927 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20610,6 +20715,11 @@
       <c r="K22" t="n">
         <v>2466</v>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-5B1 (系列: FSV)。 幾何規格：公稱外徑 28mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 28.6mm，根徑 25.324mm，珠卷數為 2.5x1。 機械性能：剛性達 26 kfg/umk，額定動負荷(C)為 984 kgf，靜負荷(Co)為 2466 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -20651,6 +20761,11 @@
       <c r="K23" t="n">
         <v>4932</v>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-5B2 (系列: FSV)。 幾何規格：公稱外徑 28mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 28.6mm，根徑 25.324mm，珠卷數為 2.5x2。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 1785 kgf，靜負荷(Co)為 4932 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -20692,6 +20807,11 @@
       <c r="K24" t="n">
         <v>2960</v>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-6A2 (系列: FSV)。 幾何規格：公稱外徑 28mm，導程 6.0mm，珠徑 3.175mm，節圓直徑(PCD) 28.6mm，根徑 25.324mm，珠卷數為 1.5x2。 機械性能：剛性達 29 kfg/umk，額定動負荷(C)為 1150 kgf，靜負荷(Co)為 2960 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20733,6 +20853,11 @@
       <c r="K25" t="n">
         <v>4932</v>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-6B2 (系列: FSV)。 幾何規格：公稱外徑 28mm，導程 6.0mm，珠徑 3.175mm，節圓直徑(PCD) 28.6mm，根徑 25.324mm，珠卷數為 2.5x2。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 1784 kgf，靜負荷(Co)為 4932 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20774,6 +20899,11 @@
       <c r="K26" t="n">
         <v>5666</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5B2 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 2.5x2。 機械性能：剛性達 55 kfg/umk，額定動負荷(C)為 1886 kgf，靜負荷(Co)為 5666 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -20815,6 +20945,11 @@
       <c r="K27" t="n">
         <v>3967</v>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5C1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 3.5x1。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 1388 kgf，靜負荷(Co)為 3967 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20856,6 +20991,11 @@
       <c r="K28" t="n">
         <v>7020</v>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6B2 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 2.5x2。 機械性能：剛性達 56 kfg/umk，額定動負荷(C)為 2556 kgf，靜負荷(Co)為 7020 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20897,6 +21037,11 @@
       <c r="K29" t="n">
         <v>4936</v>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6C1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 3.5x1。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 1888 kgf，靜負荷(Co)為 4936 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -20938,6 +21083,11 @@
       <c r="K30" t="n">
         <v>8453</v>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8B2 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 2.5x2。 機械性能：剛性達 59 kfg/umk，額定動負荷(C)為 3284 kgf，靜負荷(Co)為 8453 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -20979,6 +21129,11 @@
       <c r="K31" t="n">
         <v>5948</v>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8C1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 3.5x1。 機械性能：剛性達 41 kfg/umk，額定動負荷(C)為 2428 kgf，靜負荷(Co)為 5948 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -21020,6 +21175,11 @@
       <c r="K32" t="n">
         <v>5599</v>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10B1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x1。 機械性能：剛性達 30 kfg/umk，額定動負荷(C)為 2650 kgf，靜負荷(Co)為 5599 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -21061,6 +21221,11 @@
       <c r="K33" t="n">
         <v>11199</v>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10B2 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x2。 機械性能：剛性達 60 kfg/umk，額定動負荷(C)為 4810 kgf，靜負荷(Co)為 11199 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -21102,6 +21267,11 @@
       <c r="K34" t="n">
         <v>7785</v>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10C1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 3.5x1。 機械性能：剛性達 44 kfg/umk，額定動負荷(C)為 3519 kgf，靜負荷(Co)為 7785 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -21143,6 +21313,11 @@
       <c r="K35" t="n">
         <v>5599</v>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-16B1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 16.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x1。 機械性能：剛性達 30 kfg/umk，額定動負荷(C)為 2650 kgf，靜負荷(Co)為 5599 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -21184,6 +21359,11 @@
       <c r="K36" t="n">
         <v>4227</v>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-20B1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 20.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 2.5x1。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1810 kgf，靜負荷(Co)為 4227 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -21225,6 +21405,11 @@
       <c r="K37" t="n">
         <v>4227</v>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-25B1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 25.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 2.5x1。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1810 kgf，靜負荷(Co)為 4227 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -21266,6 +21451,11 @@
       <c r="K38" t="n">
         <v>2505</v>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-32A1 (系列: FSV)。 幾何規格：公稱外徑 32mm，導程 32.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 1.5x1。 機械性能：剛性達 18 kfg/umk，額定動負荷(C)為 1154 kgf，靜負荷(Co)為 2505 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21307,6 +21497,11 @@
       <c r="K39" t="n">
         <v>3969</v>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-6B1 (系列: FSV)。 幾何規格：公稱外徑 36mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 36.8mm，根徑 32.744mm，珠卷數為 2.5x1。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1486 kgf，靜負荷(Co)為 3969 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21348,6 +21543,11 @@
       <c r="K40" t="n">
         <v>7937</v>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-6B2 (系列: FSV)。 幾何規格：公稱外徑 36mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 36.8mm，根徑 32.744mm，珠卷數為 2.5x2。 機械性能：剛性達 60 kfg/umk，額定動負荷(C)為 2696 kgf，靜負荷(Co)為 7937 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21389,6 +21589,11 @@
       <c r="K41" t="n">
         <v>12669</v>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-10B2 (系列: FSV)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 37.4mm，根徑 30.91mm，珠卷數為 2.5x2。 機械性能：剛性達 68 kfg/umk，額定動負荷(C)為 5105 kgf，靜負荷(Co)為 12669 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21430,6 +21635,11 @@
       <c r="K42" t="n">
         <v>7134</v>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5B2 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 40.6mm，根徑 37.324mm，珠卷數為 2.5x2。 機械性能：剛性達 66 kfg/umk，額定動負荷(C)為 2071 kgf，靜負荷(Co)為 7134 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21471,6 +21681,11 @@
       <c r="K43" t="n">
         <v>8855</v>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-6B2 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 40.8mm，根徑 36.744mm，珠卷數為 2.5x2。 機械性能：剛性達 69 kfg/umk，額定動負荷(C)為 2817 kgf，靜負荷(Co)為 8855 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -21512,6 +21727,11 @@
       <c r="K44" t="n">
         <v>10603</v>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8B2 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 2.5x2。 機械性能：剛性達 70 kfg/umk，額定動負荷(C)為 3634 kgf，靜負荷(Co)為 10603 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -21553,6 +21773,11 @@
       <c r="K45" t="n">
         <v>7438</v>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8C1 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 3.5x1。 機械性能：剛性達 49 kfg/umk，額定動負荷(C)為 2679 kgf，靜負荷(Co)為 7438 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -21594,6 +21819,11 @@
       <c r="K46" t="n">
         <v>14138</v>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10B2 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 2.5x2。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 5370 kgf，靜負荷(Co)為 14138 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -21635,6 +21865,11 @@
       <c r="K47" t="n">
         <v>9841</v>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10C1 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 3.5x1。 機械性能：剛性達 51 kfg/umk，額定動負荷(C)為 3932 kgf，靜負荷(Co)為 9841 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -21676,6 +21911,11 @@
       <c r="K48" t="n">
         <v>15674</v>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-12B2 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 12.0mm，珠徑 7.144mm，節圓直徑(PCD) 41.6mm，根徑 34.299mm，珠卷數為 2.5x2。 機械性能：剛性達 72 kfg/umk，額定動負荷(C)為 6216 kgf，靜負荷(Co)為 15674 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -21717,6 +21957,11 @@
       <c r="K49" t="n">
         <v>15674</v>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-16B2 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 16.0mm，珠徑 7.144mm，節圓直徑(PCD) 41.6mm，根徑 34.299mm，珠卷數為 2.5x2。 機械性能：剛性達 72 kfg/umk，額定動負荷(C)為 6216 kgf，靜負荷(Co)為 15674 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -21758,6 +22003,11 @@
       <c r="K50" t="n">
         <v>7069</v>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-25B1 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 25.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 2.5x1。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 2959 kgf，靜負荷(Co)為 7069 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -21799,6 +22049,11 @@
       <c r="K51" t="n">
         <v>7069</v>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-32B1 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 32.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 2.5x1。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 2959 kgf，靜負荷(Co)為 7069 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -21840,6 +22095,11 @@
       <c r="K52" t="n">
         <v>4159</v>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-40A1 (系列: FSV)。 幾何規格：公稱外徑 40mm，導程 40.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 1.5x1。 機械性能：剛性達 24 kfg/umk，額定動負荷(C)為 1875 kgf，靜負荷(Co)為 4159 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -21881,6 +22141,11 @@
       <c r="K53" t="n">
         <v>11161</v>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-10B1 (系列: FSV)。 幾何規格：公稱外徑 45mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 46.4mm，根徑 39.91mm，珠卷數為 2.5x1。 機械性能：剛性達 45 kfg/umk，額定動負荷(C)為 4170 kgf，靜負荷(Co)為 11161 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -21922,6 +22187,11 @@
       <c r="K54" t="n">
         <v>15905</v>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-10B2 (系列: FSV)。 幾何規格：公稱外徑 45mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 46.4mm，根徑 39.91mm，珠卷數為 2.5x2。 機械性能：剛性達 79 kfg/umk，額定動負荷(C)為 5655 kgf，靜負荷(Co)為 15905 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -21963,6 +22233,11 @@
       <c r="K55" t="n">
         <v>19799</v>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-12B2 (系列: FSV)。 幾何規格：公稱外徑 45mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 46.8mm，根徑 38.688mm，珠卷數為 2.5x2。 機械性能：剛性達 81 kfg/umk，額定動負荷(C)為 7627 kgf，靜負荷(Co)為 19799 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -22004,6 +22279,11 @@
       <c r="K56" t="n">
         <v>5382</v>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5A2 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 1.5x2。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 1447 kgf，靜負荷(Co)為 5382 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -22045,6 +22325,11 @@
       <c r="K57" t="n">
         <v>8072</v>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5A3 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 1.5x3。 機械性能：剛性達 73 kfg/umk，額定動負荷(C)為 2051 kgf，靜負荷(Co)為 8072 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22086,6 +22371,11 @@
       <c r="K58" t="n">
         <v>11149</v>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6B2 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 2.5x2。 機械性能：剛性達 81 kfg/umk，額定動負荷(C)為 3093 kgf，靜負荷(Co)為 11149 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22127,6 +22417,11 @@
       <c r="K59" t="n">
         <v>16723</v>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6B3 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 2.5x3。 機械性能：剛性達 119 kfg/umk，額定動負荷(C)為 4384 kgf，靜負荷(Co)為 16723 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -22168,6 +22463,11 @@
       <c r="K60" t="n">
         <v>13409</v>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8B2 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 2.5x2。 機械性能：剛性達 84 kfg/umk，額定動負荷(C)為 4004 kgf，靜負荷(Co)為 13409 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -22209,6 +22509,11 @@
       <c r="K61" t="n">
         <v>20114</v>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8B3 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 2.5x3。 機械性能：剛性達 124 kfg/umk，額定動負荷(C)為 5674 kgf，靜負荷(Co)為 20114 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -22250,6 +22555,11 @@
       <c r="K62" t="n">
         <v>17670</v>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10B2 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 2.5x2。 機械性能：剛性達 87 kfg/umk，額定動負荷(C)為 5923 kgf，靜負荷(Co)為 17670 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -22291,6 +22601,11 @@
       <c r="K63" t="n">
         <v>26505</v>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10B3 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 2.5x3。 機械性能：剛性達 129 kfg/umk，額定動負荷(C)為 8394 kgf，靜負荷(Co)為 26505 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -22332,6 +22647,11 @@
       <c r="K64" t="n">
         <v>12481</v>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10C1 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 3.5x1。 機械性能：剛性達 60 kfg/umk，額定動負荷(C)為 4393 kgf，靜負荷(Co)為 12481 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22373,6 +22693,11 @@
       <c r="K65" t="n">
         <v>11047</v>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12B1 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 2.5x1。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 4420 kgf，靜負荷(Co)為 11047 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22414,6 +22739,11 @@
       <c r="K66" t="n">
         <v>22094</v>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12B2 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 2.5x2。 機械性能：剛性達 90 kfg/umk，額定動負荷(C)為 8022 kgf，靜負荷(Co)為 22094 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22455,6 +22785,11 @@
       <c r="K67" t="n">
         <v>15380</v>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12C1 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 3.5x1。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 5875 kgf，靜負荷(Co)為 15380 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22496,6 +22831,11 @@
       <c r="K68" t="n">
         <v>6499</v>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-40A1 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 40.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 1.5x1。 機械性能：剛性達 27 kfg/umk，額定動負荷(C)為 2801 kgf，靜負荷(Co)為 6499 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -22537,6 +22877,11 @@
       <c r="K69" t="n">
         <v>6499</v>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-50A1 (系列: FSV)。 幾何規格：公稱外徑 50mm，導程 50.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 1.5x1。 機械性能：剛性達 30 kfg/umk，額定動負荷(C)為 2801 kgf，靜負荷(Co)為 6499 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22578,6 +22923,11 @@
       <c r="K70" t="n">
         <v>13661</v>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 55-10C1 (系列: FSV)。 幾何規格：公稱外徑 55mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 56.4mm，根徑 49.91mm，珠卷數為 3.5x1。 機械性能：剛性達 66 kfg/umk，額定動負荷(C)為 4562 kgf，靜負荷(Co)為 13661 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -22619,6 +22969,11 @@
       <c r="K71" t="n">
         <v>24390</v>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 55-12B2 (系列: FSV)。 幾何規格：公稱外徑 55mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 56.8mm，根徑 48.688mm，珠卷數為 2.5x2。 機械性能：剛性達 95 kfg/umk，額定動負荷(C)為 8392 kgf，靜負荷(Co)為 24390 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -22660,6 +23015,11 @@
       <c r="K72" t="n">
         <v>52439</v>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 55-20B2 (系列: FSV)。 幾何規格：公稱外徑 55mm，導程 20.0mm，珠徑 12.7mm，節圓直徑(PCD) 58.0mm，根徑 45.16mm，珠卷數為 2.5x2。 機械性能：剛性達 127 kfg/umk，額定動負荷(C)為 20160 kgf，靜負荷(Co)為 52439 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -22701,6 +23061,11 @@
       <c r="K73" t="n">
         <v>10129</v>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8A2 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 1.5x2。 機械性能：剛性達 54 kfg/umk，額定動負荷(C)為 2826 kgf，靜負荷(Co)為 10129 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -22742,6 +23107,11 @@
       <c r="K74" t="n">
         <v>15193</v>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8A3 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 1.5x3。 機械性能：剛性達 80 kfg/umk，額定動負荷(C)為 4004 kgf，靜負荷(Co)為 15193 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -22783,6 +23153,11 @@
       <c r="K75" t="n">
         <v>22371</v>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10B2 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 2.5x2。 機械性能：剛性達 104 kfg/umk，額定動負荷(C)為 6533 kgf，靜負荷(Co)為 22371 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -22824,6 +23199,11 @@
       <c r="K76" t="n">
         <v>33556</v>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10B3 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 2.5x3。 機械性能：剛性達 154 kfg/umk，額定動負荷(C)為 9258 kgf，靜負荷(Co)為 33556 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -22865,6 +23245,11 @@
       <c r="K77" t="n">
         <v>28062</v>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12B2 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 64.8mm，根徑 56.688mm，珠卷數為 2.5x2。 機械性能：剛性達 109 kfg/umk，額定動負荷(C)為 8943 kgf，靜負荷(Co)為 28062 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -22906,6 +23291,11 @@
       <c r="K78" t="n">
         <v>46009</v>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-16B2 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 65.2mm，根徑 55.466mm，珠卷數為 2.5x2。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 14862 kgf，靜負荷(Co)為 46009 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -22947,6 +23337,11 @@
       <c r="K79" t="n">
         <v>46009</v>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-20B2 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 65.2mm，根徑 55.466mm，珠卷數為 2.5x2。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 14862 kgf，靜負荷(Co)為 46009 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -22988,6 +23383,11 @@
       <c r="K80" t="n">
         <v>90887</v>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-20B3 (系列: FSV)。 幾何規格：公稱外徑 63mm，導程 20.0mm，珠徑 12.7mm，節圓直徑(PCD) 66.0mm，根徑 53.16mm，珠卷數為 2.5x3。 機械性能：剛性達 210 kfg/umk，額定動負荷(C)為 30715 kgf，靜負荷(Co)為 90887 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -23029,6 +23429,11 @@
       <c r="K81" t="n">
         <v>25011</v>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-10B2 (系列: FSV)。 幾何規格：公稱外徑 70mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 71.4mm，根徑 64.91mm，珠卷數為 2.5x2。 機械性能：剛性達 115 kfg/umk，額定動負荷(C)為 6843 kgf，靜負荷(Co)為 25011 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -23070,6 +23475,11 @@
       <c r="K82" t="n">
         <v>37516</v>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-10B3 (系列: FSV)。 幾何規格：公稱外徑 70mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 71.4mm，根徑 64.91mm，珠卷數為 2.5x3。 機械性能：剛性達 170 kfg/umk，額定動負荷(C)為 9688 kgf，靜負荷(Co)為 37516 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -23111,6 +23521,11 @@
       <c r="K83" t="n">
         <v>31275</v>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-12B2 (系列: FSV)。 幾何規格：公稱外徑 70mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 71.8mm，根徑 63.688mm，珠卷數為 2.5x2。 機械性能：剛性達 120 kfg/umk，額定動負荷(C)為 9382 kgf，靜負荷(Co)為 31275 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -23152,6 +23567,11 @@
       <c r="K84" t="n">
         <v>46912</v>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-12B3 (系列: FSV)。 幾何規格：公稱外徑 70mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 71.8mm，根徑 63.688mm，珠卷數為 2.5x3。 機械性能：剛性達 170 kfg/umk，額定動負荷(C)為 13296 kgf，靜負荷(Co)為 46912 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -23193,6 +23613,11 @@
       <c r="K85" t="n">
         <v>28538</v>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10B2 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 2.5x2。 機械性能：剛性達 126 kfg/umk，額定動負荷(C)為 7202 kgf，靜負荷(Co)為 28538 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -23234,6 +23659,11 @@
       <c r="K86" t="n">
         <v>42807</v>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10B3 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 2.5x3。 機械性能：剛性達 186 kfg/umk，額定動負荷(C)為 10207 kgf，靜負荷(Co)為 42807 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -23275,6 +23705,11 @@
       <c r="K87" t="n">
         <v>35422</v>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12B2 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 2.5x2。 機械性能：剛性達 130 kfg/umk，額定動負荷(C)為 9797 kgf，靜負荷(Co)為 35422 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -23316,6 +23751,11 @@
       <c r="K88" t="n">
         <v>53132</v>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12B3 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 2.5x3。 機械性能：剛性達 192 kfg/umk，額定動負荷(C)為 13884 kgf，靜負荷(Co)為 53132 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -23357,6 +23797,11 @@
       <c r="K89" t="n">
         <v>58851</v>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16B2 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x2。 機械性能：剛性達 171 kfg/umk，額定動負荷(C)為 16485 kgf，靜負荷(Co)為 58851 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -23398,6 +23843,11 @@
       <c r="K90" t="n">
         <v>88276</v>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16B3 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x3。 機械性能：剛性達 252 kfg/umk，額定動負荷(C)為 23363 kgf，靜負荷(Co)為 88276 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -23439,6 +23889,11 @@
       <c r="K91" t="n">
         <v>58851</v>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20B2 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x2。 機械性能：剛性達 171 kfg/umk，額定動負荷(C)為 16485 kgf，靜負荷(Co)為 58851 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -23480,6 +23935,11 @@
       <c r="K92" t="n">
         <v>88276</v>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20B3 (系列: FSV)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x3。 機械性能：剛性達 252 kfg/umk，額定動負荷(C)為 23363 kgf，靜負荷(Co)為 88276 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -23521,6 +23981,11 @@
       <c r="K93" t="n">
         <v>44586</v>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12B2 (系列: FSV)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 2.5x2。 機械性能：剛性達 156 kfg/umk，額定動負荷(C)為 10761 kgf，靜負荷(Co)為 44586 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -23562,6 +24027,11 @@
       <c r="K94" t="n">
         <v>66894</v>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12B3 (系列: FSV)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 2.5x3。 機械性能：剛性達 229 kfg/umk，額定動負荷(C)為 15251 kgf，靜負荷(Co)為 66894 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -23603,6 +24073,11 @@
       <c r="K95" t="n">
         <v>74425</v>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16B2 (系列: FSV)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x2。 機械性能：剛性達 200 kfg/umk，額定動負荷(C)為 18123 kgf，靜負荷(Co)為 74425 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -23644,6 +24119,11 @@
       <c r="K96" t="n">
         <v>111637</v>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16B3 (系列: FSV)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x3。 機械性能：剛性達 305 kfg/umk，額定動負荷(C)為 25684 kgf，靜負荷(Co)為 111637 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -23685,6 +24165,11 @@
       <c r="K97" t="n">
         <v>74425</v>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-20B2 (系列: FSV)。 幾何規格：公稱外徑 100mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x2。 機械性能：剛性達 200 kfg/umk，額定動負荷(C)為 18123 kgf，靜負荷(Co)為 74425 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -23726,6 +24211,11 @@
       <c r="K98" t="n">
         <v>111637</v>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-20B3 (系列: FSV)。 幾何規格：公稱外徑 100mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x3。 機械性能：剛性達 305 kfg/umk，額定動負荷(C)為 18123 kgf，靜負荷(Co)為 111637 kgf。 此型號為標準單螺帽設計，傳動效率優異，是工業自動化最通用的選型。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23769,6 +24259,11 @@
           <t>638</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 12-4B1 (系列: FSW)。 幾何規格：公稱外徑 12mm，導程 4.0mm，珠徑 2.381mm，節圓直徑(PCD) 12.25mm，根徑 9.792mm，珠卷數為 2.5x1。 機械性能：剛性達 8 kfg/umk，額定動負荷(C)為 383 kgf，靜負荷(Co)為 638 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -23812,6 +24307,11 @@
           <t>893</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 12-4C1 (系列: FSW)。 幾何規格：公稱外徑 12mm，導程 4.0mm，珠徑 2.381mm，節圓直徑(PCD) 12.25mm，根徑 9.792mm，珠卷數為 3.5x1。 機械性能：剛性達 9 kfg/umk，額定動負荷(C)為 511 kgf，靜負荷(Co)為 893 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -23855,6 +24355,11 @@
           <t>638</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 12-5B1 (系列: FSW)。 幾何規格：公稱外徑 12mm，導程 5.0mm，珠徑 2.381mm，節圓直徑(PCD) 12.25mm，根徑 9.792mm，珠卷數為 2.5x1。 機械性能：剛性達 8 kfg/umk，額定動負荷(C)為 383 kgf，靜負荷(Co)為 638 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -23898,6 +24403,11 @@
           <t>1216</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 14-5B1 (系列: FSW)。 幾何規格：公稱外徑 14mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 14.6mm，根徑 11.324mm，珠卷數為 2.5x1。 機械性能：剛性達 10 kfg/umk，額定動負荷(C)為 710 kgf，靜負荷(Co)為 1216 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -23941,6 +24451,11 @@
           <t>781</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 15-10A1 (系列: FSW)。 幾何規格：公稱外徑 15mm，導程 10.0mm，珠徑 3.175mm，節圓直徑(PCD) 15.6mm，根徑 12.324mm，珠卷數為 1.5x1。 機械性能：剛性達 9 kfg/umk，額定動負荷(C)為 474 kgf，靜負荷(Co)為 781 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -23984,6 +24499,11 @@
           <t>781</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 15-20A1 (系列: FSW)。 幾何規格：公稱外徑 15mm，導程 20.0mm，珠徑 3.175mm，節圓直徑(PCD) 15.6mm，根徑 12.324mm，珠卷數為 1.5x1。 機械性能：剛性達 9 kfg/umk，額定動負荷(C)為 474 kgf，靜負荷(Co)為 781 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -24027,6 +24547,11 @@
           <t>870</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-4B1 (系列: FSW)。 幾何規格：公稱外徑 16mm，導程 4.0mm，珠徑 2.381mm，節圓直徑(PCD) 16.25mm，根徑 13.792mm，珠卷數為 2.5x1。 機械性能：剛性達 14 kfg/umk，額定動負荷(C)為 439 kgf，靜負荷(Co)為 870 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -24070,6 +24595,11 @@
           <t>1400</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5B1 (系列: FSW)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 2.5x1。 機械性能：剛性達 16 kfg/umk，額定動負荷(C)為 763 kgf，靜負荷(Co)為 1400 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -24113,6 +24643,11 @@
           <t>2799</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5B2 (系列: FSW)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 2.5x2。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1385 kgf，靜負荷(Co)為 2799 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -24156,6 +24691,11 @@
           <t>1946</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5C1 (系列: FSW)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 3.5x1。 機械性能：剛性達 22 kfg/umk，額定動負荷(C)為 1013 kgf，靜負荷(Co)為 1946 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -24199,6 +24739,11 @@
           <t>1733</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5B1 (系列: FSW)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 2.5x1。 機械性能：剛性達 19 kfg/umk，額定動負荷(C)為 837 kgf，靜負荷(Co)為 1733 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -24242,6 +24787,11 @@
           <t>3465</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5B2 (系列: FSW)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 2.5x2。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 1519 kgf，靜負荷(Co)為 3465 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -24285,6 +24835,11 @@
           <t>2187</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6B1 (系列: FSW)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 2.5x1。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 1137 kgf，靜負荷(Co)為 2187 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -24328,6 +24883,11 @@
           <t>3041</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6C1 (系列: FSW)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 3.5x1。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 1512 kgf，靜負荷(Co)為 3041 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -24371,6 +24931,11 @@
           <t>2776</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-4B2 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 4.0mm，珠徑 2.381mm，節圓直徑(PCD) 25.25mm，根徑 22.792mm，珠卷數為 2.5x2。 機械性能：剛性達 38 kfg/umk，額定動負荷(C)為 976 kgf，靜負荷(Co)為 2776 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -24414,6 +24979,11 @@
           <t>4417</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5B2 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 2.5x2。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 1704 kgf，靜負荷(Co)為 4417 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -24457,6 +25027,11 @@
           <t>3085</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5C1 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 3.5x1。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1252 kgf，靜負荷(Co)為 3085 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -24500,6 +25075,11 @@
           <t>2735</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6B1 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 2.5x1。 機械性能：剛性達 24 kfg/umk，額定動負荷(C)為 1255 kgf，靜負荷(Co)為 2735 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -24543,6 +25123,11 @@
           <t>5523</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6B2 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 2.5x2。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 2308 kgf，靜負荷(Co)為 5523 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -24586,6 +25171,11 @@
           <t>3844</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6C1 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 3.5x1。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1690 kgf，靜負荷(Co)為 3844 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -24629,6 +25219,11 @@
           <t>3237</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10B1 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 10.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 2.5x1。 機械性能：剛性達 25 kfg/umk，額定動負荷(C)為 1592 kgf，靜負荷(Co)為 3237 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -24672,6 +25267,11 @@
           <t>6472</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10B2 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 10.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 2.5x2。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 2888 kgf，靜負荷(Co)為 6472 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -24715,6 +25315,11 @@
           <t>2761</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-12B1 (系列: FSW)。 幾何規格：公稱外徑 25mm，導程 12.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 2.5x1。 機械性能：剛性達 24 kfg/umk，額定動負荷(C)為 1271 kgf，靜負荷(Co)為 2761 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -24758,6 +25363,11 @@
           <t>2466</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-5B1 (系列: FSW)。 幾何規格：公稱外徑 28mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 28.6mm，根徑 25.324mm，珠卷數為 2.5x1。 機械性能：剛性達 26 kfg/umk，額定動負荷(C)為 984 kgf，靜負荷(Co)為 2466 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -24801,6 +25411,11 @@
           <t>4932</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-5B2 (系列: FSW)。 幾何規格：公稱外徑 28mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 28.6mm，根徑 25.324mm，珠卷數為 2.5x2。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 1785 kgf，靜負荷(Co)為 4932 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -24844,6 +25459,11 @@
           <t>2960</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-6A2 (系列: FSW)。 幾何規格：公稱外徑 28mm，導程 6.0mm，珠徑 3.175mm，節圓直徑(PCD) 28.6mm，根徑 25.324mm，珠卷數為 1.5x2。 機械性能：剛性達 29 kfg/umk，額定動負荷(C)為 1150 kgf，靜負荷(Co)為 2960 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -24887,6 +25507,11 @@
           <t>7299</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-12B2 (系列: FSW)。 幾何規格：公稱外徑 28mm，導程 12.0mm，珠徑 4.763mm，節圓直徑(PCD) 29.0mm，根徑 24.132mm，珠卷數為 2.5x2。 機械性能：剛性達 51 kfg/umk，額定動負荷(C)為 3060 kgf，靜負荷(Co)為 7299 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -24930,6 +25555,11 @@
           <t>3649</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-16B1 (系列: FSW)。 幾何規格：公稱外徑 28mm，導程 16.0mm，珠徑 4.763mm，節圓直徑(PCD) 29.0mm，根徑 24.132mm，珠卷數為 2.5x1。 機械性能：剛性達 25 kfg/umk，額定動負荷(C)為 1686 kgf，靜負荷(Co)為 3649 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -24973,6 +25603,11 @@
           <t>5666</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5B2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 2.5x2。 機械性能：剛性達 55 kfg/umk，額定動負荷(C)為 1886 kgf，靜負荷(Co)為 5666 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -25016,6 +25651,11 @@
           <t>3967</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5C1 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 3.5x1。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 1388 kgf，靜負荷(Co)為 3967 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -25059,6 +25699,11 @@
           <t>7020</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6B2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 2.5x2。 機械性能：剛性達 56 kfg/umk，額定動負荷(C)為 2556 kgf，靜負荷(Co)為 7020 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -25102,6 +25747,11 @@
           <t>4936</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6C1 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 3.5x1。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 1888 kgf，靜負荷(Co)為 4936 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -25145,6 +25795,11 @@
           <t>8453</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8B2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 2.5x2。 機械性能：剛性達 59 kfg/umk，額定動負荷(C)為 3284 kgf，靜負荷(Co)為 8453 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -25188,6 +25843,11 @@
           <t>5948</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8C1 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 3.5x1。 機械性能：剛性達 41 kfg/umk，額定動負荷(C)為 2428 kgf，靜負荷(Co)為 5948 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -25231,6 +25891,11 @@
           <t>11199</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10B2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x2。 機械性能：剛性達 60 kfg/umk，額定動負荷(C)為 4810 kgf，靜負荷(Co)為 11199 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -25274,6 +25939,11 @@
           <t>7785</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10C1 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 3.5x1。 機械性能：剛性達 44 kfg/umk，額定動負荷(C)為 3519 kgf，靜負荷(Co)為 7785 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -25317,6 +25987,11 @@
           <t>6612</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-12A2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 12.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 1.5x2。 機械性能：剛性達 37 kfg/umk，額定動負荷(C)為 3051 kgf，靜負荷(Co)為 6612 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -25360,6 +26035,11 @@
           <t>11199</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-12B2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 12.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x2。 機械性能：剛性達 59 kfg/umk，額定動負荷(C)為 4810 kgf，靜負荷(Co)為 11199 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -25403,6 +26083,11 @@
           <t>6555</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-16A2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 16.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 1.5x2。 機械性能：剛性達 36 kfg/umk，額定動負荷(C)為 3035 kgf，靜負荷(Co)為 6555 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -25446,6 +26131,11 @@
           <t>5599</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-16B1 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 16.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x1。 機械性能：剛性達 30 kfg/umk，額定動負荷(C)為 2650 kgf，靜負荷(Co)為 5599 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -25489,6 +26179,11 @@
           <t>11199</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-16B2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 16.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x2。 機械性能：剛性達 59 kfg/umk，額定動負荷(C)為 4810 kgf，靜負荷(Co)為 11199 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -25532,6 +26227,11 @@
           <t>6555</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-20A2 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 20.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 1.5x2。 機械性能：剛性達 37 kfg/umk，額定動負荷(C)為 3035 kgf，靜負荷(Co)為 6555 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -25575,6 +26275,11 @@
           <t>5599</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-20B1 (系列: FSW)。 幾何規格：公稱外徑 32mm，導程 20.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 2.5x1。 機械性能：剛性達 30 kfg/umk，額定動負荷(C)為 2650 kgf，靜負荷(Co)為 5599 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -25618,6 +26323,11 @@
           <t>3969</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-6B1 (系列: FSW)。 幾何規格：公稱外徑 36mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 36.8mm，根徑 32.744mm，珠卷數為 2.5x1。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1486 kgf，靜負荷(Co)為 3969 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -25661,6 +26371,11 @@
           <t>7937</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-6B2 (系列: FSW)。 幾何規格：公稱外徑 36mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 36.8mm，根徑 32.744mm，珠卷數為 2.5x2。 機械性能：剛性達 60 kfg/umk，額定動負荷(C)為 2696 kgf，靜負荷(Co)為 7937 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -25704,6 +26419,11 @@
           <t>12669</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-10B2 (系列: FSW)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 37.4mm，根徑 30.91mm，珠卷數為 2.5x2。 機械性能：剛性達 68 kfg/umk，額定動負荷(C)為 5105 kgf，靜負荷(Co)為 12669 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -25747,6 +26467,11 @@
           <t>12668</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-12B2 (系列: FSW)。 幾何規格：公稱外徑 36mm，導程 12.0mm，珠徑 6.35mm，節圓直徑(PCD) 37.4mm，根徑 30.91mm，珠卷數為 2.5x2。 機械性能：剛性達 65 kfg/umk，額定動負荷(C)為 5105 kgf，靜負荷(Co)為 12668 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -25790,6 +26515,11 @@
           <t>8813</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-16C1 (系列: FSW)。 幾何規格：公稱外徑 36mm，導程 16.0mm，珠徑 6.35mm，節圓直徑(PCD) 37.4mm，根徑 30.91mm，珠卷數為 3.5x1。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 3736 kgf，靜負荷(Co)為 8813 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -25833,6 +26563,11 @@
           <t>7134</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5B2 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 40.6mm，根徑 37.324mm，珠卷數為 2.5x2。 機械性能：剛性達 66 kfg/umk，額定動負荷(C)為 2071 kgf，靜負荷(Co)為 7134 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -25876,6 +26611,11 @@
           <t>8855</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-6B2 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 40.8mm，根徑 36.744mm，珠卷數為 2.5x2。 機械性能：剛性達 69 kfg/umk，額定動負荷(C)為 2817 kgf，靜負荷(Co)為 8855 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -25919,6 +26659,11 @@
           <t>10603</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8B2 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 2.5x2。 機械性能：剛性達 70 kfg/umk，額定動負荷(C)為 3634 kgf，靜負荷(Co)為 10603 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -25962,6 +26707,11 @@
           <t>7438</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8C1 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 3.5x1。 機械性能：剛性達 49 kfg/umk，額定動負荷(C)為 2679 kgf，靜負荷(Co)為 7438 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -26005,6 +26755,11 @@
           <t>14138</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10B2 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 2.5x2。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 5370 kgf，靜負荷(Co)為 14138 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -26048,6 +26803,11 @@
           <t>9841</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10C1 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 3.5x1。 機械性能：剛性達 51 kfg/umk，額定動負荷(C)為 3932 kgf，靜負荷(Co)為 9841 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -26091,6 +26851,11 @@
           <t>7837</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-12B1 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 12.0mm，珠徑 7.144mm，節圓直徑(PCD) 41.6mm，根徑 34.299mm，珠卷數為 2.5x1。 機械性能：剛性達 36 kfg/umk，額定動負荷(C)為 3425 kgf，靜負荷(Co)為 7837 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -26134,6 +26899,11 @@
           <t>15674</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-12B2 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 12.0mm，珠徑 7.144mm，節圓直徑(PCD) 41.6mm，根徑 34.299mm，珠卷數為 2.5x2。 機械性能：剛性達 72 kfg/umk，額定動負荷(C)為 6217 kgf，靜負荷(Co)為 15674 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -26177,6 +26947,11 @@
           <t>9405</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-16A2 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 16.0mm，珠徑 7.144mm，節圓直徑(PCD) 41.6mm，根徑 34.299mm，珠卷數為 1.5x2。 機械性能：剛性達 42 kfg/umk，額定動負荷(C)為 4007 kgf，靜負荷(Co)為 9405 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -26220,6 +26995,11 @@
           <t>7837</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-16B1 (系列: FSW)。 幾何規格：公稱外徑 40mm，導程 16.0mm，珠徑 7.144mm，節圓直徑(PCD) 41.6mm，根徑 34.299mm，珠卷數為 2.5x1。 機械性能：剛性達 37 kfg/umk，額定動負荷(C)為 3425 kgf，靜負荷(Co)為 7837 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -26263,6 +27043,11 @@
           <t>7953</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-10B1 (系列: FSW)。 幾何規格：公稱外徑 45mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 46.4mm，根徑 39.91mm，珠卷數為 2.5x1。 機械性能：剛性達 45 kfg/umk，額定動負荷(C)為 3116 kgf，靜負荷(Co)為 7953 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -26306,6 +27091,11 @@
           <t>15905</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-10B2 (系列: FSW)。 幾何規格：公稱外徑 45mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 46.4mm，根徑 39.91mm，珠卷數為 2.5x2。 機械性能：剛性達 79 kfg/umk，額定動負荷(C)為 5655 kgf，靜負荷(Co)為 15905 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -26349,6 +27139,11 @@
           <t>19799</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-12B2 (系列: FSW)。 幾何規格：公稱外徑 45mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 46.8mm，根徑 38.688mm，珠卷數為 2.5x2。 機械性能：剛性達 81 kfg/umk，額定動負荷(C)為 7627 kgf，靜負荷(Co)為 19799 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -26392,6 +27187,11 @@
           <t>5382</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5A2 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 1.5x2。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 1447 kgf，靜負荷(Co)為 5382 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -26435,6 +27235,11 @@
           <t>8072</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5A3 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 1.5x3。 機械性能：剛性達 73 kfg/umk，額定動負荷(C)為 2051 kgf，靜負荷(Co)為 8072 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -26478,6 +27283,11 @@
           <t>11149</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6B2 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 2.5x2。 機械性能：剛性達 81 kfg/umk，額定動負荷(C)為 3093 kgf，靜負荷(Co)為 11149 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -26521,6 +27331,11 @@
           <t>15608</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6C2 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 3.5x2。 機械性能：剛性達 109 kfg/umk，額定動負荷(C)為 4131 kgf，靜負荷(Co)為 15608 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -26564,6 +27379,11 @@
           <t>16723</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6B3 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 2.5x3。 機械性能：剛性達 119 kfg/umk，額定動負荷(C)為 4384 kgf，靜負荷(Co)為 16723 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -26607,6 +27427,11 @@
           <t>13409</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8B2 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 2.5x2。 機械性能：剛性達 84 kfg/umk，額定動負荷(C)為 4004 kgf，靜負荷(Co)為 13409 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -26650,6 +27475,11 @@
           <t>20114</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8B3 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 2.5x3。 機械性能：剛性達 124 kfg/umk，額定動負荷(C)為 5674 kgf，靜負荷(Co)為 20114 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -26693,6 +27523,11 @@
           <t>17670</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10B2 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 2.5x2。 機械性能：剛性達 87 kfg/umk，額定動負荷(C)為 5923 kgf，靜負荷(Co)為 17670 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -26736,6 +27571,11 @@
           <t>26505</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10B3 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 2.5x3。 機械性能：剛性達 129 kfg/umk，額定動負荷(C)為 8394 kgf，靜負荷(Co)為 26505 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -26779,6 +27619,11 @@
           <t>12481</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10C1 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 3.5x1。 機械性能：剛性達 60 kfg/umk，額定動負荷(C)為 4393 kgf，靜負荷(Co)為 12481 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -26822,6 +27667,11 @@
           <t>11047</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12B1 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 2.5x1。 機械性能：剛性達 46 kfg/umk，額定動負荷(C)為 4420 kgf，靜負荷(Co)為 11047 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -26865,6 +27715,11 @@
           <t>22094</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12B2 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 2.5x2。 機械性能：剛性達 90 kfg/umk，額定動負荷(C)為 8022 kgf，靜負荷(Co)為 22094 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -26908,6 +27763,11 @@
           <t>15380</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12C1 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 3.5x1。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 5875 kgf，靜負荷(Co)為 15380 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -26951,6 +27811,11 @@
           <t>10658</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-30A2 (系列: FSW)。 幾何規格：公稱外徑 50mm，導程 30.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 1.5x2。 機械性能：剛性達 52 kfg/umk，額定動負荷(C)為 3834 kgf，靜負荷(Co)為 10658 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -26994,6 +27859,11 @@
           <t>19592</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 55-10B2 (系列: FSW)。 幾何規格：公稱外徑 55mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 56.4mm，根徑 49.91mm，珠卷數為 2.5x2。 機械性能：剛性達 93 kfg/umk，額定動負荷(C)為 6071 kgf，靜負荷(Co)為 19592 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -27037,6 +27907,11 @@
           <t>13661</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 55-10C1 (系列: FSW)。 幾何規格：公稱外徑 55mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 56.4mm，根徑 49.91mm，珠卷數為 3.5x1。 機械性能：剛性達 66 kfg/umk，額定動負荷(C)為 4562 kgf，靜負荷(Co)為 13661 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -27080,6 +27955,11 @@
           <t>24390</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 55-12B2 (系列: FSW)。 幾何規格：公稱外徑 55mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 56.8mm，根徑 48.688mm，珠卷數為 2.5x2。 機械性能：剛性達 95 kfg/umk，額定動負荷(C)為 8392 kgf，靜負荷(Co)為 24390 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -27123,6 +28003,11 @@
           <t>26685</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 60-12B2 (系列: FSW)。 幾何規格：公稱外徑 60mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 61.8mm，根徑 53.688mm，珠卷數為 2.5x2。 機械性能：剛性達 101 kfg/umk，額定動負荷(C)為 8742 kgf，靜負荷(Co)為 26685 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -27166,6 +28051,11 @@
           <t>10129</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8A2 (系列: FSW)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 1.5x2。 機械性能：剛性達 54 kfg/umk，額定動負荷(C)為 2826 kgf，靜負荷(Co)為 10129 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -27209,6 +28099,11 @@
           <t>15193</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8A3 (系列: FSW)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 1.5x3。 機械性能：剛性達 80 kfg/umk，額定動負荷(C)為 4004 kgf，靜負荷(Co)為 15193 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -27252,6 +28147,11 @@
           <t>22371</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10B2 (系列: FSW)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 2.5x2。 機械性能：剛性達 104 kfg/umk，額定動負荷(C)為 6533 kgf，靜負荷(Co)為 22371 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -27295,6 +28195,11 @@
           <t>33556</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10B3 (系列: FSW)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 2.5x3。 機械性能：剛性達 154 kfg/umk，額定動負荷(C)為 9528 kgf，靜負荷(Co)為 33556 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -27338,6 +28243,11 @@
           <t>28062</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12B2 (系列: FSW)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 64.8mm，根徑 56.688mm，珠卷數為 2.5x2。 機械性能：剛性達 109 kfg/umk，額定動負荷(C)為 8943 kgf，靜負荷(Co)為 28062 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -27381,6 +28291,11 @@
           <t>46009</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-16B2 (系列: FSW)。 幾何規格：公稱外徑 63mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 65.2mm，根徑 55.466mm，珠卷數為 2.5x2。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 14862 kgf，靜負荷(Co)為 46009 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -27424,6 +28339,11 @@
           <t>46009</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-20B2 (系列: FSW)。 幾何規格：公稱外徑 63mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 65.2mm，根徑 55.466mm，珠卷數為 2.5x2。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 14862 kgf，靜負荷(Co)為 46009 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -27467,6 +28387,11 @@
           <t>25011</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-10B2 (系列: FSW)。 幾何規格：公稱外徑 70mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 71.4mm，根徑 64.91mm，珠卷數為 2.5x2。 機械性能：剛性達 115 kfg/umk，額定動負荷(C)為 6843 kgf，靜負荷(Co)為 25011 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -27510,6 +28435,11 @@
           <t>37516</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-10B3 (系列: FSW)。 幾何規格：公稱外徑 70mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 71.4mm，根徑 64.91mm，珠卷數為 2.5x3。 機械性能：剛性達 170 kfg/umk，額定動負荷(C)為 9698 kgf，靜負荷(Co)為 37516 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -27553,6 +28483,11 @@
           <t>31275</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-12B2 (系列: FSW)。 幾何規格：公稱外徑 70mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 71.8mm，根徑 63.688mm，珠卷數為 2.5x2。 機械性能：剛性達 120 kfg/umk，額定動負荷(C)為 9382 kgf，靜負荷(Co)為 31275 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -27596,6 +28531,11 @@
           <t>46912</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-12B3 (系列: FSW)。 幾何規格：公稱外徑 70mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 71.8mm，根徑 63.688mm，珠卷數為 2.5x3。 機械性能：剛性達 170 kfg/umk，額定動負荷(C)為 13296 kgf，靜負荷(Co)為 46912 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -27639,6 +28579,11 @@
           <t>28538</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10B2 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 2.5x2。 機械性能：剛性達 126 kfg/umk，額定動負荷(C)為 7202 kgf，靜負荷(Co)為 28538 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -27682,6 +28627,11 @@
           <t>42807</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10B3 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 2.5x3。 機械性能：剛性達 186 kfg/umk，額定動負荷(C)為 10207 kgf，靜負荷(Co)為 42807 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -27725,6 +28675,11 @@
           <t>35422</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12B2 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 2.5x2。 機械性能：剛性達 130 kfg/umk，額定動負荷(C)為 9797 kgf，靜負荷(Co)為 35422 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -27768,6 +28723,11 @@
           <t>53132</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12B3 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 2.5x3。 機械性能：剛性達 192 kfg/umk，額定動負荷(C)為 13844 kgf，靜負荷(Co)為 53132 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -27811,6 +28771,11 @@
           <t>58851</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16B2 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x2。 機械性能：剛性達 171 kfg/umk，額定動負荷(C)為 16485 kgf，靜負荷(Co)為 58851 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -27854,6 +28819,11 @@
           <t>88276</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16B3 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x3。 機械性能：剛性達 252 kfg/umk，額定動負荷(C)為 23363 kgf，靜負荷(Co)為 88276 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -27897,6 +28867,11 @@
           <t>58851</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20B2 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x2。 機械性能：剛性達 171 kfg/umk，額定動負荷(C)為 16485 kgf，靜負荷(Co)為 58851 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -27940,6 +28915,11 @@
           <t>88276</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20B3 (系列: FSW)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 2.5x3。 機械性能：剛性達 252 kfg/umk，額定動負荷(C)為 23363 kgf，靜負荷(Co)為 88276 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -27983,6 +28963,11 @@
           <t>44596</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12B2 (系列: FSW)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 2.5x2。 機械性能：剛性達 156 kfg/umk，額定動負荷(C)為 10761 kgf，靜負荷(Co)為 44596 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -28026,6 +29011,11 @@
           <t>66894</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12B3 (系列: FSW)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 2.5x3。 機械性能：剛性達 229 kfg/umk，額定動負荷(C)為 15251 kgf，靜負荷(Co)為 66894 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -28069,6 +29059,11 @@
           <t>77425</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16B2 (系列: FSW)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x2。 機械性能：剛性達 200 kfg/umk，額定動負荷(C)為 18123 kgf，靜負荷(Co)為 77425 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -28112,6 +29107,11 @@
           <t>111637</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16B3 (系列: FSW)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x3。 機械性能：剛性達 305 kfg/umk，額定動負荷(C)為 25684 kgf，靜負荷(Co)為 111637 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -28156,6 +29156,12 @@
 170</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-20B2 (系列: FSW)。 幾何規格：公稱外徑 100mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x2。 機械性能：剛性達 200 kfg/umk，額定動負荷(C)為 18123 kgf，靜負荷(Co)為 74425
+170 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -28200,6 +29206,12 @@
 170</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-20B3 (系列: FSW)。 幾何規格：公稱外徑 100mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 2.5x3。 機械性能：剛性達 305 kfg/umk，額定動負荷(C)為 25684 kgf，靜負荷(Co)為 111637
+170 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -28239,6 +29251,11 @@
       <c r="K203" t="n">
         <v>267</v>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 8-2.5T3 (系列: FSI)。 幾何規格：公稱外徑 8mm，導程 2.5mm，珠徑 1.5mm，節圓直徑(PCD) 8.2mm，根徑 6.652mm，珠卷數為 3。 機械性能：剛性達 8 kfg/umk，額定動負荷(C)為 170 kgf，靜負荷(Co)為 267 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -28278,6 +29295,11 @@
       <c r="K204" t="n">
         <v>655</v>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 14-2.54T3 (系列: FSI)。 幾何規格：公稱外徑 14mm，導程 2.54mm，珠徑 2.0mm，節圓直徑(PCD) 14.2mm，根徑 12.136mm，珠卷數為 3。 機械性能：剛性達 12 kfg/umk，額定動負荷(C)為 339 kgf，靜負荷(Co)為 655 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -28317,6 +29339,11 @@
       <c r="K205" t="n">
         <v>655</v>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 14-4T3 (系列: FSI)。 幾何規格：公稱外徑 14mm，導程 4.0mm，珠徑 2.0mm，節圓直徑(PCD) 14.2mm，根徑 12.136mm，珠卷數為 3。 機械性能：剛性達 12 kfg/umk，額定動負荷(C)為 339 kgf，靜負荷(Co)為 655 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -28356,6 +29383,11 @@
       <c r="K206" t="n">
         <v>593</v>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-2T3 (系列: FSI)。 幾何規格：公稱外徑 16mm，導程 2.0mm，珠徑 1.5mm，節圓直徑(PCD) 16.2mm，根徑 14.652mm，珠卷數為 3。 機械性能：剛性達 14 kfg/umk，額定動負荷(C)為 252 kgf，靜負荷(Co)為 593 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -28395,6 +29427,11 @@
       <c r="K207" t="n">
         <v>862</v>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-2.5T4 (系列: FSI)。 幾何規格：公稱外徑 16mm，導程 2.5mm，珠徑 1.5mm，節圓直徑(PCD) 16.2mm，根徑 14.652mm，珠卷數為 4。 機械性能：剛性達 19 kfg/umk，額定動負荷(C)為 358 kgf，靜負荷(Co)為 862 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -28434,6 +29471,11 @@
       <c r="K208" t="n">
         <v>1331</v>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5T3 (系列: FSI)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 3。 機械性能：剛性達 11 kfg/umk，額定動負荷(C)為 731 kgf，靜負荷(Co)為 1331 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -28473,6 +29515,11 @@
       <c r="K209" t="n">
         <v>1775</v>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5T4 (系列: FSI)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 4。 機械性能：剛性達 12 kfg/umk，額定動負荷(C)為 936 kgf，靜負荷(Co)為 1775 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -28512,6 +29559,11 @@
       <c r="K210" t="n">
         <v>1775</v>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-6T4 (系列: FSI)。 幾何規格：公稱外徑 16mm，導程 6.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 4。 機械性能：剛性達 21 kfg/umk，額定動負荷(C)為 936 kgf，靜負荷(Co)為 1775 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -28551,6 +29603,11 @@
       <c r="K211" t="n">
         <v>1551</v>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-2T6 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 2.0mm，珠徑 1.5mm，節圓直徑(PCD) 20.2mm，根徑 18.652mm，珠卷數為 6。 機械性能：剛性達 32 kfg/umk，額定動負荷(C)為 518 kgf，靜負荷(Co)為 1551 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -28590,6 +29647,11 @@
       <c r="K212" t="n">
         <v>1112</v>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-2T4 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 2.0mm，珠徑 1.5mm，節圓直徑(PCD) 20.2mm，根徑 18.652mm，珠卷數為 4。 機械性能：剛性達 36 kfg/umk，額定動負荷(C)為 399 kgf，靜負荷(Co)為 1112 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -28629,6 +29691,11 @@
       <c r="K213" t="n">
         <v>1635</v>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-2.5T5 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 2.5mm，珠徑 2.0mm，節圓直徑(PCD) 20.2mm，根徑 18.136mm，珠卷數為 5。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 637 kgf，靜負荷(Co)為 1635 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -28668,6 +29735,11 @@
       <c r="K214" t="n">
         <v>1962</v>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-2.54T6 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 2.54mm，珠徑 2.0mm，節圓直徑(PCD) 20.2mm，根徑 18.136mm，珠卷數為 6。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 745 kgf，靜負荷(Co)為 1962 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -28707,6 +29779,11 @@
       <c r="K215" t="n">
         <v>1134</v>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-4T3 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 4.0mm，珠徑 2.381mm，節圓直徑(PCD) 20.25mm，根徑 17.792mm，珠卷數為 3。 機械性能：剛性達 17 kfg/umk，額定動負荷(C)為 509 kgf，靜負荷(Co)為 1134 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -28746,6 +29823,11 @@
       <c r="K216" t="n">
         <v>1767</v>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5T3 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 3。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 852 kgf，靜負荷(Co)為 1767 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -28785,6 +29867,11 @@
       <c r="K217" t="n">
         <v>2356</v>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5T4 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 4。 機械性能：剛性達 27 kfg/umk，額定動負荷(C)為 1091 kgf，靜負荷(Co)為 2356 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -28824,6 +29911,11 @@
       <c r="K218" t="n">
         <v>2081</v>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6T3 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 3。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 1091 kgf，靜負荷(Co)為 2081 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -28863,6 +29955,11 @@
       <c r="K219" t="n">
         <v>2774</v>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6T4 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 4。 機械性能：剛性達 27 kfg/umk，額定動負荷(C)為 1398 kgf，靜負荷(Co)為 2774 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -28902,6 +29999,11 @@
       <c r="K220" t="n">
         <v>2080</v>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-10T3 (系列: FSI)。 幾何規格：公稱外徑 20mm，導程 10.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 3。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 1091 kgf，靜負荷(Co)為 2080 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -28941,6 +30043,11 @@
       <c r="K221" t="n">
         <v>1960</v>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-2T6 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 2.0mm，珠徑 1.5mm，節圓直徑(PCD) 25.2mm，根徑 23.652mm，珠卷數為 6。 機械性能：剛性達 39 kfg/umk，額定動負荷(C)為 560 kgf，靜負荷(Co)為 1960 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -28980,6 +30087,11 @@
       <c r="K222" t="n">
         <v>1307</v>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-2T4 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 2.0mm，珠徑 1.5mm，節圓直徑(PCD) 25.2mm，根徑 23.652mm，珠卷數為 4。 機械性能：剛性達 27 kfg/umk，額定動負荷(C)為 395 kgf，靜負荷(Co)為 1307 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -29019,6 +30131,11 @@
       <c r="K223" t="n">
         <v>980</v>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-2T3 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 2.0mm，珠徑 1.5mm，節圓直徑(PCD) 25.2mm，根徑 23.652mm，珠卷數為 3。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 309 kgf，靜負荷(Co)為 980 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -29058,6 +30175,11 @@
       <c r="K224" t="n">
         <v>2117</v>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-2.5T5 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 2.5mm，珠徑 2.0mm，節圓直徑(PCD) 25.2mm，根徑 23.136mm，珠卷數為 5。 機械性能：剛性達 34 kfg/umk，額定動負荷(C)為 716 kgf，靜負荷(Co)為 2117 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -29097,6 +30219,11 @@
       <c r="K225" t="n">
         <v>1989</v>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-4T4 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 4.0mm，珠徑 2.381mm，節圓直徑(PCD) 25.25mm，根徑 22.792mm，珠卷數為 4。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 747 kgf，靜負荷(Co)為 1989 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -29136,6 +30263,11 @@
       <c r="K226" t="n">
         <v>2314</v>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5T3 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 3。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 977 kgf，靜負荷(Co)為 2314 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -29175,6 +30307,11 @@
       <c r="K227" t="n">
         <v>3085</v>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5T4 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 4。 機械性能：剛性達 37 kfg/umk，額定動負荷(C)為 1252 kgf，靜負荷(Co)為 3085 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -29214,6 +30351,11 @@
       <c r="K228" t="n">
         <v>3856</v>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5T5 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 5。 機械性能：剛性達 40 kfg/umk，額定動負荷(C)為 1516 kgf，靜負荷(Co)為 3856 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -29253,6 +30395,11 @@
       <c r="K229" t="n">
         <v>4627</v>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5T6 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 6。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 1773 kgf，靜負荷(Co)為 4627 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -29292,6 +30439,11 @@
       <c r="K230" t="n">
         <v>2762</v>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6T3 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 3。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 1272 kgf，靜負荷(Co)為 2762 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -29331,6 +30483,11 @@
       <c r="K231" t="n">
         <v>3682</v>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6T4 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 4。 機械性能：剛性達 37 kfg/umk，額定動負荷(C)為 1628 kgf，靜負荷(Co)為 3682 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -29370,6 +30527,11 @@
       <c r="K232" t="n">
         <v>3236</v>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10T3 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 10.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 3。 機械性能：剛性達 25 kfg/umk，額定動負荷(C)為 1591 kgf，靜負荷(Co)為 3236 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -29409,6 +30571,11 @@
       <c r="K233" t="n">
         <v>4315</v>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10T4 (系列: FSI)。 幾何規格：公稱外徑 25mm，導程 10.0mm，珠徑 4.763mm，節圓直徑(PCD) 26.0mm，根徑 21.132mm，珠卷數為 4。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 2038 kgf，靜負荷(Co)為 4315 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -29448,6 +30615,11 @@
       <c r="K234" t="n">
         <v>3081</v>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5T3 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 3。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1117 kgf，靜負荷(Co)為 3081 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -29487,6 +30659,11 @@
       <c r="K235" t="n">
         <v>4108</v>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5T4 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 4。 機械性能：剛性達 42 kfg/umk，額定動負荷(C)為 1431 kgf，靜負荷(Co)為 4108 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -29526,6 +30703,11 @@
       <c r="K236" t="n">
         <v>6162</v>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5T6 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 6。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 2027 kgf，靜負荷(Co)為 6162 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -29565,6 +30747,11 @@
       <c r="K237" t="n">
         <v>3620</v>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6T3 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 3。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1446 kgf，靜負荷(Co)為 3620 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -29604,6 +30791,11 @@
       <c r="K238" t="n">
         <v>4826</v>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6T4 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 4。 機械性能：剛性達 43 kfg/umk，額定動負荷(C)為 1852 kgf，靜負荷(Co)為 4826 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -29643,6 +30835,11 @@
       <c r="K239" t="n">
         <v>7239</v>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6T6 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 6。 機械性能：剛性達 65 kfg/umk，額定動負荷(C)為 2625 kgf，靜負荷(Co)為 7239 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -29682,6 +30879,11 @@
       <c r="K240" t="n">
         <v>4227</v>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8T3 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 3。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1810 kgf，靜負荷(Co)為 4227 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -29721,6 +30923,11 @@
       <c r="K241" t="n">
         <v>5635</v>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8T4 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 4。 機械性能：剛性達 47 kfg/umk，額定動負荷(C)為 2317 kgf，靜負荷(Co)為 5635 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -29760,6 +30967,11 @@
       <c r="K242" t="n">
         <v>5327</v>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10T3 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 3。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 2539 kgf，靜負荷(Co)為 5327 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -29799,6 +31011,11 @@
       <c r="K243" t="n">
         <v>7102</v>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10T4 (系列: FSI)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 4。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 3252 kgf，靜負荷(Co)為 7102 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -29838,6 +31055,11 @@
       <c r="K244" t="n">
         <v>5280</v>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5T4 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 40.6mm，根徑 37.324mm，珠卷數為 4。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 1599 kgf，靜負荷(Co)為 5280 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -29877,6 +31099,11 @@
       <c r="K245" t="n">
         <v>7919</v>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5T6 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 40.6mm，根徑 37.324mm，珠卷數為 6。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 2265 kgf，靜負荷(Co)為 7919 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -29916,6 +31143,11 @@
       <c r="K246" t="n">
         <v>7919</v>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5.08T6 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 5.08mm，珠徑 3.175mm，節圓直徑(PCD) 40.6mm，根徑 37.324mm，珠卷數為 6。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 2265 kgf，靜負荷(Co)為 7919 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -29955,6 +31187,11 @@
       <c r="K247" t="n">
         <v>6420</v>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-6T4 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 40.8mm，根徑 36.744mm，珠卷數為 4。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 2136 kgf，靜負荷(Co)為 6420 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -29994,6 +31231,11 @@
       <c r="K248" t="n">
         <v>9630</v>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-6T6 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 40.8mm，根徑 36.744mm，珠卷數為 6。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 3028 kgf，靜負荷(Co)為 9630 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -30033,6 +31275,11 @@
       <c r="K249" t="n">
         <v>7596</v>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8T4 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 4。 機械性能：剛性達 52 kfg/umk，額定動負荷(C)為 2728 kgf，靜負荷(Co)為 7596 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -30072,6 +31319,11 @@
       <c r="K250" t="n">
         <v>11394</v>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8T6 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 6。 機械性能：剛性達 76 kfg/umk，額定動負荷(C)為 3866 kgf，靜負荷(Co)為 11394 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -30111,6 +31363,11 @@
       <c r="K251" t="n">
         <v>7069</v>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10T3 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 3。 機械性能：剛性達 40 kfg/umk，額定動負荷(C)為 2959 kgf，靜負荷(Co)為 7069 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -30150,6 +31407,11 @@
       <c r="K252" t="n">
         <v>9426</v>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10T4 (系列: FSI)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 4。 機械性能：剛性達 51 kfg/umk，額定動負荷(C)為 3789 kgf，靜負荷(Co)為 9426 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -30189,6 +31451,11 @@
       <c r="K253" t="n">
         <v>6745</v>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5T4 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 4。 機械性能：剛性達 62 kfg/umk，額定動負荷(C)為 1757 kgf，靜負荷(Co)為 6745 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -30228,6 +31495,11 @@
       <c r="K254" t="n">
         <v>10117</v>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5T6 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 6。 機械性能：剛性達 91 kfg/umk，額定動負荷(C)為 2490 kgf，靜負荷(Co)為 10117 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -30267,6 +31539,11 @@
       <c r="K255" t="n">
         <v>8250</v>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6T4 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 4。 機械性能：剛性達 62 kfg/umk，額定動負荷(C)為 2388 kgf，靜負荷(Co)為 8250 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -30306,6 +31583,11 @@
       <c r="K256" t="n">
         <v>12375</v>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6T6 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 6。 機械性能：剛性達 93 kfg/umk，額定動負荷(C)為 3384 kgf，靜負荷(Co)為 12375 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -30345,6 +31627,11 @@
       <c r="K257" t="n">
         <v>9578</v>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8T4 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 4。 機械性能：剛性達 62 kfg/umk，額定動負荷(C)為 2998 kgf，靜負荷(Co)為 9578 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -30384,6 +31671,11 @@
       <c r="K258" t="n">
         <v>14367</v>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8T6 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 6。 機械性能：剛性達 92 kfg/umk，額定動負荷(C)為 4249 kgf，靜負荷(Co)為 14367 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -30423,6 +31715,11 @@
       <c r="K259" t="n">
         <v>9256</v>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10T3 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 3。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 3397 kgf，靜負荷(Co)為 9256 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -30462,6 +31759,11 @@
       <c r="K260" t="n">
         <v>12341</v>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10T4 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 4。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 4350 kgf，靜負荷(Co)為 12341 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -30501,6 +31803,11 @@
       <c r="K261" t="n">
         <v>18511</v>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10T6 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 6。 機械性能：剛性達 94 kfg/umk，額定動負荷(C)為 6165 kgf，靜負荷(Co)為 18511 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -30540,6 +31847,11 @@
       <c r="K262" t="n">
         <v>11047</v>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12T3 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 3。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 4420 kgf，靜負荷(Co)為 11047 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -30579,6 +31891,11 @@
       <c r="K263" t="n">
         <v>14730</v>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12T4 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 4。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 5660 kgf，靜負荷(Co)為 14730 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -30618,6 +31935,11 @@
       <c r="K264" t="n">
         <v>23955</v>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-20T4 (系列: FSI)。 幾何規格：公稱外徑 50mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 52.2mm，根徑 42.466mm，珠卷數為 4。 機械性能：剛性達 80 kfg/umk，額定動負荷(C)為 9327 kgf，靜負荷(Co)為 23955 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -30657,6 +31979,11 @@
       <c r="K265" t="n">
         <v>10542</v>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-6T4 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 63.8mm，根徑 59.744mm，珠卷數為 4。 機械性能：剛性達 75 kfg/umk，額定動負荷(C)為 2614 kgf，靜負荷(Co)為 10542 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -30696,6 +32023,11 @@
       <c r="K266" t="n">
         <v>15813</v>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-6T6 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 63.8mm，根徑 59.744mm，珠卷數為 6。 機械性能：剛性達 113 kfg/umk，額定動負荷(C)為 3704 kgf，靜負荷(Co)為 15813 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -30735,6 +32067,11 @@
       <c r="K267" t="n">
         <v>12541</v>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8T4 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 4。 機械性能：剛性達 77 kfg/umk，額定動負荷(C)為 3395 kgf，靜負荷(Co)為 12541 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -30774,6 +32111,11 @@
       <c r="K268" t="n">
         <v>18811</v>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8T6 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 6。 機械性能：剛性達 114 kfg/umk，額定動負荷(C)為 4812 kgf，靜負荷(Co)為 18811 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -30813,6 +32155,11 @@
       <c r="K269" t="n">
         <v>15858</v>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10T4 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 4。 機械性能：剛性達 79 kfg/umk，額定動負荷(C)為 4860 kgf，靜負荷(Co)為 15858 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -30852,6 +32199,11 @@
       <c r="K270" t="n">
         <v>23786</v>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10T6 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 6。 機械性能：剛性達 115 kfg/umk，額定動負荷(C)為 6887 kgf，靜負荷(Co)為 23786 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -30891,6 +32243,11 @@
       <c r="K271" t="n">
         <v>19293</v>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12T4 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 64.8mm，根徑 56.688mm，珠卷數為 4。 機械性能：剛性達 78 kfg/umk，額定動負荷(C)為 6479 kgf，靜負荷(Co)為 19293 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -30930,6 +32287,11 @@
       <c r="K272" t="n">
         <v>28939</v>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12T6 (系列: FSI)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 64.8mm，根徑 56.688mm，珠卷數為 6。 機械性能：剛性達 113 kfg/umk，額定動負荷(C)為 9182 kgf，靜負荷(Co)為 28939 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -30969,6 +32331,11 @@
       <c r="K273" t="n">
         <v>21118</v>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10T4 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 4。 機械性能：剛性達 96 kfg/umk，額定動負荷(C)為 5559 kgf，靜負荷(Co)為 21118 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -31008,6 +32375,11 @@
       <c r="K274" t="n">
         <v>31677</v>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10T6 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 6。 機械性能：剛性達 140 kfg/umk，額定動負荷(C)為 7879 kgf，靜負荷(Co)為 31677 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -31047,6 +32419,11 @@
       <c r="K275" t="n">
         <v>25681</v>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12T4 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 4。 機械性能：剛性達 97 kfg/umk，額定動負荷(C)為 7430 kgf，靜負荷(Co)為 25681 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -31086,6 +32463,11 @@
       <c r="K276" t="n">
         <v>38521</v>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12T6 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 6。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 10530 kgf，靜負荷(Co)為 38521 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -31125,6 +32507,11 @@
       <c r="K277" t="n">
         <v>31622</v>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16T3 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 3。 機械性能：剛性達 95 kfg/umk，額定動負荷(C)為 9663 kgf，靜負荷(Co)為 31622 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -31164,6 +32551,11 @@
       <c r="K278" t="n">
         <v>42162</v>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16T4 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 4。 機械性能：剛性達 130 kfg/umk，額定動負荷(C)為 12375 kgf，靜負荷(Co)為 42162 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -31203,6 +32595,11 @@
       <c r="K279" t="n">
         <v>31622</v>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20T3 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 3。 機械性能：剛性達 95 kfg/umk，額定動負荷(C)為 9663 kgf，靜負荷(Co)為 31622 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -31242,6 +32639,11 @@
       <c r="K280" t="n">
         <v>42162</v>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20T4 (系列: FSI)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 4。 機械性能：剛性達 125 kfg/umk，額定動負荷(C)為 12375 kgf，靜負荷(Co)為 42162 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -31281,6 +32683,11 @@
       <c r="K281" t="n">
         <v>33001</v>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12T4 (系列: FSI)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 4。 機械性能：剛性達 105 kfg/umk，額定動負荷(C)為 8306 kgf，靜負荷(Co)為 33001 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -31320,6 +32727,11 @@
       <c r="K282" t="n">
         <v>49502</v>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12T6 (系列: FSI)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 6。 機械性能：剛性達 175 kfg/umk，額定動負荷(C)為 11772 kgf，靜負荷(Co)為 49502 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -31359,6 +32771,11 @@
       <c r="K283" t="n">
         <v>53161</v>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16T4 (系列: FSI)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 4。 機械性能：剛性達 107 kfg/umk，額定動負荷(C)為 13569 kgf，靜負荷(Co)為 53161 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -31398,6 +32815,11 @@
       <c r="K284" t="n">
         <v>79741</v>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16T6 (系列: FSI)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 6。 機械性能：剛性達 140 kfg/umk，額定動負荷(C)為 19230 kgf，靜負荷(Co)為 79741 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -31437,6 +32859,11 @@
       <c r="K285" t="n">
         <v>53161</v>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-20T4 (系列: FSI)。 幾何規格：公稱外徑 100mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 4。 機械性能：剛性達 155 kfg/umk，額定動負荷(C)為 13569 kgf，靜負荷(Co)為 53161 kgf。 此型號結構輕巧省空間，適合小型自動化設備或精密儀器。</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -31478,6 +32905,11 @@
           <t>395</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-2T4 (系列: RSI)。 幾何規格：公稱外徑 16mm，導程 2.0mm，珠徑 1.5mm，節圓直徑(PCD) 16.2mm，根徑 14.652mm，珠卷數為 4。 機械性能：剛性達 15 kfg/umk，額定動負荷(C)為 178 kgf，靜負荷(Co)為 395 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -31519,6 +32951,11 @@
           <t>1331</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5T3 (系列: RSI)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 3。 機械性能：剛性達 11 kfg/umk，額定動負荷(C)為 731 kgf，靜負荷(Co)為 1331 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -31560,6 +32997,11 @@
           <t>1775</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-5T4 (系列: RSI)。 幾何規格：公稱外徑 16mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 16.6mm，根徑 13.324mm，珠卷數為 4。 機械性能：剛性達 12 kfg/umk，額定動負荷(C)為 936 kgf，靜負荷(Co)為 1775 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -31601,6 +33043,11 @@
           <t>1767</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5T3 (系列: RSI)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 3。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 852 kgf，靜負荷(Co)為 1767 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -31642,6 +33089,11 @@
           <t>2356</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5T4 (系列: RSI)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 20.6mm，根徑 17.324mm，珠卷數為 4。 機械性能：剛性達 27 kfg/umk，額定動負荷(C)為 1091 kgf，靜負荷(Co)為 2356 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -31683,6 +33135,11 @@
           <t>2081</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6T3 (系列: RSI)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 3。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 1091 kgf，靜負荷(Co)為 2081 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -31724,6 +33181,11 @@
           <t>2774</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6T4 (系列: RSI)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 20.8mm，根徑 16.744mm，珠卷數為 4。 機械性能：剛性達 27 kfg/umk，額定動負荷(C)為 1398 kgf，靜負荷(Co)為 2774 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -31765,6 +33227,11 @@
           <t>2314</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5T3 (系列: RSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 3。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 977 kgf，靜負荷(Co)為 2314 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -31806,6 +33273,11 @@
           <t>3085</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5T4 (系列: RSI)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 25.6mm，根徑 22.324mm，珠卷數為 4。 機械性能：剛性達 37 kfg/umk，額定動負荷(C)為 1252 kgf，靜負荷(Co)為 3085 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -31847,6 +33319,11 @@
           <t>2762</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6T3 (系列: RSI)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 3。 機械性能：剛性達 28 kfg/umk，額定動負荷(C)為 1272 kgf，靜負荷(Co)為 2762 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -31888,6 +33365,11 @@
           <t>3682</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6T4 (系列: RSI)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 25.8mm，根徑 21.744mm，珠卷數為 4。 機械性能：剛性達 37 kfg/umk，額定動負荷(C)為 1628 kgf，靜負荷(Co)為 3682 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -31929,6 +33411,11 @@
           <t>3081</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5T3 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 3。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1117 kgf，靜負荷(Co)為 3081 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -31970,6 +33457,11 @@
           <t>4108</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5T4 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 4。 機械性能：剛性達 42 kfg/umk，額定動負荷(C)為 1431 kgf，靜負荷(Co)為 4108 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -32011,6 +33503,11 @@
           <t>6162</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5T6 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 32.6mm，根徑 29.324mm，珠卷數為 6。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 2027 kgf，靜負荷(Co)為 6162 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -32052,6 +33549,11 @@
           <t>3620</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6T3 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 3。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 1446 kgf，靜負荷(Co)為 3620 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -32093,6 +33595,11 @@
           <t>4826</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6T4 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 4。 機械性能：剛性達 43 kfg/umk，額定動負荷(C)為 1852 kgf，靜負荷(Co)為 4826 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -32134,6 +33641,11 @@
           <t>7239</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6T6 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 32.8mm，根徑 28.744mm，珠卷數為 6。 機械性能：剛性達 65 kfg/umk，額定動負荷(C)為 2625 kgf，靜負荷(Co)為 7239 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -32175,6 +33687,11 @@
           <t>4227</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8T3 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 3。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 1810 kgf，靜負荷(Co)為 4227 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -32216,6 +33733,11 @@
           <t>5635</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8T4 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 33.0mm，根徑 28.132mm，珠卷數為 4。 機械性能：剛性達 47 kfg/umk，額定動負荷(C)為 2317 kgf，靜負荷(Co)為 5635 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -32257,6 +33779,11 @@
           <t>5327</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10T3 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 3。 機械性能：剛性達 35 kfg/umk，額定動負荷(C)為 2539 kgf，靜負荷(Co)為 5327 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -32298,6 +33825,11 @@
           <t>7102</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10T4 (系列: RSI)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 33.4mm，根徑 26.91mm，珠卷數為 4。 機械性能：剛性達 48 kfg/umk，額定動負荷(C)為 3252 kgf，靜負荷(Co)為 7102 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -32339,6 +33871,11 @@
           <t>5280</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5T4 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 40.6mm，根徑 37.324mm，珠卷數為 4。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 1599 kgf，靜負荷(Co)為 5280 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -32380,6 +33917,11 @@
           <t>7919</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5T6 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 40.6mm，根徑 37.324mm，珠卷數為 6。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 2265 kgf，靜負荷(Co)為 7919 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -32421,6 +33963,11 @@
           <t>6420</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-6T4 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 40.8mm，根徑 36.744mm，珠卷數為 4。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 2136 kgf，靜負荷(Co)為 6420 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -32462,6 +34009,11 @@
           <t>9630</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-6T6 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 40.8mm，根徑 36.744mm，珠卷數為 6。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 3028 kgf，靜負荷(Co)為 9630 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -32503,6 +34055,11 @@
           <t>7596</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8T4 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 4。 機械性能：剛性達 52 kfg/umk，額定動負荷(C)為 2728 kgf，靜負荷(Co)為 7596 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -32544,6 +34101,11 @@
           <t>11394</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8T6 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 41.0mm，根徑 36.132mm，珠卷數為 6。 機械性能：剛性達 76 kfg/umk，額定動負荷(C)為 3866 kgf，靜負荷(Co)為 11394 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -32585,6 +34147,11 @@
           <t>7069</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10T3 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 3。 機械性能：剛性達 40 kfg/umk，額定動負荷(C)為 2959 kgf，靜負荷(Co)為 7069 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -32626,6 +34193,11 @@
           <t>9426</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10T4 (系列: RSI)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 41.4mm，根徑 34.91mm，珠卷數為 4。 機械性能：剛性達 51 kfg/umk，額定動負荷(C)為 3789 kgf，靜負荷(Co)為 9426 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -32667,6 +34239,11 @@
           <t>6745</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5T4 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 4。 機械性能：剛性達 62 kfg/umk，額定動負荷(C)為 1757 kgf，靜負荷(Co)為 6745 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -32708,6 +34285,11 @@
           <t>10117</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5T6 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 3.175mm，節圓直徑(PCD) 50.6mm，根徑 47.324mm，珠卷數為 6。 機械性能：剛性達 91 kfg/umk，額定動負荷(C)為 2490 kgf，靜負荷(Co)為 10117 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -32749,6 +34331,11 @@
           <t>8250</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6T4 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 4。 機械性能：剛性達 62 kfg/umk，額定動負荷(C)為 2388 kgf，靜負荷(Co)為 8250 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -32790,6 +34377,11 @@
           <t>12375</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-6T6 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 50.8mm，根徑 46.744mm，珠卷數為 6。 機械性能：剛性達 93 kfg/umk，額定動負荷(C)為 3384 kgf，靜負荷(Co)為 12375 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -32831,6 +34423,11 @@
           <t>9578</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8T4 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 4。 機械性能：剛性達 62 kfg/umk，額定動負荷(C)為 2998 kgf，靜負荷(Co)為 9578 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -32872,6 +34469,11 @@
           <t>14367</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8T6 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 51.0mm，根徑 46.132mm，珠卷數為 6。 機械性能：剛性達 92 kfg/umk，額定動負荷(C)為 4249 kgf，靜負荷(Co)為 14367 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -32913,6 +34515,11 @@
           <t>9256</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10T3 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 3。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 3397 kgf，靜負荷(Co)為 9256 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -32955,6 +34562,12 @@
 69</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10T4 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 4。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 4350 kgf，靜負荷(Co)為 12341
+69 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -32996,6 +34609,11 @@
           <t>18511</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10T6 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 6.35mm，節圓直徑(PCD) 51.4mm，根徑 44.91mm，珠卷數為 6。 機械性能：剛性達 94 kfg/umk，額定動負荷(C)為 6165 kgf，靜負荷(Co)為 18511 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -33037,6 +34655,11 @@
           <t>11047</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12T3 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 3。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 4420 kgf，靜負荷(Co)為 11047 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -33078,6 +34701,11 @@
           <t>14730</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12T4 (系列: RSI)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 51.8mm，根徑 43.688mm，珠卷數為 4。 機械性能：剛性達 63 kfg/umk，額定動負荷(C)為 5660 kgf，靜負荷(Co)為 14730 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -33119,6 +34747,11 @@
           <t>10542</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-6T4 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 63.8mm，根徑 59.744mm，珠卷數為 4。 機械性能：剛性達 75 kfg/umk，額定動負荷(C)為 2674 kgf，靜負荷(Co)為 10542 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -33160,6 +34793,11 @@
           <t>15813</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-6T6 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 6.0mm，珠徑 3.969mm，節圓直徑(PCD) 63.8mm，根徑 59.744mm，珠卷數為 6。 機械性能：剛性達 113 kfg/umk，額定動負荷(C)為 3704 kgf，靜負荷(Co)為 15813 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -33201,6 +34839,11 @@
           <t>12541</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8T4 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 4。 機械性能：剛性達 77 kfg/umk，額定動負荷(C)為 3395 kgf，靜負荷(Co)為 12541 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -33242,6 +34885,11 @@
           <t>18811</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-8T6 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 8.0mm，珠徑 4.763mm，節圓直徑(PCD) 64.0mm，根徑 59.132mm，珠卷數為 6。 機械性能：剛性達 114 kfg/umk，額定動負荷(C)為 4812 kgf，靜負荷(Co)為 18811 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -33283,6 +34931,11 @@
           <t>15858</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10T4 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 4。 機械性能：剛性達 79 kfg/umk，額定動負荷(C)為 4860 kgf，靜負荷(Co)為 15858 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -33324,6 +34977,11 @@
           <t>23786</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10T6 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 64.4mm，根徑 57.91mm，珠卷數為 6。 機械性能：剛性達 115 kfg/umk，額定動負荷(C)為 6887 kgf，靜負荷(Co)為 23786 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -33365,6 +35023,11 @@
           <t>19293</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12T4 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 64.8mm，根徑 56.688mm，珠卷數為 4。 機械性能：剛性達 78 kfg/umk，額定動負荷(C)為 6479 kgf，靜負荷(Co)為 19293 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -33406,6 +35069,11 @@
           <t>28939</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12T6 (系列: RSI)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 64.8mm，根徑 56.688mm，珠卷數為 6。 機械性能：剛性達 113 kfg/umk，額定動負荷(C)為 9182 kgf，靜負荷(Co)為 28939 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -33447,6 +35115,11 @@
           <t>21118</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10T4 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 4。 機械性能：剛性達 96 kfg/umk，額定動負荷(C)為 5559 kgf，靜負荷(Co)為 21118 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -33488,6 +35161,11 @@
           <t>31677</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10T6 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 6.35mm，節圓直徑(PCD) 81.4mm，根徑 74.91mm，珠卷數為 6。 機械性能：剛性達 140 kfg/umk，額定動負荷(C)為 7879 kgf，靜負荷(Co)為 31677 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -33529,6 +35207,11 @@
           <t>25681</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12T4 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 4。 機械性能：剛性達 97 kfg/umk，額定動負荷(C)為 7430 kgf，靜負荷(Co)為 25681 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -33570,6 +35253,11 @@
           <t>38521</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12T6 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 81.8mm，根徑 73.688mm，珠卷數為 6。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 10530 kgf，靜負荷(Co)為 38521 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -33611,6 +35299,11 @@
           <t>31622</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16T3 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 3。 機械性能：剛性達 95 kfg/umk，額定動負荷(C)為 9663 kgf，靜負荷(Co)為 31622 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -33652,6 +35345,11 @@
           <t>42162</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16T4 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 4。 機械性能：剛性達 130 kfg/umk，額定動負荷(C)為 12375 kgf，靜負荷(Co)為 42162 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -33693,6 +35391,11 @@
           <t>31622</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20T3 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 3。 機械性能：剛性達 95 kfg/umk，額定動負荷(C)為 9663 kgf，靜負荷(Co)為 31622 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -33734,6 +35437,11 @@
           <t>42162</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20T4 (系列: RSI)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 82.2mm，根徑 72.466mm，珠卷數為 4。 機械性能：剛性達 125 kfg/umk，額定動負荷(C)為 12375 kgf，靜負荷(Co)為 42162 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -33775,6 +35483,11 @@
           <t>33001</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12T4 (系列: RSI)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 4。 機械性能：剛性達 105 kfg/umk，額定動負荷(C)為 8306 kgf，靜負荷(Co)為 33001 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -33816,6 +35529,11 @@
           <t>49502</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-12T6 (系列: RSI)。 幾何規格：公稱外徑 100mm，導程 12.0mm，珠徑 7.938mm，節圓直徑(PCD) 101.8mm，根徑 93.688mm，珠卷數為 6。 機械性能：剛性達 175 kfg/umk，額定動負荷(C)為 11772 kgf，靜負荷(Co)為 49502 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -33857,6 +35575,11 @@
           <t>53161</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16T4 (系列: RSI)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 4。 機械性能：剛性達 107 kfg/umk，額定動負荷(C)為 13569 kgf，靜負荷(Co)為 53161 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -33898,6 +35621,11 @@
           <t>79741</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-16T6 (系列: RSI)。 幾何規格：公稱外徑 100mm，導程 16.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 6。 機械性能：剛性達 140 kfg/umk，額定動負荷(C)為 19230 kgf，靜負荷(Co)為 79741 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -33939,6 +35667,11 @@
           <t>53161</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 100-20T4 (系列: RSI)。 幾何規格：公稱外徑 100mm，導程 20.0mm，珠徑 9.525mm，節圓直徑(PCD) 102.2mm，根徑 92.466mm，珠卷數為 4。 機械性能：剛性達 155 kfg/umk，額定動負荷(C)為 13569 kgf，靜負荷(Co)為 53161 kgf。 此型號為旋轉螺帽設計，適合長行程且需高速旋轉螺帽的特殊機構。</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -33978,6 +35711,11 @@
       <c r="K347" t="n">
         <v>1790</v>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 14-10K3 (系列: FDC)。 幾何規格：公稱外徑 14mm，導程 10.0mm，珠徑 14.6mm，節圓直徑(PCD) 10.724mm，根徑 3.175mm，珠卷數為 3。 機械性能：剛性達 31 kfg/umk，額定動負荷(C)為 920 kgf，靜負荷(Co)為 1790 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -34017,6 +35755,11 @@
       <c r="K348" t="n">
         <v>1970</v>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 15-10K3 (系列: FDC)。 幾何規格：公稱外徑 15mm，導程 10.0mm，珠徑 16.0mm，節圓直徑(PCD) 12.869mm，根徑 3.0mm，珠卷數為 3。 機械性能：剛性達 34 kfg/umk，額定動負荷(C)為 930 kgf，靜負荷(Co)為 1970 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -34056,6 +35799,11 @@
       <c r="K349" t="n">
         <v>1230</v>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 15-16K2 (系列: FDC)。 幾何規格：公稱外徑 15mm，導程 10.0mm，珠徑 16.0mm，節圓直徑(PCD) 12.869mm，根徑 3.0mm，珠卷數為 2。 機械性能：剛性達 21 kfg/umk，額定動負荷(C)為 610 kgf，靜負荷(Co)為 1230 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -34095,6 +35843,11 @@
       <c r="K350" t="n">
         <v>1930</v>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 15-10K3 (系列: FDC)。 幾何規格：公稱外徑 15mm，導程 10.0mm，珠徑 20.0mm，節圓直徑(PCD) 12.324mm，根徑 3.175mm，珠卷數為 3。 機械性能：剛性達 33 kfg/umk，額定動負荷(C)為 960 kgf，靜負荷(Co)為 1930 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -34134,6 +35887,11 @@
       <c r="K351" t="n">
         <v>1256</v>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 15-20K2 (系列: FDC)。 幾何規格：公稱外徑 15mm，導程 10.0mm，珠徑 20.0mm，節圓直徑(PCD) 12.324mm，根徑 3.175mm，珠卷數為 2。 機械性能：剛性達 20 kfg/umk，額定動負荷(C)為 630 kgf，靜負荷(Co)為 1256 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -34173,6 +35931,11 @@
       <c r="K352" t="n">
         <v>1385</v>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 16-16K2 (系列: FDC)。 幾何規格：公稱外徑 16mm，導程 16.0mm，珠徑 16.4mm，節圓直徑(PCD) 13.124mm，根徑 3.175mm，珠卷數為 2。 機械性能：剛性達 23 kfg/umk，額定動負荷(C)為 680 kgf，靜負荷(Co)為 1385 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -34212,6 +35975,11 @@
       <c r="K353" t="n">
         <v>3560</v>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-10K4 (系列: FDC)。 幾何規格：公稱外徑 20mm，導程 10.0mm，珠徑 21.0mm，節圓直徑(PCD) 17.868mm，根徑 3.0mm，珠卷數為 4。 機械性能：剛性達 57 kfg/umk，額定動負荷(C)為 1390 kgf，靜負荷(Co)為 3560 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -34251,6 +36019,11 @@
       <c r="K354" t="n">
         <v>3640</v>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-5K4 (系列: FDC)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 17.324mm，根徑 3.175mm，珠卷數為 4。 機械性能：剛性達 55 kfg/umk，額定動負荷(C)為 1490 kgf，靜負荷(Co)為 3640 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -34290,6 +36063,11 @@
       <c r="K355" t="n">
         <v>2660</v>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-10K3 (系列: FDC)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 17.324mm，根徑 3.175mm，珠卷數為 3。 機械性能：剛性達 42 kfg/umk，額定動負荷(C)為 1130 kgf，靜負荷(Co)為 2660 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -34329,6 +36107,11 @@
       <c r="K356" t="n">
         <v>1730</v>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-20K2 (系列: FDC)。 幾何規格：公稱外徑 20mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 17.324mm，根徑 3.175mm，珠卷數為 2。 機械性能：剛性達 27 kfg/umk，額定動負荷(C)為 760 kgf，靜負荷(Co)為 1730 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -34368,6 +36151,11 @@
       <c r="K357" t="n">
         <v>5660</v>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-6K5 (系列: FDC)。 幾何規格：公稱外徑 20mm，導程 6.0mm，珠徑 20.8mm，節圓直徑(PCD) 16.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 77 kfg/umk，額定動負荷(C)為 2420 kgf，靜負荷(Co)為 5660 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -34407,6 +36195,11 @@
       <c r="K358" t="n">
         <v>6505</v>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 20-8K5 (系列: FDC)。 幾何規格：公稱外徑 20mm，導程 8.0mm，珠徑 21.0mm，節圓直徑(PCD) 16.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 77 kfg/umk，額定動負荷(C)為 2960 kgf，靜負荷(Co)為 6505 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -34446,6 +36239,11 @@
       <c r="K359" t="n">
         <v>4612</v>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-5K4 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 16.132mm，根徑 3.175mm，珠卷數為 4。 機械性能：剛性達 65 kfg/umk，額定動負荷(C)為 1650 kgf，靜負荷(Co)為 4612 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -34485,6 +36283,11 @@
       <c r="K360" t="n">
         <v>3370</v>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10K3 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 16.132mm，根徑 3.175mm，珠卷數為 3。 機械性能：剛性達 50 kfg/umk，額定動負荷(C)為 1260 kgf，靜負荷(Co)為 3370 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -34524,6 +36327,11 @@
       <c r="K361" t="n">
         <v>5730</v>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-15K5 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 22.324mm，根徑 3.175mm，珠卷數為 5。 機械性能：剛性達 83 kfg/umk，額定動負荷(C)為 1980 kgf，靜負荷(Co)為 5730 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -34563,6 +36371,11 @@
       <c r="K362" t="n">
         <v>3436</v>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-20K3 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 22.324mm，根徑 3.175mm，珠卷數為 3。 機械性能：剛性達 51 kfg/umk，額定動負荷(C)為 1260 kgf，靜負荷(Co)為 3436 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -34602,6 +36415,11 @@
       <c r="K363" t="n">
         <v>2170</v>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-25K2 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 5.0mm，珠徑 10.0mm，節圓直徑(PCD) 22.324mm，根徑 3.175mm，珠卷數為 2。 機械性能：剛性達 32 kfg/umk，額定動負荷(C)為 840 kgf，靜負荷(Co)為 2170 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -34641,6 +36459,11 @@
       <c r="K364" t="n">
         <v>7192</v>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-6K5 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 21.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 91 kfg/umk，額定動負荷(C)為 2720 kgf，靜負荷(Co)為 7192 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -34680,6 +36503,11 @@
       <c r="K365" t="n">
         <v>7170</v>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-8K5 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 21.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 92 kfg/umk，額定動負荷(C)為 2710 kgf，靜負荷(Co)為 7170 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -34719,6 +36547,11 @@
       <c r="K366" t="n">
         <v>5660</v>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-10K4 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 21.744mm，根徑 3.969mm，珠卷數為 4。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 2210 kgf，靜負荷(Co)為 5660 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -34758,6 +36591,11 @@
       <c r="K367" t="n">
         <v>5640</v>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-12K4 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 21.744mm，根徑 3.969mm，珠卷數為 4。 機械性能：剛性達 74 kfg/umk，額定動負荷(C)為 2200 kgf，靜負荷(Co)為 5640 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -34797,6 +36635,11 @@
       <c r="K368" t="n">
         <v>4127</v>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-16K3 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 21.744mm，根徑 3.969mm，珠卷數為 3。 機械性能：剛性達 55 kfg/umk，額定動負荷(C)為 1670 kgf，靜負荷(Co)為 4127 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -34836,6 +36679,11 @@
       <c r="K369" t="n">
         <v>4290</v>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-20K3 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 21.744mm，根徑 3.969mm，珠卷數為 3。 機械性能：剛性達 55 kfg/umk，額定動負荷(C)為 1710 kgf，靜負荷(Co)為 4290 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -34875,6 +36723,11 @@
       <c r="K370" t="n">
         <v>8683</v>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 25-8K5 (系列: FDC)。 幾何規格：公稱外徑 25mm，導程 8.0mm，珠徑 26.0mm，節圓直徑(PCD) 21.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 96 kfg/umk，額定動負荷(C)為 3480 kgf，靜負荷(Co)為 8683 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -34914,6 +36767,11 @@
       <c r="K371" t="n">
         <v>7966</v>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-6K5 (系列: FDC)。 幾何規格：公稱外徑 28mm，導程 6.0mm，珠徑 28.8mm，節圓直徑(PCD) 24.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 93 kfg/umk，額定動負荷(C)為 2840 kgf，靜負荷(Co)為 7966 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -34953,6 +36811,11 @@
       <c r="K372" t="n">
         <v>9780</v>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-8K5 (系列: FDC)。 幾何規格：公稱外徑 28mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 24.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 104 kfg/umk，額定動負荷(C)為 3690 kgf，靜負荷(Co)為 9780 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -34992,6 +36855,11 @@
       <c r="K373" t="n">
         <v>9760</v>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-10K5 (系列: FDC)。 幾何規格：公稱外徑 28mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 24.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 105 kfg/umk，額定動負荷(C)為 3680 kgf，靜負荷(Co)為 9760 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -35031,6 +36899,11 @@
       <c r="K374" t="n">
         <v>7661</v>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 28-16K4 (系列: FDC)。 幾何規格：公稱外徑 28mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 24.132mm，根徑 4.763mm，珠卷數為 4。 機械性能：剛性達 84 kfg/umk，額定動負荷(C)為 2970 kgf，靜負荷(Co)為 7661 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -35070,6 +36943,11 @@
       <c r="K375" t="n">
         <v>5960</v>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5K4 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 5.08mm，節圓直徑(PCD) 29.324mm，根徑 3.175mm，珠卷數為 4。 機械性能：剛性達 77 kfg/umk，額定動負荷(C)為 1840 kgf，靜負荷(Co)為 5960 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -35109,6 +36987,11 @@
       <c r="K376" t="n">
         <v>5940</v>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-5.08K4 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 5.0mm，珠徑 5.08mm，節圓直徑(PCD) 29.324mm，根徑 3.175mm，珠卷數為 4。 機械性能：剛性達 77 kfg/umk，額定動負荷(C)為 1840 kgf，靜負荷(Co)為 5940 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -35148,6 +37031,11 @@
       <c r="K377" t="n">
         <v>9480</v>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-6K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 111 kfg/umk，額定動負荷(C)為 3090 kgf，靜負荷(Co)為 9480 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -35187,6 +37075,11 @@
       <c r="K378" t="n">
         <v>9430</v>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 112 kfg/umk，額定動負荷(C)為 3080 kgf，靜負荷(Co)為 9430 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -35226,6 +37119,11 @@
       <c r="K379" t="n">
         <v>9460</v>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 112 kfg/umk，額定動負荷(C)為 3080 kgf，靜負荷(Co)為 9460 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -35265,6 +37163,11 @@
       <c r="K380" t="n">
         <v>9450</v>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 113 kfg/umk，額定動負荷(C)為 3080 kgf，靜負荷(Co)為 9450 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -35304,6 +37207,11 @@
       <c r="K381" t="n">
         <v>7440</v>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-15K4 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 4。 機械性能：剛性達 91 kfg/umk，額定動負荷(C)為 2500 kgf，靜負荷(Co)為 7440 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -35343,6 +37251,11 @@
       <c r="K382" t="n">
         <v>5430</v>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-20K3 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 3。 機械性能：剛性達 68 kfg/umk，額定動負荷(C)為 1900 kgf，靜負荷(Co)為 5430 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -35382,6 +37295,11 @@
       <c r="K383" t="n">
         <v>3530</v>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-32K2 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 2。 機械性能：剛性達 44 kfg/umk，額定動負荷(C)為 1280 kgf，靜負荷(Co)為 3530 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -35421,6 +37339,11 @@
       <c r="K384" t="n">
         <v>3440</v>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-40K2 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 6.0mm，珠徑 8.0mm，節圓直徑(PCD) 28.744mm，根徑 3.969mm，珠卷數為 2。 機械性能：剛性達 42 kfg/umk，額定動負荷(C)為 1240 kgf，靜負荷(Co)為 3440 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -35460,6 +37383,11 @@
       <c r="K385" t="n">
         <v>10914</v>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-8K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 28.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 112 kfg/umk，額定動負荷(C)為 3860 kgf，靜負荷(Co)為 10914 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -35499,6 +37427,11 @@
       <c r="K386" t="n">
         <v>10890</v>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 28.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 113 kfg/umk，額定動負荷(C)為 3850 kgf，靜負荷(Co)為 10890 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -35538,6 +37471,11 @@
       <c r="K387" t="n">
         <v>10870</v>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-12K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 28.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 114 kfg/umk，額定動負荷(C)為 3840 kgf，靜負荷(Co)為 10870 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -35577,6 +37515,11 @@
       <c r="K388" t="n">
         <v>8914</v>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-20K4 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 28.132mm，根徑 4.763mm，珠卷數為 4。 機械性能：剛性達 94 kfg/umk，額定動負荷(C)為 3190 kgf，靜負荷(Co)為 8914 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -35616,6 +37559,11 @@
       <c r="K389" t="n">
         <v>6500</v>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-25K3 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 28.132mm，根徑 4.763mm，珠卷數為 3。 機械性能：剛性達 70 kfg/umk，額定動負荷(C)為 2420 kgf，靜負荷(Co)為 6500 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -35655,6 +37603,11 @@
       <c r="K390" t="n">
         <v>4100</v>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-32K2 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 8.0mm，珠徑 10.0mm，節圓直徑(PCD) 28.132mm，根徑 4.763mm，珠卷數為 2。 機械性能：剛性達 44 kfg/umk，額定動負荷(C)為 1620 kgf，靜負荷(Co)為 4100 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -35694,6 +37647,11 @@
       <c r="K391" t="n">
         <v>14480</v>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-10K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 26.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 119 kfg/umk，額定動負荷(C)為 5640 kgf，靜負荷(Co)為 14480 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -35733,6 +37691,11 @@
       <c r="K392" t="n">
         <v>14450</v>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-12K5 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 26.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 119 kfg/umk，額定動負荷(C)為 5620 kgf，靜負荷(Co)為 14450 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -35772,6 +37735,11 @@
       <c r="K393" t="n">
         <v>11390</v>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-16K4 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 26.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 96 kfg/umk，額定動負荷(C)為 4570 kgf，靜負荷(Co)為 11390 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -35811,6 +37779,11 @@
       <c r="K394" t="n">
         <v>10854</v>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 32-20K4 (系列: FDC)。 幾何規格：公稱外徑 32mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 26.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 71 kfg/umk，額定動負荷(C)為 4240 kgf，靜負荷(Co)為 10854 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -35850,6 +37823,11 @@
       <c r="K395" t="n">
         <v>10632</v>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-6K5 (系列: FDC)。 幾何規格：公稱外徑 36mm，導程 6.0mm，珠徑 36.8mm，節圓直徑(PCD) 32.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 118 kfg/umk，額定動負荷(C)為 3240 kgf，靜負荷(Co)為 10632 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -35889,6 +37867,11 @@
       <c r="K396" t="n">
         <v>16440</v>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-10K5 (系列: FDC)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 30.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 130 kfg/umk，額定動負荷(C)為 6010 kgf，靜負荷(Co)為 16440 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -35928,6 +37911,11 @@
       <c r="K397" t="n">
         <v>16420</v>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-12K5 (系列: FDC)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 30.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 131 kfg/umk，額定動負荷(C)為 5990 kgf，靜負荷(Co)為 16420 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -35967,6 +37955,11 @@
       <c r="K398" t="n">
         <v>16350</v>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-16K5 (系列: FDC)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 30.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 132 kfg/umk，額定動負荷(C)為 5960 kgf，靜負荷(Co)為 16350 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -36006,6 +37999,11 @@
       <c r="K399" t="n">
         <v>12880</v>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-20K4 (系列: FDC)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 30.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 105 kfg/umk，額定動負荷(C)為 4840 kgf，靜負荷(Co)為 12880 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -36045,6 +38043,11 @@
       <c r="K400" t="n">
         <v>12880</v>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-20K4 (系列: FDC)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 30.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 105 kfg/umk，額定動負荷(C)為 4840 kgf，靜負荷(Co)為 12880 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -36084,6 +38087,11 @@
       <c r="K401" t="n">
         <v>6240</v>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 36-36K2 (系列: FDC)。 幾何規格：公稱外徑 36mm，導程 10.0mm，珠徑 12.0mm，節圓直徑(PCD) 30.91mm，根徑 6.35mm，珠卷數為 2。 機械性能：剛性達 51 kfg/umk，額定動負荷(C)為 2540 kgf，靜負荷(Co)為 6240 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -36123,6 +38131,11 @@
       <c r="K402" t="n">
         <v>13110</v>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 38-8K5 (系列: FDC)。 幾何規格：公稱外徑 38mm，導程 8.0mm，珠徑 39.0mm，節圓直徑(PCD) 34.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 127 kfg/umk，額定動負荷(C)為 4190 kgf，靜負荷(Co)為 13110 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -36162,6 +38175,11 @@
       <c r="K403" t="n">
         <v>13790</v>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 38-10K4 (系列: FDC)。 幾何規格：公稱外徑 38mm，導程 10.0mm，珠徑 15.0mm，節圓直徑(PCD) 32.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 107 kfg/umk，額定動負荷(C)為 5050 kgf，靜負荷(Co)為 13790 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -36201,6 +38219,11 @@
       <c r="K404" t="n">
         <v>13740</v>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 38-15K4 (系列: FDC)。 幾何規格：公稱外徑 38mm，導程 10.0mm，珠徑 15.0mm，節圓直徑(PCD) 32.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 109 kfg/umk，額定動負荷(C)為 5020 kgf，靜負荷(Co)為 13740 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -36240,6 +38263,11 @@
       <c r="K405" t="n">
         <v>17340</v>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 38-16K5 (系列: FDC)。 幾何規格：公稱外徑 38mm，導程 10.0mm，珠徑 15.0mm，節圓直徑(PCD) 32.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 137 kfg/umk，額定動負荷(C)為 6140 kgf，靜負荷(Co)為 17340 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -36279,6 +38307,11 @@
       <c r="K406" t="n">
         <v>13660</v>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 38-20K4 (系列: FDC)。 幾何規格：公稱外徑 38mm，導程 10.0mm，珠徑 15.0mm，節圓直徑(PCD) 32.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 110 kfg/umk，額定動負荷(C)為 4990 kgf，靜負荷(Co)為 13660 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -36318,6 +38351,11 @@
       <c r="K407" t="n">
         <v>13560</v>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 38-25K4 (系列: FDC)。 幾何規格：公稱外徑 38mm，導程 10.0mm，珠徑 15.0mm，節圓直徑(PCD) 32.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 109 kfg/umk，額定動負荷(C)為 4940 kgf，靜負荷(Co)為 13560 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -36357,6 +38395,11 @@
       <c r="K408" t="n">
         <v>6560</v>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 38-40K2 (系列: FDC)。 幾何規格：公稱外徑 38mm，導程 10.0mm，珠徑 15.0mm，節圓直徑(PCD) 32.91mm，根徑 6.35mm，珠卷數為 2。 機械性能：剛性達 53 kfg/umk，額定動負荷(C)為 2590 kgf，靜負荷(Co)為 6560 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -36396,6 +38439,11 @@
       <c r="K409" t="n">
         <v>9490</v>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-5K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 5.0mm，珠徑 40.6mm，節圓直徑(PCD) 37.324mm，根徑 3.175mm，珠卷數為 5。 機械性能：剛性達 114 kfg/umk，額定動負荷(C)為 2470 kgf，靜負荷(Co)為 9490 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -36435,6 +38483,11 @@
       <c r="K410" t="n">
         <v>11780</v>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-6K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 6.0mm，珠徑 40.8mm，節圓直徑(PCD) 36.744mm，根徑 3.969mm，珠卷數為 5。 機械性能：剛性達 127 kfg/umk，額定動負荷(C)為 3370 kgf，靜負荷(Co)為 11780 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -36474,6 +38527,11 @@
       <c r="K411" t="n">
         <v>14200</v>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-8K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 8.0mm，珠徑 41.0mm，節圓直徑(PCD) 36.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 135 kfg/umk，額定動負荷(C)為 4360 kgf，靜負荷(Co)為 14200 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -36513,6 +38571,11 @@
       <c r="K412" t="n">
         <v>14180</v>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 41.0mm，節圓直徑(PCD) 36.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 136 kfg/umk，額定動負荷(C)為 4350 kgf，靜負荷(Co)為 14180 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -36552,6 +38615,11 @@
       <c r="K413" t="n">
         <v>14060</v>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-20K4 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 20.0mm，珠徑 41.0mm，節圓直徑(PCD) 36.132mm，根徑 4.763mm，珠卷數為 4。 機械性能：剛性達 119 kfg/umk，額定動負荷(C)為 4300 kgf，靜負荷(Co)為 14060 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -36591,6 +38659,11 @@
       <c r="K414" t="n">
         <v>15510</v>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-16K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 16.0mm，珠徑 41.2mm，節圓直徑(PCD) 35.522mm，根徑 5.556mm，珠卷數為 5。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 5170 kgf，靜負荷(Co)為 15510 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -36630,6 +38703,11 @@
       <c r="K415" t="n">
         <v>18400</v>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-10K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 10.0mm，珠徑 41.4mm，節圓直徑(PCD) 34.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 141 kfg/umk，額定動負荷(C)為 6340 kgf，靜負荷(Co)為 18400 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -36669,6 +38747,11 @@
       <c r="K416" t="n">
         <v>18380</v>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-12K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 12.0mm，珠徑 41.4mm，節圓直徑(PCD) 34.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 142 kfg/umk，額定動負荷(C)為 6330 kgf，靜負荷(Co)為 18380 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -36708,6 +38791,11 @@
       <c r="K417" t="n">
         <v>18320</v>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-16K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 16.0mm，珠徑 41.4mm，節圓直徑(PCD) 34.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 143 kfg/umk，額定動負荷(C)為 6300 kgf，靜負荷(Co)為 18320 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -36747,6 +38835,11 @@
       <c r="K418" t="n">
         <v>14440</v>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-20K4 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 20.0mm，珠徑 41.4mm，節圓直徑(PCD) 34.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 115 kfg/umk，額定動負荷(C)為 5130 kgf，靜負荷(Co)為 14440 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -36786,6 +38879,11 @@
       <c r="K419" t="n">
         <v>11010</v>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-30K3 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 30.0mm，珠徑 41.4mm，節圓直徑(PCD) 34.91mm，根徑 6.35mm，珠卷數為 3。 機械性能：剛性達 88 kfg/umk，額定動負荷(C)為 4000 kgf，靜負荷(Co)為 11010 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -36825,6 +38923,11 @@
       <c r="K420" t="n">
         <v>14350</v>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-25K4 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 25.0mm，珠徑 41.4mm，節圓直徑(PCD) 34.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 114 kfg/umk，額定動負荷(C)為 5080 kgf，靜負荷(Co)為 14350 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -36864,6 +38967,11 @@
       <c r="K421" t="n">
         <v>6940</v>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-40K2 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 40.0mm，珠徑 41.4mm，節圓直徑(PCD) 34.91mm，根徑 6.35mm，珠卷數為 2。 機械性能：剛性達 56 kfg/umk，額定動負荷(C)為 2660 kgf，靜負荷(Co)為 6940 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -36903,6 +39011,11 @@
       <c r="K422" t="n">
         <v>20790</v>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-12K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 12.0mm，珠徑 41.6mm，節圓直徑(PCD) 34.299mm，根徑 7.144mm，珠卷數為 5。 機械性能：剛性達 146 kfg/umk，額定動負荷(C)為 7430 kgf，靜負荷(Co)為 20790 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -36942,6 +39055,11 @@
       <c r="K423" t="n">
         <v>20720</v>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 40-16K5 (系列: FDC)。 幾何規格：公稱外徑 40mm，導程 16.0mm，珠徑 41.6mm，節圓直徑(PCD) 34.299mm，根徑 7.144mm，珠卷數為 5。 機械性能：剛性達 147 kfg/umk，額定動負荷(C)為 7400 kgf，靜負荷(Co)為 20720 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -36981,6 +39099,11 @@
       <c r="K424" t="n">
         <v>15860</v>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-8K5 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 8.0mm，珠徑 46.0mm，節圓直徑(PCD) 41.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 145 kfg/umk，額定動負荷(C)為 4550 kgf，靜負荷(Co)為 15860 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -37020,6 +39143,11 @@
       <c r="K425" t="n">
         <v>21320</v>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-10K5 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 10.0mm，珠徑 46.4mm，節圓直徑(PCD) 39.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 156 kfg/umk，額定動負荷(C)為 6810 kgf，靜負荷(Co)為 21320 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -37059,6 +39187,11 @@
       <c r="K426" t="n">
         <v>21290</v>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-12K5 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 12.0mm，珠徑 46.4mm，節圓直徑(PCD) 39.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 158 kfg/umk，額定動負荷(C)為 6800 kgf，靜負荷(Co)為 21290 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -37098,6 +39231,11 @@
       <c r="K427" t="n">
         <v>21240</v>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-16K5 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 16.0mm，珠徑 46.4mm，節圓直徑(PCD) 39.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 160 kfg/umk，額定動負荷(C)為 6780 kgf，靜負荷(Co)為 21240 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -37137,6 +39275,11 @@
       <c r="K428" t="n">
         <v>16760</v>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-20K4 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 20.0mm，珠徑 46.4mm，節圓直徑(PCD) 39.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 129 kfg/umk，額定動負荷(C)為 5520 kgf，靜負荷(Co)為 16760 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -37176,6 +39319,11 @@
       <c r="K429" t="n">
         <v>16670</v>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-25K4 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 25.0mm，珠徑 46.4mm，節圓直徑(PCD) 39.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 129 kfg/umk，額定動負荷(C)為 5480 kgf，靜負荷(Co)為 16670 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -37215,6 +39363,11 @@
       <c r="K430" t="n">
         <v>12020</v>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-40K3 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 40.0mm，珠徑 46.4mm，節圓直徑(PCD) 39.91mm，根徑 6.35mm，珠卷數為 3。 機械性能：剛性達 93 kfg/umk，額定動負荷(C)為 4100 kgf，靜負荷(Co)為 12020 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -37254,6 +39407,11 @@
       <c r="K431" t="n">
         <v>23290</v>
       </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-12K5 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 12.0mm，珠徑 46.6mm，節圓直徑(PCD) 39.91mm，根徑 7.144mm，珠卷數為 5。 機械性能：剛性達 157 kfg/umk，額定動負荷(C)為 7830 kgf，靜負荷(Co)為 23290 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -37293,6 +39451,11 @@
       <c r="K432" t="n">
         <v>23230</v>
       </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-16K5 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 16.0mm，珠徑 46.6mm，節圓直徑(PCD) 39.299mm，根徑 7.144mm，珠卷數為 5。 機械性能：剛性達 159 kfg/umk，額定動負荷(C)為 7810 kgf，靜負荷(Co)為 23230 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -37332,6 +39495,11 @@
       <c r="K433" t="n">
         <v>18330</v>
       </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 45-20K4 (系列: FDC)。 幾何規格：公稱外徑 45mm，導程 20.0mm，珠徑 46.6mm，節圓直徑(PCD) 39.299mm，根徑 7.144mm，珠卷數為 4。 機械性能：剛性達 128 kfg/umk，額定動負荷(C)為 6360 kgf，靜負荷(Co)為 18330 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -37371,6 +39539,11 @@
       <c r="K434" t="n">
         <v>11940</v>
       </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-5K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 5.0mm，珠徑 50.6mm，節圓直徑(PCD) 47.324mm，根徑 3.175mm，珠卷數為 5。 機械性能：剛性達 129 kfg/umk，額定動負荷(C)為 2700 kgf，靜負荷(Co)為 11940 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -37410,6 +39583,11 @@
       <c r="K435" t="n">
         <v>17530</v>
       </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-8K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 8.0mm，珠徑 51.0mm，節圓直徑(PCD) 46.132mm，根徑 4.763mm，珠卷數為 5。 機械性能：剛性達 154 kfg/umk，額定動負荷(C)為 4730 kgf，靜負荷(Co)為 17530 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -37449,6 +39627,11 @@
       <c r="K436" t="n">
         <v>23300</v>
       </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-10K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 10.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 166 kfg/umk，額定動負荷(C)為 7050 kgf，靜負荷(Co)為 23300 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -37488,6 +39671,11 @@
       <c r="K437" t="n">
         <v>23280</v>
       </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 169 kfg/umk，額定動負荷(C)為 7040 kgf，靜負荷(Co)為 23280 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -37527,6 +39715,11 @@
       <c r="K438" t="n">
         <v>23250</v>
       </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-15K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 15.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 171 kfg/umk，額定動負荷(C)為 7030 kgf，靜負荷(Co)為 23250 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -37566,6 +39759,11 @@
       <c r="K439" t="n">
         <v>23230</v>
       </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-16K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 16.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 171 kfg/umk，額定動負荷(C)為 7020 kgf，靜負荷(Co)為 23230 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -37605,6 +39803,11 @@
       <c r="K440" t="n">
         <v>18340</v>
       </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-20K4 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 20.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 138 kfg/umk，額定動負荷(C)為 5720 kgf，靜負荷(Co)為 18340 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -37644,6 +39847,11 @@
       <c r="K441" t="n">
         <v>18260</v>
       </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-25K4 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 25.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 134 kfg/umk，額定動負荷(C)為 5690 kgf，靜負荷(Co)為 18260 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -37683,6 +39891,11 @@
       <c r="K442" t="n">
         <v>18170</v>
       </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-30K4 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 30.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 4。 機械性能：剛性達 136 kfg/umk，額定動負荷(C)為 5650 kgf，靜負荷(Co)為 18170 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -37722,6 +39935,11 @@
       <c r="K443" t="n">
         <v>13840</v>
       </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-35K3 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 35.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 3。 機械性能：剛性達 105 kfg/umk，額定動負荷(C)為 4430 kgf，靜負荷(Co)為 13840 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -37761,6 +39979,11 @@
       <c r="K444" t="n">
         <v>13750</v>
       </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-40K3 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 40.0mm，珠徑 51.4mm，節圓直徑(PCD) 44.91mm，根徑 6.35mm，珠卷數為 3。 機械性能：剛性達 104 kfg/umk，額定動負荷(C)為 4390 kgf，靜負荷(Co)為 13750 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -37800,6 +40023,11 @@
       <c r="K445" t="n">
         <v>9960</v>
       </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-30K2 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 30.0mm，珠徑 51.6mm，節圓直徑(PCD) 44.299mm，根徑 7.144mm，珠卷數為 2。 機械性能：剛性達 70 kfg/umk，額定動負荷(C)為 3560 kgf，靜負荷(Co)為 9960 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -37839,6 +40067,11 @@
       <c r="K446" t="n">
         <v>28776</v>
       </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-12K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 12.0mm，珠徑 51.8mm，節圓直徑(PCD) 43.688mm，根徑 7.938mm，珠卷數為 5。 機械性能：剛性達 173 kfg/umk，額定動負荷(C)為 9480 kgf，靜負荷(Co)為 28776 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -37878,6 +40111,11 @@
       <c r="K447" t="n">
         <v>28710</v>
       </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-16K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 16.0mm，珠徑 51.8mm，節圓直徑(PCD) 43.688mm，根徑 7.938mm，珠卷數為 5。 機械性能：剛性達 175 kfg/umk，額定動負荷(C)為 9450 kgf，靜負荷(Co)為 28710 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -37917,6 +40155,11 @@
       <c r="K448" t="n">
         <v>28630</v>
       </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-20K5 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 20.0mm，珠徑 51.8mm，節圓直徑(PCD) 43.688mm，根徑 7.938mm，珠卷數為 5。 機械性能：剛性達 176 kfg/umk，額定動負荷(C)為 9420 kgf，靜負荷(Co)為 28630 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -37956,6 +40199,11 @@
       <c r="K449" t="n">
         <v>10860</v>
       </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-50K2 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 50.0mm，珠徑 51.8mm，節圓直徑(PCD) 43.688mm，根徑 7.938mm，珠卷數為 2。 機械性能：剛性達 69 kfg/umk，額定動負荷(C)為 3980 kgf，靜負荷(Co)為 10860 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -37995,6 +40243,11 @@
       <c r="K450" t="n">
         <v>27420</v>
       </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 50-20K4 (系列: FDC)。 幾何規格：公稱外徑 50mm，導程 20.0mm，珠徑 52.2mm，節圓直徑(PCD) 42.466mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 149 kfg/umk，額定動負荷(C)為 9870 kgf，靜負荷(Co)為 27420 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -38034,6 +40287,11 @@
       <c r="K451" t="n">
         <v>26157</v>
       </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 55-16K5 (系列: FDC)。 幾何規格：公稱外徑 55mm，導程 16.0mm，珠徑 56.4mm，節圓直徑(PCD) 49.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 185 kfg/umk，額定動負荷(C)為 7420 kgf，靜負荷(Co)為 26157 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -38073,6 +40331,11 @@
       <c r="K452" t="n">
         <v>29190</v>
       </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-10K5 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 10.0mm，珠徑 64.4mm，節圓直徑(PCD) 57.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 192 kfg/umk，額定動負荷(C)為 7720 kgf，靜負荷(Co)為 29190 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -38112,6 +40375,11 @@
       <c r="K453" t="n">
         <v>29180</v>
       </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12K5 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 64.4mm，節圓直徑(PCD) 57.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 196 kfg/umk，額定動負荷(C)為 7720 kgf，靜負荷(Co)為 29180 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -38151,6 +40419,11 @@
       <c r="K454" t="n">
         <v>30020</v>
       </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-20K5 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 20.0mm，珠徑 64.4mm，節圓直徑(PCD) 57.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 208 kfg/umk，額定動負荷(C)為 7850 kgf，靜負荷(Co)為 30020 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -38190,6 +40463,11 @@
       <c r="K455" t="n">
         <v>11100</v>
       </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-40K2 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 40.0mm，珠徑 64.4mm，節圓直徑(PCD) 57.91mm，根徑 6.35mm，珠卷數為 2。 機械性能：剛性達 82 kfg/umk，額定動負荷(C)為 3310 kgf，靜負荷(Co)為 11100 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -38229,6 +40507,11 @@
       <c r="K456" t="n">
         <v>36440</v>
       </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-12K5 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 12.0mm，珠徑 64.8mm，節圓直徑(PCD) 56.688mm，根徑 7.938mm，珠卷數為 5。 機械性能：剛性達 202 kfg/umk，額定動負荷(C)為 10520 kgf，靜負荷(Co)為 36440 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -38268,6 +40551,11 @@
       <c r="K457" t="n">
         <v>34520</v>
       </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-16K4 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 16.0mm，珠徑 65.2mm，節圓直徑(PCD) 55.466mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 175 kfg/umk，額定動負荷(C)為 11010 kgf，靜負荷(Co)為 34520 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -38307,6 +40595,11 @@
       <c r="K458" t="n">
         <v>43530</v>
       </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-20K5 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 20.0mm，珠徑 65.2mm，節圓直徑(PCD) 55.466mm，根徑 9.525mm，珠卷數為 5。 機械性能：剛性達 222 kfg/umk，額定動負荷(C)為 13430 kgf，靜負荷(Co)為 43530 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -38346,6 +40639,11 @@
       <c r="K459" t="n">
         <v>43420</v>
       </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 63-25K5 (系列: FDC)。 幾何規格：公稱外徑 63mm，導程 25.0mm，珠徑 65.2mm，節圓直徑(PCD) 55.466mm，根徑 9.525mm，珠卷數為 5。 機械性能：剛性達 218 kfg/umk，額定動負荷(C)為 13390 kgf，靜負荷(Co)為 43420 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -38385,6 +40683,11 @@
       <c r="K460" t="n">
         <v>38040</v>
       </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-16K4 (系列: FDC)。 幾何規格：公稱外徑 70mm，導程 16.0mm，珠徑 72.2mm，節圓直徑(PCD) 62.466mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 187 kfg/umk，額定動負荷(C)為 11470 kgf，靜負荷(Co)為 38040 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -38424,6 +40727,11 @@
       <c r="K461" t="n">
         <v>37990</v>
       </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 70-20K4 (系列: FDC)。 幾何規格：公稱外徑 70mm，導程 20.0mm，珠徑 72.2mm，節圓直徑(PCD) 62.466mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 190 kfg/umk，額定動負荷(C)為 11450 kgf，靜負荷(Co)為 37990 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -38463,6 +40771,11 @@
       <c r="K462" t="n">
         <v>37980</v>
       </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-10K5 (系列: FDC)。 幾何規格：公稱外徑 80mm，導程 10.0mm，珠徑 81.4mm，節圓直徑(PCD) 74.91mm，根徑 6.35mm，珠卷數為 5。 機械性能：剛性達 223 kfg/umk，額定動負荷(C)為 8620 kgf，靜負荷(Co)為 37980 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -38502,6 +40815,11 @@
       <c r="K463" t="n">
         <v>47130</v>
       </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-12K5 (系列: FDC)。 幾何規格：公稱外徑 80mm，導程 12.0mm，珠徑 81.8mm，節圓直徑(PCD) 73.688mm，根徑 7.938mm，珠卷數為 5。 機械性能：剛性達 238 kfg/umk，額定動負荷(C)為 11740 kgf，靜負荷(Co)為 47130 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -38541,6 +40859,11 @@
       <c r="K464" t="n">
         <v>44960</v>
       </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-16K4 (系列: FDC)。 幾何規格：公稱外徑 80mm，導程 16.0mm，珠徑 82.2mm，節圓直徑(PCD) 73.688mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 206 kfg/umk，額定動負荷(C)為 12410 kgf，靜負荷(Co)為 44960 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -38580,6 +40903,11 @@
       <c r="K465" t="n">
         <v>44910</v>
       </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-20K4 (系列: FDC)。 幾何規格：公稱外徑 80mm，導程 20.0mm，珠徑 82.2mm，節圓直徑(PCD) 73.688mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 212 kfg/umk，額定動負荷(C)為 12400 kgf，靜負荷(Co)為 44910 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -38619,6 +40947,11 @@
       <c r="K466" t="n">
         <v>44840</v>
       </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-25K4 (系列: FDC)。 幾何規格：公稱外徑 80mm，導程 25.0mm，珠徑 82.2mm，節圓直徑(PCD) 72.466mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 211 kfg/umk，額定動負荷(C)為 12370 kgf，靜負荷(Co)為 44840 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -38657,6 +40990,11 @@
       </c>
       <c r="K467" t="n">
         <v>44750</v>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>上銀 HIWIN 滾珠螺桿型號 80-30K4 (系列: FDC)。 幾何規格：公稱外徑 80mm，導程 30.0mm，珠徑 82.2mm，節圓直徑(PCD) 72.466mm，根徑 9.525mm，珠卷數為 4。 機械性能：剛性達 212 kfg/umk，額定動負荷(C)為 12340 kgf，靜負荷(Co)為 44750 kgf。 此型號為雙螺帽設計，具備極高剛性，專為重負荷精密機台開發。</t>
+        </is>
       </c>
     </row>
   </sheetData>
